--- a/3.1.4答案/智能健康监测系统数据集.xlsx
+++ b/3.1.4答案/智能健康监测系统数据集.xlsx
@@ -1,20 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\python_work\2025_AI_operational\AI_operational_ans\3.1.4答案\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="10400"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25605" windowHeight="10395"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$O$169</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId2"/>
+    <pivotCache cacheId="1" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="153">
   <si>
     <t>时间戳</t>
   </si>
@@ -471,23 +477,39 @@
   </si>
   <si>
     <t>2024-09-22 22:00</t>
+  </si>
+  <si>
+    <t>hour</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>行标签</t>
+  </si>
+  <si>
+    <t>总计</t>
+  </si>
+  <si>
+    <t>平均值项:血糖</t>
+  </si>
+  <si>
+    <t>平均值项:体脂分析</t>
+  </si>
+  <si>
+    <t>平均值项:舒张压</t>
+  </si>
+  <si>
+    <t>平均值项:收缩压</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -498,352 +520,28 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -851,253 +549,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1106,69 +562,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" refreshedDate="45785.9247569444" refreshedBy="hello" recordCount="168">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="hello" refreshedDate="45785.924756944398" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="168">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:G169" sheet="Sheet1"/>
   </cacheSource>
@@ -1385,19 +802,19 @@
       </sharedItems>
     </cacheField>
     <cacheField name="血糖" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="4.02" maxValue="7.75" count="70">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="4.0199999999999996" maxValue="7.75" count="70">
         <m/>
         <n v="4.37"/>
         <n v="7.71"/>
         <n v="6.46"/>
-        <n v="4.6"/>
+        <n v="4.5999999999999996"/>
         <n v="6.28"/>
         <n v="5.31"/>
-        <n v="4.06"/>
+        <n v="4.0599999999999996"/>
         <n v="7.56"/>
         <n v="6.2"/>
         <n v="4.91"/>
-        <n v="4.02"/>
+        <n v="4.0199999999999996"/>
         <n v="7.75"/>
         <n v="6.66"/>
         <n v="4.21"/>
@@ -1407,7 +824,7 @@
         <n v="6.94"/>
         <n v="5.86"/>
         <n v="4.49"/>
-        <n v="4.61"/>
+        <n v="4.6100000000000003"/>
         <n v="6.25"/>
         <n v="5.58"/>
         <n v="6.82"/>
@@ -1422,33 +839,33 @@
         <n v="7.74"/>
         <n v="6.62"/>
         <n v="6.37"/>
-        <n v="4.64"/>
+        <n v="4.6399999999999997"/>
         <n v="4.12"/>
         <n v="6.89"/>
         <n v="5.07"/>
         <n v="6.47"/>
-        <n v="4.31"/>
+        <n v="4.3099999999999996"/>
         <n v="6.09"/>
         <n v="4.38"/>
         <n v="4.97"/>
         <n v="7.4"/>
         <n v="6.88"/>
-        <n v="4.89"/>
+        <n v="4.8899999999999997"/>
         <n v="7.08"/>
         <n v="6.84"/>
         <n v="4.09"/>
         <n v="6.35"/>
         <n v="5.09"/>
         <n v="4.53"/>
-        <n v="4.39"/>
+        <n v="4.3899999999999997"/>
         <n v="6.49"/>
-        <n v="4.36"/>
+        <n v="4.3600000000000003"/>
         <n v="6.51"/>
-        <n v="4.14"/>
+        <n v="4.1399999999999997"/>
         <n v="7.44"/>
         <n v="5.15"/>
         <n v="5.19"/>
-        <n v="4.77"/>
+        <n v="4.7699999999999996"/>
         <n v="6.36"/>
         <n v="5.01"/>
         <n v="4.82"/>
@@ -1470,7 +887,7 @@
         <n v="0.5"/>
         <n v="0.89"/>
         <n v="0.69"/>
-        <n v="0.57"/>
+        <n v="0.56999999999999995"/>
         <n v="0.74"/>
         <n v="0.7"/>
         <n v="0.78"/>
@@ -1484,12 +901,12 @@
         <n v="0.39"/>
         <n v="0.66"/>
         <n v="0.87"/>
-        <n v="0.28"/>
+        <n v="0.28000000000000003"/>
         <n v="0.37"/>
         <n v="0.65"/>
         <n v="0.23"/>
         <n v="0.86"/>
-        <n v="0.56"/>
+        <n v="0.56000000000000005"/>
         <n v="0.27"/>
         <n v="0.33"/>
         <n v="0.64"/>
@@ -1527,14 +944,14 @@
         <n v="0.38"/>
         <n v="0.93"/>
         <n v="0.36"/>
-        <n v="0.58"/>
+        <n v="0.57999999999999996"/>
         <n v="0.3"/>
         <n v="0.35"/>
         <n v="0.26"/>
         <n v="0.91"/>
         <n v="0.24"/>
         <n v="0.84"/>
-        <n v="0.29"/>
+        <n v="0.28999999999999998"/>
         <n v="0.34"/>
       </sharedItems>
     </cacheField>
@@ -1558,6 +975,11 @@
       </sharedItems>
     </cacheField>
   </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
 </pivotCacheDefinition>
 </file>
 
@@ -3079,7 +2501,123 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" autoFormatId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" useAutoFormatting="1" compact="0" indent="0" outline="1" compactData="0" outlineData="1" showDrill="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="数据透视表1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:E19" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="16">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="16">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+  </colItems>
+  <dataFields count="4">
+    <dataField name="平均值项:血糖" fld="3" subtotal="average" baseField="6" baseItem="0"/>
+    <dataField name="平均值项:体脂分析" fld="4" subtotal="average" baseField="6" baseItem="0"/>
+    <dataField name="平均值项:舒张压" fld="2" subtotal="average" baseField="6" baseItem="0"/>
+    <dataField name="平均值项:收缩压" fld="1" subtotal="average" baseField="6" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" createdVersion="5" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0">
   <location ref="L9:O25" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField compact="0" showAll="0"/>
@@ -3181,7 +2719,7 @@
     <dataField name="Average of 体脂分析" fld="4" subtotal="average" baseField="0" baseItem="0"/>
     <dataField name="Average of 舒张压" fld="2" subtotal="average" baseField="0" baseItem="0"/>
   </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -3469,22 +3007,271 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:O169"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A3:E19"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="17.3636363636364" style="1" customWidth="1"/>
-    <col min="2" max="6" width="8.72727272727273" style="1"/>
-    <col min="12" max="12" width="11.6363636363636"/>
-    <col min="13" max="15" width="20.0909090909091"/>
+    <col min="1" max="1" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6">
+        <v>79.875</v>
+      </c>
+      <c r="E4" s="6">
+        <v>110.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6">
+        <v>81.375</v>
+      </c>
+      <c r="E5" s="6">
+        <v>113.75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="6">
+        <v>4.4824999999999999</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.16999999999999998</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6">
+        <v>72.375</v>
+      </c>
+      <c r="E7" s="6">
+        <v>131.375</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="6">
+        <v>6.8949999999999996</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="6">
+        <v>5.9312499999999995</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6">
+        <v>72.5</v>
+      </c>
+      <c r="E10" s="6">
+        <v>115.875</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="6">
+        <v>4.6387499999999999</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6">
+        <v>70.25</v>
+      </c>
+      <c r="E11" s="6">
+        <v>118.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="6">
+        <v>6.8125</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6">
+        <v>72.5</v>
+      </c>
+      <c r="E12" s="6">
+        <v>115.375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" s="6">
+        <v>6.1987500000000013</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6">
+        <v>73</v>
+      </c>
+      <c r="E14" s="6">
+        <v>114.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="6">
+        <v>4.2712500000000002</v>
+      </c>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6">
+        <v>77</v>
+      </c>
+      <c r="E15" s="6">
+        <v>106.875</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="6">
+        <v>6.8087499999999999</v>
+      </c>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6">
+        <v>74.375</v>
+      </c>
+      <c r="E16" s="6">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="6">
+        <v>5.8325000000000005</v>
+      </c>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="6">
+        <v>4.5887500000000001</v>
+      </c>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6">
+        <v>72</v>
+      </c>
+      <c r="E18" s="6">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="B19" s="6">
+        <v>5.6459999999999981</v>
+      </c>
+      <c r="C19" s="6">
+        <v>0.16999999999999998</v>
+      </c>
+      <c r="D19" s="6">
+        <v>74.525000000000006</v>
+      </c>
+      <c r="E19" s="6">
+        <v>114.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O169"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="17.375" style="1" customWidth="1"/>
+    <col min="2" max="6" width="8.75" style="1"/>
+    <col min="12" max="12" width="11.625"/>
+    <col min="13" max="15" width="20.125"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3506,8 +3293,11 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -3524,8 +3314,12 @@
         <f>RIGHT(A2,5)</f>
         <v>00:00</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2" t="str">
+        <f>TEXT(A2,"HH:MM")</f>
+        <v>00:00</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -3542,8 +3336,12 @@
         <f t="shared" ref="G3:G47" si="0">RIGHT(A3,5)</f>
         <v>06:00</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H66" si="1">TEXT(A3,"HH:MM")</f>
+        <v>06:00</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -3557,8 +3355,12 @@
         <f t="shared" si="0"/>
         <v>07:00</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="H4" t="str">
+        <f t="shared" si="1"/>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -3572,8 +3374,12 @@
         <f t="shared" si="0"/>
         <v>07:00</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5" t="str">
+        <f t="shared" si="1"/>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -3584,14 +3390,18 @@
         <v>74</v>
       </c>
       <c r="F6" s="1">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="G6" t="str">
         <f t="shared" si="0"/>
         <v>07:30</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6" t="str">
+        <f t="shared" si="1"/>
+        <v>07:30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -3605,8 +3415,12 @@
         <f t="shared" si="0"/>
         <v>08:00</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="H7" t="str">
+        <f t="shared" si="1"/>
+        <v>08:00</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -3620,6 +3434,10 @@
         <f t="shared" si="0"/>
         <v>09:00</v>
       </c>
+      <c r="H8" t="str">
+        <f t="shared" si="1"/>
+        <v>09:00</v>
+      </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="1" t="s">
@@ -3638,6 +3456,10 @@
         <f t="shared" si="0"/>
         <v>10:00</v>
       </c>
+      <c r="H9" t="str">
+        <f t="shared" si="1"/>
+        <v>10:00</v>
+      </c>
       <c r="L9" t="s">
         <v>6</v>
       </c>
@@ -3656,7 +3478,7 @@
         <v>17</v>
       </c>
       <c r="D10" s="1">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F10" s="1">
         <v>0.47</v>
@@ -3665,11 +3487,13 @@
         <f t="shared" si="0"/>
         <v>12:00</v>
       </c>
+      <c r="H10" t="str">
+        <f t="shared" si="1"/>
+        <v>12:00</v>
+      </c>
       <c r="L10" t="s">
         <v>18</v>
       </c>
-      <c r="M10"/>
-      <c r="N10"/>
       <c r="O10">
         <v>79.875</v>
       </c>
@@ -3691,16 +3515,18 @@
         <f t="shared" si="0"/>
         <v>12:00</v>
       </c>
+      <c r="H11" t="str">
+        <f t="shared" si="1"/>
+        <v>12:00</v>
+      </c>
       <c r="L11" t="s">
         <v>19</v>
       </c>
-      <c r="M11"/>
-      <c r="N11"/>
       <c r="O11">
         <v>81.375</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:15">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -3714,11 +3540,15 @@
         <f t="shared" si="0"/>
         <v>13:00</v>
       </c>
+      <c r="H12" t="str">
+        <f t="shared" si="1"/>
+        <v>13:00</v>
+      </c>
       <c r="L12" t="s">
         <v>21</v>
       </c>
       <c r="M12">
-        <v>4.4825</v>
+        <v>4.4824999999999999</v>
       </c>
       <c r="N12">
         <v>0.17</v>
@@ -3741,16 +3571,18 @@
         <f t="shared" si="0"/>
         <v>13:00</v>
       </c>
+      <c r="H13" t="str">
+        <f t="shared" si="1"/>
+        <v>13:00</v>
+      </c>
       <c r="L13" t="s">
         <v>22</v>
       </c>
-      <c r="M13"/>
-      <c r="N13"/>
       <c r="O13">
         <v>72.375</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:15">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
@@ -3764,14 +3596,18 @@
         <f t="shared" si="0"/>
         <v>14:00</v>
       </c>
+      <c r="H14" t="str">
+        <f t="shared" si="1"/>
+        <v>14:00</v>
+      </c>
       <c r="L14" t="s">
         <v>24</v>
       </c>
       <c r="M14">
-        <v>6.895</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>6.8949999999999996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="1" t="s">
         <v>25</v>
       </c>
@@ -3788,11 +3624,15 @@
         <f t="shared" si="0"/>
         <v>16:00</v>
       </c>
+      <c r="H15" t="str">
+        <f t="shared" si="1"/>
+        <v>16:00</v>
+      </c>
       <c r="L15" t="s">
         <v>26</v>
       </c>
       <c r="M15">
-        <v>5.93125</v>
+        <v>5.9312500000000004</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -3800,7 +3640,7 @@
         <v>27</v>
       </c>
       <c r="D16" s="1">
-        <v>4.06</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="F16" s="1">
         <v>0.97</v>
@@ -3809,11 +3649,13 @@
         <f t="shared" si="0"/>
         <v>18:00</v>
       </c>
+      <c r="H16" t="str">
+        <f t="shared" si="1"/>
+        <v>18:00</v>
+      </c>
       <c r="L16" t="s">
         <v>28</v>
       </c>
-      <c r="M16"/>
-      <c r="N16"/>
       <c r="O16">
         <v>72.5</v>
       </c>
@@ -3835,13 +3677,16 @@
         <f t="shared" si="0"/>
         <v>18:00</v>
       </c>
+      <c r="H17" t="str">
+        <f t="shared" si="1"/>
+        <v>18:00</v>
+      </c>
       <c r="L17" t="s">
         <v>29</v>
       </c>
       <c r="M17">
-        <v>4.63875</v>
-      </c>
-      <c r="N17"/>
+        <v>4.6387499999999999</v>
+      </c>
       <c r="O17">
         <v>70.25</v>
       </c>
@@ -3860,18 +3705,21 @@
         <f t="shared" si="0"/>
         <v>19:00</v>
       </c>
+      <c r="H18" t="str">
+        <f t="shared" si="1"/>
+        <v>19:00</v>
+      </c>
       <c r="L18" t="s">
         <v>31</v>
       </c>
       <c r="M18">
         <v>6.8125</v>
       </c>
-      <c r="N18"/>
       <c r="O18">
         <v>72.5</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:15">
       <c r="A19" s="1" t="s">
         <v>30</v>
       </c>
@@ -3888,11 +3736,15 @@
         <f t="shared" si="0"/>
         <v>19:00</v>
       </c>
+      <c r="H19" t="str">
+        <f t="shared" si="1"/>
+        <v>19:00</v>
+      </c>
       <c r="L19" t="s">
         <v>32</v>
       </c>
       <c r="M19">
-        <v>6.19875</v>
+        <v>6.1987500000000004</v>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -3909,11 +3761,13 @@
         <f t="shared" si="0"/>
         <v>20:00</v>
       </c>
+      <c r="H20" t="str">
+        <f t="shared" si="1"/>
+        <v>20:00</v>
+      </c>
       <c r="L20" t="s">
         <v>34</v>
       </c>
-      <c r="M20"/>
-      <c r="N20"/>
       <c r="O20">
         <v>73</v>
       </c>
@@ -3932,13 +3786,16 @@
         <f t="shared" si="0"/>
         <v>22:00</v>
       </c>
+      <c r="H21" t="str">
+        <f t="shared" si="1"/>
+        <v>22:00</v>
+      </c>
       <c r="L21" t="s">
         <v>36</v>
       </c>
       <c r="M21">
-        <v>4.27125</v>
-      </c>
-      <c r="N21"/>
+        <v>4.2712500000000002</v>
+      </c>
       <c r="O21">
         <v>77</v>
       </c>
@@ -3960,18 +3817,21 @@
         <f t="shared" si="0"/>
         <v>22:00</v>
       </c>
+      <c r="H22" t="str">
+        <f t="shared" si="1"/>
+        <v>22:00</v>
+      </c>
       <c r="L22" t="s">
         <v>37</v>
       </c>
       <c r="M22">
-        <v>6.80875</v>
-      </c>
-      <c r="N22"/>
+        <v>6.8087499999999999</v>
+      </c>
       <c r="O22">
         <v>74.375</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:15">
       <c r="A23" s="1" t="s">
         <v>38</v>
       </c>
@@ -3982,17 +3842,21 @@
         <v>74</v>
       </c>
       <c r="F23" s="1">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G23" t="str">
         <f t="shared" si="0"/>
         <v>00:00</v>
       </c>
+      <c r="H23" t="str">
+        <f t="shared" si="1"/>
+        <v>00:00</v>
+      </c>
       <c r="L23" t="s">
         <v>39</v>
       </c>
       <c r="M23">
-        <v>5.8325</v>
+        <v>5.8324999999999996</v>
       </c>
     </row>
     <row r="24" spans="1:15">
@@ -4012,13 +3876,16 @@
         <f t="shared" si="0"/>
         <v>06:00</v>
       </c>
+      <c r="H24" t="str">
+        <f t="shared" si="1"/>
+        <v>06:00</v>
+      </c>
       <c r="L24" t="s">
         <v>41</v>
       </c>
       <c r="M24">
-        <v>4.58875</v>
-      </c>
-      <c r="N24"/>
+        <v>4.5887500000000001</v>
+      </c>
       <c r="O24">
         <v>72</v>
       </c>
@@ -4028,7 +3895,7 @@
         <v>42</v>
       </c>
       <c r="D25" s="1">
-        <v>4.02</v>
+        <v>4.0199999999999996</v>
       </c>
       <c r="F25" s="1">
         <v>0.8</v>
@@ -4037,20 +3904,24 @@
         <f t="shared" si="0"/>
         <v>07:00</v>
       </c>
+      <c r="H25" t="str">
+        <f t="shared" si="1"/>
+        <v>07:00</v>
+      </c>
       <c r="L25" t="s">
         <v>43</v>
       </c>
       <c r="M25">
-        <v>5.646</v>
+        <v>5.6459999999999999</v>
       </c>
       <c r="N25">
         <v>0.17</v>
       </c>
       <c r="O25">
-        <v>74.525</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
+        <v>74.525000000000006</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" s="1" t="s">
         <v>42</v>
       </c>
@@ -4064,8 +3935,12 @@
         <f t="shared" si="0"/>
         <v>07:00</v>
       </c>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="H26" t="str">
+        <f t="shared" si="1"/>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" s="1" t="s">
         <v>44</v>
       </c>
@@ -4082,8 +3957,12 @@
         <f t="shared" si="0"/>
         <v>07:30</v>
       </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="H27" t="str">
+        <f t="shared" si="1"/>
+        <v>07:30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" s="1" t="s">
         <v>45</v>
       </c>
@@ -4097,8 +3976,12 @@
         <f t="shared" si="0"/>
         <v>08:00</v>
       </c>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="H28" t="str">
+        <f t="shared" si="1"/>
+        <v>08:00</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" s="1" t="s">
         <v>46</v>
       </c>
@@ -4112,8 +3995,12 @@
         <f t="shared" si="0"/>
         <v>09:00</v>
       </c>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="H29" t="str">
+        <f t="shared" si="1"/>
+        <v>09:00</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" s="1" t="s">
         <v>47</v>
       </c>
@@ -4124,14 +4011,18 @@
         <v>61</v>
       </c>
       <c r="F30" s="1">
-        <v>0.56</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="G30" t="str">
         <f t="shared" si="0"/>
         <v>10:00</v>
       </c>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="H30" t="str">
+        <f t="shared" si="1"/>
+        <v>10:00</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" s="1" t="s">
         <v>48</v>
       </c>
@@ -4145,8 +4036,12 @@
         <f t="shared" si="0"/>
         <v>12:00</v>
       </c>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="H31" t="str">
+        <f t="shared" si="1"/>
+        <v>12:00</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" s="1" t="s">
         <v>48</v>
       </c>
@@ -4163,8 +4058,12 @@
         <f t="shared" si="0"/>
         <v>12:00</v>
       </c>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="H32" t="str">
+        <f t="shared" si="1"/>
+        <v>12:00</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
         <v>49</v>
       </c>
@@ -4178,8 +4077,12 @@
         <f t="shared" si="0"/>
         <v>13:00</v>
       </c>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="H33" t="str">
+        <f t="shared" si="1"/>
+        <v>13:00</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
         <v>49</v>
       </c>
@@ -4196,8 +4099,12 @@
         <f t="shared" si="0"/>
         <v>13:00</v>
       </c>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="H34" t="str">
+        <f t="shared" si="1"/>
+        <v>13:00</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
         <v>50</v>
       </c>
@@ -4211,8 +4118,12 @@
         <f t="shared" si="0"/>
         <v>14:00</v>
       </c>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="H35" t="str">
+        <f t="shared" si="1"/>
+        <v>14:00</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
         <v>51</v>
       </c>
@@ -4229,8 +4140,12 @@
         <f t="shared" si="0"/>
         <v>16:00</v>
       </c>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="H36" t="str">
+        <f t="shared" si="1"/>
+        <v>16:00</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
         <v>52</v>
       </c>
@@ -4244,8 +4159,12 @@
         <f t="shared" si="0"/>
         <v>18:00</v>
       </c>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="H37" t="str">
+        <f t="shared" si="1"/>
+        <v>18:00</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
         <v>52</v>
       </c>
@@ -4262,8 +4181,12 @@
         <f t="shared" si="0"/>
         <v>18:00</v>
       </c>
-    </row>
-    <row r="39" spans="1:7">
+      <c r="H38" t="str">
+        <f t="shared" si="1"/>
+        <v>18:00</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
         <v>53</v>
       </c>
@@ -4271,14 +4194,18 @@
         <v>6.94</v>
       </c>
       <c r="F39" s="1">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="G39" t="str">
         <f t="shared" si="0"/>
         <v>19:00</v>
       </c>
-    </row>
-    <row r="40" spans="1:7">
+      <c r="H39" t="str">
+        <f t="shared" si="1"/>
+        <v>19:00</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
         <v>53</v>
       </c>
@@ -4295,8 +4222,12 @@
         <f t="shared" si="0"/>
         <v>19:00</v>
       </c>
-    </row>
-    <row r="41" spans="1:7">
+      <c r="H40" t="str">
+        <f t="shared" si="1"/>
+        <v>19:00</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
         <v>54</v>
       </c>
@@ -4310,8 +4241,12 @@
         <f t="shared" si="0"/>
         <v>20:00</v>
       </c>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="H41" t="str">
+        <f t="shared" si="1"/>
+        <v>20:00</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
         <v>55</v>
       </c>
@@ -4325,8 +4260,12 @@
         <f t="shared" si="0"/>
         <v>22:00</v>
       </c>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="H42" t="str">
+        <f t="shared" si="1"/>
+        <v>22:00</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
         <v>55</v>
       </c>
@@ -4343,8 +4282,12 @@
         <f t="shared" si="0"/>
         <v>22:00</v>
       </c>
-    </row>
-    <row r="44" spans="1:7">
+      <c r="H43" t="str">
+        <f t="shared" si="1"/>
+        <v>22:00</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
         <v>56</v>
       </c>
@@ -4361,8 +4304,12 @@
         <f t="shared" si="0"/>
         <v>00:00</v>
       </c>
-    </row>
-    <row r="45" spans="1:7">
+      <c r="H44" t="str">
+        <f t="shared" si="1"/>
+        <v>00:00</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
         <v>57</v>
       </c>
@@ -4379,13 +4326,17 @@
         <f t="shared" si="0"/>
         <v>06:00</v>
       </c>
-    </row>
-    <row r="46" spans="1:7">
+      <c r="H45" t="str">
+        <f t="shared" si="1"/>
+        <v>06:00</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D46" s="1">
-        <v>4.61</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="F46" s="1">
         <v>0.59</v>
@@ -4394,8 +4345,12 @@
         <f t="shared" si="0"/>
         <v>07:00</v>
       </c>
-    </row>
-    <row r="47" spans="1:7">
+      <c r="H46" t="str">
+        <f t="shared" si="1"/>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
         <v>58</v>
       </c>
@@ -4409,8 +4364,12 @@
         <f t="shared" si="0"/>
         <v>07:00</v>
       </c>
-    </row>
-    <row r="48" spans="1:7">
+      <c r="H47" t="str">
+        <f t="shared" si="1"/>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
         <v>59</v>
       </c>
@@ -4424,11 +4383,15 @@
         <v>0.6</v>
       </c>
       <c r="G48" t="str">
-        <f t="shared" ref="G48:G79" si="1">RIGHT(A48,5)</f>
+        <f t="shared" ref="G48:G79" si="2">RIGHT(A48,5)</f>
         <v>07:30</v>
       </c>
-    </row>
-    <row r="49" spans="1:7">
+      <c r="H48" t="str">
+        <f t="shared" si="1"/>
+        <v>07:30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
         <v>60</v>
       </c>
@@ -4439,11 +4402,15 @@
         <v>0.76</v>
       </c>
       <c r="G49" t="str">
+        <f t="shared" si="2"/>
+        <v>08:00</v>
+      </c>
+      <c r="H49" t="str">
         <f t="shared" si="1"/>
         <v>08:00</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
         <v>61</v>
       </c>
@@ -4454,11 +4421,15 @@
         <v>0.46</v>
       </c>
       <c r="G50" t="str">
+        <f t="shared" si="2"/>
+        <v>09:00</v>
+      </c>
+      <c r="H50" t="str">
         <f t="shared" si="1"/>
         <v>09:00</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
         <v>62</v>
       </c>
@@ -4472,11 +4443,15 @@
         <v>0.61</v>
       </c>
       <c r="G51" t="str">
+        <f t="shared" si="2"/>
+        <v>10:00</v>
+      </c>
+      <c r="H51" t="str">
         <f t="shared" si="1"/>
         <v>10:00</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
         <v>63</v>
       </c>
@@ -4487,11 +4462,15 @@
         <v>0.52</v>
       </c>
       <c r="G52" t="str">
+        <f t="shared" si="2"/>
+        <v>12:00</v>
+      </c>
+      <c r="H52" t="str">
         <f t="shared" si="1"/>
         <v>12:00</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
         <v>63</v>
       </c>
@@ -4505,11 +4484,15 @@
         <v>0.53</v>
       </c>
       <c r="G53" t="str">
+        <f t="shared" si="2"/>
+        <v>12:00</v>
+      </c>
+      <c r="H53" t="str">
         <f t="shared" si="1"/>
         <v>12:00</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
         <v>64</v>
       </c>
@@ -4520,11 +4503,15 @@
         <v>0.79</v>
       </c>
       <c r="G54" t="str">
+        <f t="shared" si="2"/>
+        <v>13:00</v>
+      </c>
+      <c r="H54" t="str">
         <f t="shared" si="1"/>
         <v>13:00</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
         <v>64</v>
       </c>
@@ -4538,11 +4525,15 @@
         <v>0.44</v>
       </c>
       <c r="G55" t="str">
+        <f t="shared" si="2"/>
+        <v>13:00</v>
+      </c>
+      <c r="H55" t="str">
         <f t="shared" si="1"/>
         <v>13:00</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
         <v>65</v>
       </c>
@@ -4553,11 +4544,15 @@
         <v>0.8</v>
       </c>
       <c r="G56" t="str">
+        <f t="shared" si="2"/>
+        <v>14:00</v>
+      </c>
+      <c r="H56" t="str">
         <f t="shared" si="1"/>
         <v>14:00</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
         <v>66</v>
       </c>
@@ -4571,11 +4566,15 @@
         <v>0.45</v>
       </c>
       <c r="G57" t="str">
+        <f t="shared" si="2"/>
+        <v>16:00</v>
+      </c>
+      <c r="H57" t="str">
         <f t="shared" si="1"/>
         <v>16:00</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
         <v>67</v>
       </c>
@@ -4586,11 +4585,15 @@
         <v>0.62</v>
       </c>
       <c r="G58" t="str">
+        <f t="shared" si="2"/>
+        <v>18:00</v>
+      </c>
+      <c r="H58" t="str">
         <f t="shared" si="1"/>
         <v>18:00</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
         <v>67</v>
       </c>
@@ -4604,11 +4607,15 @@
         <v>0.61</v>
       </c>
       <c r="G59" t="str">
+        <f t="shared" si="2"/>
+        <v>18:00</v>
+      </c>
+      <c r="H59" t="str">
         <f t="shared" si="1"/>
         <v>18:00</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
         <v>68</v>
       </c>
@@ -4619,11 +4626,15 @@
         <v>0.94</v>
       </c>
       <c r="G60" t="str">
+        <f t="shared" si="2"/>
+        <v>19:00</v>
+      </c>
+      <c r="H60" t="str">
         <f t="shared" si="1"/>
         <v>19:00</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
         <v>68</v>
       </c>
@@ -4637,11 +4648,15 @@
         <v>0.65</v>
       </c>
       <c r="G61" t="str">
+        <f t="shared" si="2"/>
+        <v>19:00</v>
+      </c>
+      <c r="H61" t="str">
         <f t="shared" si="1"/>
         <v>19:00</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
         <v>69</v>
       </c>
@@ -4652,11 +4667,15 @@
         <v>0.76</v>
       </c>
       <c r="G62" t="str">
+        <f t="shared" si="2"/>
+        <v>20:00</v>
+      </c>
+      <c r="H62" t="str">
         <f t="shared" si="1"/>
         <v>20:00</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
         <v>70</v>
       </c>
@@ -4667,11 +4686,15 @@
         <v>0.51</v>
       </c>
       <c r="G63" t="str">
+        <f t="shared" si="2"/>
+        <v>22:00</v>
+      </c>
+      <c r="H63" t="str">
         <f t="shared" si="1"/>
         <v>22:00</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
         <v>70</v>
       </c>
@@ -4685,11 +4708,15 @@
         <v>0.4</v>
       </c>
       <c r="G64" t="str">
+        <f t="shared" si="2"/>
+        <v>22:00</v>
+      </c>
+      <c r="H64" t="str">
         <f t="shared" si="1"/>
         <v>22:00</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
         <v>71</v>
       </c>
@@ -4703,11 +4730,15 @@
         <v>0.62</v>
       </c>
       <c r="G65" t="str">
+        <f t="shared" si="2"/>
+        <v>00:00</v>
+      </c>
+      <c r="H65" t="str">
         <f t="shared" si="1"/>
         <v>00:00</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
         <v>72</v>
       </c>
@@ -4721,26 +4752,34 @@
         <v>0.53</v>
       </c>
       <c r="G66" t="str">
+        <f t="shared" si="2"/>
+        <v>06:00</v>
+      </c>
+      <c r="H66" t="str">
         <f t="shared" si="1"/>
         <v>06:00</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D67" s="1">
-        <v>4.61</v>
+        <v>4.6100000000000003</v>
       </c>
       <c r="F67" s="1">
         <v>0.42</v>
       </c>
       <c r="G67" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>07:00</v>
       </c>
-    </row>
-    <row r="68" spans="1:7">
+      <c r="H67" t="str">
+        <f t="shared" ref="H67:H130" si="3">TEXT(A67,"HH:MM")</f>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
         <v>73</v>
       </c>
@@ -4751,11 +4790,15 @@
         <v>0.64</v>
       </c>
       <c r="G68" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>07:00</v>
       </c>
-    </row>
-    <row r="69" spans="1:7">
+      <c r="H68" t="str">
+        <f t="shared" si="3"/>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
         <v>74</v>
       </c>
@@ -4769,11 +4812,15 @@
         <v>0.62</v>
       </c>
       <c r="G69" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>07:30</v>
       </c>
-    </row>
-    <row r="70" spans="1:7">
+      <c r="H69" t="str">
+        <f t="shared" si="3"/>
+        <v>07:30</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
         <v>75</v>
       </c>
@@ -4784,11 +4831,15 @@
         <v>0.48</v>
       </c>
       <c r="G70" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>08:00</v>
       </c>
-    </row>
-    <row r="71" spans="1:7">
+      <c r="H70" t="str">
+        <f t="shared" si="3"/>
+        <v>08:00</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
         <v>76</v>
       </c>
@@ -4799,11 +4850,15 @@
         <v>0.98</v>
       </c>
       <c r="G71" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>09:00</v>
       </c>
-    </row>
-    <row r="72" spans="1:7">
+      <c r="H71" t="str">
+        <f t="shared" si="3"/>
+        <v>09:00</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
         <v>77</v>
       </c>
@@ -4817,11 +4872,15 @@
         <v>0.64</v>
       </c>
       <c r="G72" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10:00</v>
       </c>
-    </row>
-    <row r="73" spans="1:7">
+      <c r="H72" t="str">
+        <f t="shared" si="3"/>
+        <v>10:00</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
         <v>78</v>
       </c>
@@ -4832,11 +4891,15 @@
         <v>0.63</v>
       </c>
       <c r="G73" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12:00</v>
       </c>
-    </row>
-    <row r="74" spans="1:7">
+      <c r="H73" t="str">
+        <f t="shared" si="3"/>
+        <v>12:00</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
         <v>78</v>
       </c>
@@ -4850,11 +4913,15 @@
         <v>0.49</v>
       </c>
       <c r="G74" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12:00</v>
       </c>
-    </row>
-    <row r="75" spans="1:7">
+      <c r="H74" t="str">
+        <f t="shared" si="3"/>
+        <v>12:00</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
         <v>79</v>
       </c>
@@ -4865,11 +4932,15 @@
         <v>0.69</v>
       </c>
       <c r="G75" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13:00</v>
       </c>
-    </row>
-    <row r="76" spans="1:7">
+      <c r="H75" t="str">
+        <f t="shared" si="3"/>
+        <v>13:00</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
         <v>79</v>
       </c>
@@ -4883,11 +4954,15 @@
         <v>0.71</v>
       </c>
       <c r="G76" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13:00</v>
       </c>
-    </row>
-    <row r="77" spans="1:7">
+      <c r="H76" t="str">
+        <f t="shared" si="3"/>
+        <v>13:00</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
         <v>80</v>
       </c>
@@ -4898,11 +4973,15 @@
         <v>0.95</v>
       </c>
       <c r="G77" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14:00</v>
       </c>
-    </row>
-    <row r="78" spans="1:7">
+      <c r="H77" t="str">
+        <f t="shared" si="3"/>
+        <v>14:00</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
       <c r="A78" s="1" t="s">
         <v>81</v>
       </c>
@@ -4916,11 +4995,15 @@
         <v>0.89</v>
       </c>
       <c r="G78" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16:00</v>
       </c>
-    </row>
-    <row r="79" spans="1:7">
+      <c r="H78" t="str">
+        <f t="shared" si="3"/>
+        <v>16:00</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
         <v>82</v>
       </c>
@@ -4931,11 +5014,15 @@
         <v>0.22</v>
       </c>
       <c r="G79" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>18:00</v>
       </c>
-    </row>
-    <row r="80" spans="1:7">
+      <c r="H79" t="str">
+        <f t="shared" si="3"/>
+        <v>18:00</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
         <v>82</v>
       </c>
@@ -4949,11 +5036,15 @@
         <v>0.77</v>
       </c>
       <c r="G80" t="str">
-        <f t="shared" ref="G80:G111" si="2">RIGHT(A80,5)</f>
+        <f t="shared" ref="G80:G111" si="4">RIGHT(A80,5)</f>
         <v>18:00</v>
       </c>
-    </row>
-    <row r="81" spans="1:7">
+      <c r="H80" t="str">
+        <f t="shared" si="3"/>
+        <v>18:00</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
         <v>83</v>
       </c>
@@ -4964,11 +5055,15 @@
         <v>0.8</v>
       </c>
       <c r="G81" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>19:00</v>
       </c>
-    </row>
-    <row r="82" spans="1:7">
+      <c r="H81" t="str">
+        <f t="shared" si="3"/>
+        <v>19:00</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
         <v>83</v>
       </c>
@@ -4982,11 +5077,15 @@
         <v>0.95</v>
       </c>
       <c r="G82" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>19:00</v>
       </c>
-    </row>
-    <row r="83" spans="1:7">
+      <c r="H82" t="str">
+        <f t="shared" si="3"/>
+        <v>19:00</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
         <v>84</v>
       </c>
@@ -4997,26 +5096,34 @@
         <v>0.23</v>
       </c>
       <c r="G83" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20:00</v>
       </c>
-    </row>
-    <row r="84" spans="1:7">
+      <c r="H83" t="str">
+        <f t="shared" si="3"/>
+        <v>20:00</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D84" s="1">
-        <v>4.64</v>
+        <v>4.6399999999999997</v>
       </c>
       <c r="F84" s="1">
         <v>0.63</v>
       </c>
       <c r="G84" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>22:00</v>
       </c>
-    </row>
-    <row r="85" spans="1:7">
+      <c r="H84" t="str">
+        <f t="shared" si="3"/>
+        <v>22:00</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
         <v>85</v>
       </c>
@@ -5030,11 +5137,15 @@
         <v>0.73</v>
       </c>
       <c r="G85" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>22:00</v>
       </c>
-    </row>
-    <row r="86" spans="1:7">
+      <c r="H85" t="str">
+        <f t="shared" si="3"/>
+        <v>22:00</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
       <c r="A86" s="1" t="s">
         <v>86</v>
       </c>
@@ -5048,11 +5159,15 @@
         <v>0.63</v>
       </c>
       <c r="G86" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>00:00</v>
       </c>
-    </row>
-    <row r="87" spans="1:7">
+      <c r="H86" t="str">
+        <f t="shared" si="3"/>
+        <v>00:00</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
       <c r="A87" s="1" t="s">
         <v>87</v>
       </c>
@@ -5066,11 +5181,15 @@
         <v>0.92</v>
       </c>
       <c r="G87" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>06:00</v>
       </c>
-    </row>
-    <row r="88" spans="1:7">
+      <c r="H87" t="str">
+        <f t="shared" si="3"/>
+        <v>06:00</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
         <v>88</v>
       </c>
@@ -5081,11 +5200,15 @@
         <v>0.78</v>
       </c>
       <c r="G88" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>07:00</v>
       </c>
-    </row>
-    <row r="89" spans="1:7">
+      <c r="H88" t="str">
+        <f t="shared" si="3"/>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
         <v>88</v>
       </c>
@@ -5096,11 +5219,15 @@
         <v>0.66</v>
       </c>
       <c r="G89" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>07:00</v>
       </c>
-    </row>
-    <row r="90" spans="1:7">
+      <c r="H89" t="str">
+        <f t="shared" si="3"/>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
       <c r="A90" s="1" t="s">
         <v>89</v>
       </c>
@@ -5114,11 +5241,15 @@
         <v>0.82</v>
       </c>
       <c r="G90" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>07:30</v>
       </c>
-    </row>
-    <row r="91" spans="1:7">
+      <c r="H90" t="str">
+        <f t="shared" si="3"/>
+        <v>07:30</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
       <c r="A91" s="1" t="s">
         <v>90</v>
       </c>
@@ -5129,11 +5260,15 @@
         <v>0.39</v>
       </c>
       <c r="G91" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>08:00</v>
       </c>
-    </row>
-    <row r="92" spans="1:7">
+      <c r="H91" t="str">
+        <f t="shared" si="3"/>
+        <v>08:00</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
       <c r="A92" s="1" t="s">
         <v>91</v>
       </c>
@@ -5144,11 +5279,15 @@
         <v>0.69</v>
       </c>
       <c r="G92" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>09:00</v>
       </c>
-    </row>
-    <row r="93" spans="1:7">
+      <c r="H92" t="str">
+        <f t="shared" si="3"/>
+        <v>09:00</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
       <c r="A93" s="1" t="s">
         <v>92</v>
       </c>
@@ -5162,11 +5301,15 @@
         <v>0.27</v>
       </c>
       <c r="G93" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>10:00</v>
       </c>
-    </row>
-    <row r="94" spans="1:7">
+      <c r="H93" t="str">
+        <f t="shared" si="3"/>
+        <v>10:00</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
       <c r="A94" s="1" t="s">
         <v>93</v>
       </c>
@@ -5177,11 +5320,15 @@
         <v>0.74</v>
       </c>
       <c r="G94" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>12:00</v>
       </c>
-    </row>
-    <row r="95" spans="1:7">
+      <c r="H94" t="str">
+        <f t="shared" si="3"/>
+        <v>12:00</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
       <c r="A95" s="1" t="s">
         <v>93</v>
       </c>
@@ -5195,11 +5342,15 @@
         <v>0.92</v>
       </c>
       <c r="G95" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>12:00</v>
       </c>
-    </row>
-    <row r="96" spans="1:7">
+      <c r="H95" t="str">
+        <f t="shared" si="3"/>
+        <v>12:00</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
       <c r="A96" s="1" t="s">
         <v>94</v>
       </c>
@@ -5210,11 +5361,15 @@
         <v>0.82</v>
       </c>
       <c r="G96" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>13:00</v>
       </c>
-    </row>
-    <row r="97" spans="1:7">
+      <c r="H96" t="str">
+        <f t="shared" si="3"/>
+        <v>13:00</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
       <c r="A97" s="1" t="s">
         <v>94</v>
       </c>
@@ -5228,11 +5383,15 @@
         <v>0.21</v>
       </c>
       <c r="G97" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>13:00</v>
       </c>
-    </row>
-    <row r="98" spans="1:7">
+      <c r="H97" t="str">
+        <f t="shared" si="3"/>
+        <v>13:00</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
       <c r="A98" s="1" t="s">
         <v>95</v>
       </c>
@@ -5243,11 +5402,15 @@
         <v>0.27</v>
       </c>
       <c r="G98" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>14:00</v>
       </c>
-    </row>
-    <row r="99" spans="1:7">
+      <c r="H98" t="str">
+        <f t="shared" si="3"/>
+        <v>14:00</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
       <c r="A99" s="1" t="s">
         <v>96</v>
       </c>
@@ -5261,26 +5424,34 @@
         <v>0.2</v>
       </c>
       <c r="G99" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>16:00</v>
       </c>
-    </row>
-    <row r="100" spans="1:7">
+      <c r="H99" t="str">
+        <f t="shared" si="3"/>
+        <v>16:00</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
       <c r="A100" s="1" t="s">
         <v>97</v>
       </c>
       <c r="D100" s="1">
-        <v>4.31</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="F100" s="1">
         <v>0.76</v>
       </c>
       <c r="G100" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>18:00</v>
       </c>
-    </row>
-    <row r="101" spans="1:7">
+      <c r="H100" t="str">
+        <f t="shared" si="3"/>
+        <v>18:00</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
       <c r="A101" s="1" t="s">
         <v>97</v>
       </c>
@@ -5294,11 +5465,15 @@
         <v>0.64</v>
       </c>
       <c r="G101" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>18:00</v>
       </c>
-    </row>
-    <row r="102" spans="1:7">
+      <c r="H101" t="str">
+        <f t="shared" si="3"/>
+        <v>18:00</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
       <c r="A102" s="1" t="s">
         <v>98</v>
       </c>
@@ -5309,11 +5484,15 @@
         <v>0.71</v>
       </c>
       <c r="G102" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>19:00</v>
       </c>
-    </row>
-    <row r="103" spans="1:7">
+      <c r="H102" t="str">
+        <f t="shared" si="3"/>
+        <v>19:00</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
       <c r="A103" s="1" t="s">
         <v>98</v>
       </c>
@@ -5327,11 +5506,15 @@
         <v>0.38</v>
       </c>
       <c r="G103" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>19:00</v>
       </c>
-    </row>
-    <row r="104" spans="1:7">
+      <c r="H103" t="str">
+        <f t="shared" si="3"/>
+        <v>19:00</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
       <c r="A104" s="1" t="s">
         <v>99</v>
       </c>
@@ -5342,11 +5525,15 @@
         <v>0.93</v>
       </c>
       <c r="G104" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>20:00</v>
       </c>
-    </row>
-    <row r="105" spans="1:7">
+      <c r="H104" t="str">
+        <f t="shared" si="3"/>
+        <v>20:00</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
       <c r="A105" s="1" t="s">
         <v>100</v>
       </c>
@@ -5357,11 +5544,15 @@
         <v>0.76</v>
       </c>
       <c r="G105" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>22:00</v>
       </c>
-    </row>
-    <row r="106" spans="1:7">
+      <c r="H105" t="str">
+        <f t="shared" si="3"/>
+        <v>22:00</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
       <c r="A106" s="1" t="s">
         <v>100</v>
       </c>
@@ -5375,11 +5566,15 @@
         <v>0.49</v>
       </c>
       <c r="G106" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>22:00</v>
       </c>
-    </row>
-    <row r="107" spans="1:7">
+      <c r="H106" t="str">
+        <f t="shared" si="3"/>
+        <v>22:00</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
       <c r="A107" s="1" t="s">
         <v>101</v>
       </c>
@@ -5393,11 +5588,15 @@
         <v>0.88</v>
       </c>
       <c r="G107" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>00:00</v>
       </c>
-    </row>
-    <row r="108" spans="1:7">
+      <c r="H107" t="str">
+        <f t="shared" si="3"/>
+        <v>00:00</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
       <c r="A108" s="1" t="s">
         <v>102</v>
       </c>
@@ -5411,11 +5610,15 @@
         <v>0.92</v>
       </c>
       <c r="G108" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>06:00</v>
       </c>
-    </row>
-    <row r="109" spans="1:7">
+      <c r="H108" t="str">
+        <f t="shared" si="3"/>
+        <v>06:00</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
       <c r="A109" s="1" t="s">
         <v>103</v>
       </c>
@@ -5423,14 +5626,18 @@
         <v>4.97</v>
       </c>
       <c r="F109" s="1">
-        <v>0.57</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="G109" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>07:00</v>
       </c>
-    </row>
-    <row r="110" spans="1:7">
+      <c r="H109" t="str">
+        <f t="shared" si="3"/>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
       <c r="A110" s="1" t="s">
         <v>103</v>
       </c>
@@ -5441,11 +5648,15 @@
         <v>0.63</v>
       </c>
       <c r="G110" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>07:00</v>
       </c>
-    </row>
-    <row r="111" spans="1:7">
+      <c r="H110" t="str">
+        <f t="shared" si="3"/>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
       <c r="A111" s="1" t="s">
         <v>104</v>
       </c>
@@ -5459,11 +5670,15 @@
         <v>0.36</v>
       </c>
       <c r="G111" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>07:30</v>
       </c>
-    </row>
-    <row r="112" spans="1:7">
+      <c r="H111" t="str">
+        <f t="shared" si="3"/>
+        <v>07:30</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
       <c r="A112" s="1" t="s">
         <v>105</v>
       </c>
@@ -5474,11 +5689,15 @@
         <v>0.59</v>
       </c>
       <c r="G112" t="str">
-        <f t="shared" ref="G112:G143" si="3">RIGHT(A112,5)</f>
+        <f t="shared" ref="G112:G143" si="5">RIGHT(A112,5)</f>
         <v>08:00</v>
       </c>
-    </row>
-    <row r="113" spans="1:7">
+      <c r="H112" t="str">
+        <f t="shared" si="3"/>
+        <v>08:00</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
       <c r="A113" s="1" t="s">
         <v>106</v>
       </c>
@@ -5489,11 +5708,15 @@
         <v>0.76</v>
       </c>
       <c r="G113" t="str">
+        <f t="shared" si="5"/>
+        <v>09:00</v>
+      </c>
+      <c r="H113" t="str">
         <f t="shared" si="3"/>
         <v>09:00</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:8">
       <c r="A114" s="1" t="s">
         <v>107</v>
       </c>
@@ -5507,26 +5730,34 @@
         <v>0.23</v>
       </c>
       <c r="G114" t="str">
+        <f t="shared" si="5"/>
+        <v>10:00</v>
+      </c>
+      <c r="H114" t="str">
         <f t="shared" si="3"/>
         <v>10:00</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:8">
       <c r="A115" s="1" t="s">
         <v>108</v>
       </c>
       <c r="D115" s="1">
-        <v>4.89</v>
+        <v>4.8899999999999997</v>
       </c>
       <c r="F115" s="1">
         <v>0.76</v>
       </c>
       <c r="G115" t="str">
+        <f t="shared" si="5"/>
+        <v>12:00</v>
+      </c>
+      <c r="H115" t="str">
         <f t="shared" si="3"/>
         <v>12:00</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:8">
       <c r="A116" s="1" t="s">
         <v>108</v>
       </c>
@@ -5537,14 +5768,18 @@
         <v>74</v>
       </c>
       <c r="F116" s="1">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="G116" t="str">
+        <f t="shared" si="5"/>
+        <v>12:00</v>
+      </c>
+      <c r="H116" t="str">
         <f t="shared" si="3"/>
         <v>12:00</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:8">
       <c r="A117" s="1" t="s">
         <v>109</v>
       </c>
@@ -5555,11 +5790,15 @@
         <v>0.48</v>
       </c>
       <c r="G117" t="str">
+        <f t="shared" si="5"/>
+        <v>13:00</v>
+      </c>
+      <c r="H117" t="str">
         <f t="shared" si="3"/>
         <v>13:00</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:8">
       <c r="A118" s="1" t="s">
         <v>109</v>
       </c>
@@ -5573,11 +5812,15 @@
         <v>0.8</v>
       </c>
       <c r="G118" t="str">
+        <f t="shared" si="5"/>
+        <v>13:00</v>
+      </c>
+      <c r="H118" t="str">
         <f t="shared" si="3"/>
         <v>13:00</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:8">
       <c r="A119" s="1" t="s">
         <v>110</v>
       </c>
@@ -5588,11 +5831,15 @@
         <v>0.63</v>
       </c>
       <c r="G119" t="str">
+        <f t="shared" si="5"/>
+        <v>14:00</v>
+      </c>
+      <c r="H119" t="str">
         <f t="shared" si="3"/>
         <v>14:00</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:8">
       <c r="A120" s="1" t="s">
         <v>111</v>
       </c>
@@ -5606,11 +5853,15 @@
         <v>0.98</v>
       </c>
       <c r="G120" t="str">
+        <f t="shared" si="5"/>
+        <v>16:00</v>
+      </c>
+      <c r="H120" t="str">
         <f t="shared" si="3"/>
         <v>16:00</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:8">
       <c r="A121" s="1" t="s">
         <v>112</v>
       </c>
@@ -5621,11 +5872,15 @@
         <v>0.3</v>
       </c>
       <c r="G121" t="str">
+        <f t="shared" si="5"/>
+        <v>18:00</v>
+      </c>
+      <c r="H121" t="str">
         <f t="shared" si="3"/>
         <v>18:00</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:8">
       <c r="A122" s="1" t="s">
         <v>112</v>
       </c>
@@ -5639,11 +5894,15 @@
         <v>0.35</v>
       </c>
       <c r="G122" t="str">
+        <f t="shared" si="5"/>
+        <v>18:00</v>
+      </c>
+      <c r="H122" t="str">
         <f t="shared" si="3"/>
         <v>18:00</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:8">
       <c r="A123" s="1" t="s">
         <v>113</v>
       </c>
@@ -5654,11 +5913,15 @@
         <v>0.27</v>
       </c>
       <c r="G123" t="str">
+        <f t="shared" si="5"/>
+        <v>19:00</v>
+      </c>
+      <c r="H123" t="str">
         <f t="shared" si="3"/>
         <v>19:00</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:8">
       <c r="A124" s="1" t="s">
         <v>113</v>
       </c>
@@ -5672,11 +5935,15 @@
         <v>0.94</v>
       </c>
       <c r="G124" t="str">
+        <f t="shared" si="5"/>
+        <v>19:00</v>
+      </c>
+      <c r="H124" t="str">
         <f t="shared" si="3"/>
         <v>19:00</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:8">
       <c r="A125" s="1" t="s">
         <v>114</v>
       </c>
@@ -5687,11 +5954,15 @@
         <v>0.8</v>
       </c>
       <c r="G125" t="str">
+        <f t="shared" si="5"/>
+        <v>20:00</v>
+      </c>
+      <c r="H125" t="str">
         <f t="shared" si="3"/>
         <v>20:00</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:8">
       <c r="A126" s="1" t="s">
         <v>115</v>
       </c>
@@ -5702,11 +5973,15 @@
         <v>0.39</v>
       </c>
       <c r="G126" t="str">
+        <f t="shared" si="5"/>
+        <v>22:00</v>
+      </c>
+      <c r="H126" t="str">
         <f t="shared" si="3"/>
         <v>22:00</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:8">
       <c r="A127" s="1" t="s">
         <v>115</v>
       </c>
@@ -5720,11 +5995,15 @@
         <v>0.37</v>
       </c>
       <c r="G127" t="str">
+        <f t="shared" si="5"/>
+        <v>22:00</v>
+      </c>
+      <c r="H127" t="str">
         <f t="shared" si="3"/>
         <v>22:00</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:8">
       <c r="A128" s="1" t="s">
         <v>116</v>
       </c>
@@ -5738,11 +6017,15 @@
         <v>0.63</v>
       </c>
       <c r="G128" t="str">
+        <f t="shared" si="5"/>
+        <v>00:00</v>
+      </c>
+      <c r="H128" t="str">
         <f t="shared" si="3"/>
         <v>00:00</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:8">
       <c r="A129" s="1" t="s">
         <v>117</v>
       </c>
@@ -5756,26 +6039,34 @@
         <v>0.69</v>
       </c>
       <c r="G129" t="str">
+        <f t="shared" si="5"/>
+        <v>06:00</v>
+      </c>
+      <c r="H129" t="str">
         <f t="shared" si="3"/>
         <v>06:00</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:8">
       <c r="A130" s="1" t="s">
         <v>118</v>
       </c>
       <c r="D130" s="1">
-        <v>4.39</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="F130" s="1">
         <v>0.78</v>
       </c>
       <c r="G130" t="str">
+        <f t="shared" si="5"/>
+        <v>07:00</v>
+      </c>
+      <c r="H130" t="str">
         <f t="shared" si="3"/>
         <v>07:00</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:8">
       <c r="A131" s="1" t="s">
         <v>118</v>
       </c>
@@ -5786,11 +6077,15 @@
         <v>0.68</v>
       </c>
       <c r="G131" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>07:00</v>
       </c>
-    </row>
-    <row r="132" spans="1:7">
+      <c r="H131" t="str">
+        <f t="shared" ref="H131:H169" si="6">TEXT(A131,"HH:MM")</f>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
       <c r="A132" s="1" t="s">
         <v>119</v>
       </c>
@@ -5804,11 +6099,15 @@
         <v>0.2</v>
       </c>
       <c r="G132" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>07:30</v>
       </c>
-    </row>
-    <row r="133" spans="1:7">
+      <c r="H132" t="str">
+        <f t="shared" si="6"/>
+        <v>07:30</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
       <c r="A133" s="1" t="s">
         <v>120</v>
       </c>
@@ -5819,11 +6118,15 @@
         <v>0.32</v>
       </c>
       <c r="G133" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>08:00</v>
       </c>
-    </row>
-    <row r="134" spans="1:7">
+      <c r="H133" t="str">
+        <f t="shared" si="6"/>
+        <v>08:00</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
       <c r="A134" s="1" t="s">
         <v>121</v>
       </c>
@@ -5834,11 +6137,15 @@
         <v>0.63</v>
       </c>
       <c r="G134" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>09:00</v>
       </c>
-    </row>
-    <row r="135" spans="1:7">
+      <c r="H134" t="str">
+        <f t="shared" si="6"/>
+        <v>09:00</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
       <c r="A135" s="1" t="s">
         <v>122</v>
       </c>
@@ -5852,26 +6159,34 @@
         <v>0.26</v>
       </c>
       <c r="G135" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>10:00</v>
       </c>
-    </row>
-    <row r="136" spans="1:7">
+      <c r="H135" t="str">
+        <f t="shared" si="6"/>
+        <v>10:00</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
       <c r="A136" s="1" t="s">
         <v>123</v>
       </c>
       <c r="D136" s="1">
-        <v>4.36</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="F136" s="1">
         <v>0.65</v>
       </c>
       <c r="G136" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>12:00</v>
       </c>
-    </row>
-    <row r="137" spans="1:7">
+      <c r="H136" t="str">
+        <f t="shared" si="6"/>
+        <v>12:00</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
       <c r="A137" s="1" t="s">
         <v>123</v>
       </c>
@@ -5885,11 +6200,15 @@
         <v>0.91</v>
       </c>
       <c r="G137" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>12:00</v>
       </c>
-    </row>
-    <row r="138" spans="1:7">
+      <c r="H137" t="str">
+        <f t="shared" si="6"/>
+        <v>12:00</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
       <c r="A138" s="1" t="s">
         <v>124</v>
       </c>
@@ -5897,14 +6216,18 @@
         <v>6.51</v>
       </c>
       <c r="F138" s="1">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="G138" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>13:00</v>
       </c>
-    </row>
-    <row r="139" spans="1:7">
+      <c r="H138" t="str">
+        <f t="shared" si="6"/>
+        <v>13:00</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
       <c r="A139" s="1" t="s">
         <v>124</v>
       </c>
@@ -5918,11 +6241,15 @@
         <v>0.99</v>
       </c>
       <c r="G139" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>13:00</v>
       </c>
-    </row>
-    <row r="140" spans="1:7">
+      <c r="H139" t="str">
+        <f t="shared" si="6"/>
+        <v>13:00</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
       <c r="A140" s="1" t="s">
         <v>125</v>
       </c>
@@ -5930,14 +6257,18 @@
         <v>6.09</v>
       </c>
       <c r="F140" s="1">
-        <v>0.58</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="G140" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>14:00</v>
       </c>
-    </row>
-    <row r="141" spans="1:7">
+      <c r="H140" t="str">
+        <f t="shared" si="6"/>
+        <v>14:00</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
       <c r="A141" s="1" t="s">
         <v>126</v>
       </c>
@@ -5951,26 +6282,34 @@
         <v>0.89</v>
       </c>
       <c r="G141" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>16:00</v>
       </c>
-    </row>
-    <row r="142" spans="1:7">
+      <c r="H141" t="str">
+        <f t="shared" si="6"/>
+        <v>16:00</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
       <c r="A142" s="1" t="s">
         <v>127</v>
       </c>
       <c r="D142" s="1">
-        <v>4.14</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="F142" s="1">
         <v>0.65</v>
       </c>
       <c r="G142" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>18:00</v>
       </c>
-    </row>
-    <row r="143" spans="1:7">
+      <c r="H142" t="str">
+        <f t="shared" si="6"/>
+        <v>18:00</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
       <c r="A143" s="1" t="s">
         <v>127</v>
       </c>
@@ -5984,11 +6323,15 @@
         <v>0.82</v>
       </c>
       <c r="G143" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>18:00</v>
       </c>
-    </row>
-    <row r="144" spans="1:7">
+      <c r="H143" t="str">
+        <f t="shared" si="6"/>
+        <v>18:00</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
       <c r="A144" s="1" t="s">
         <v>128</v>
       </c>
@@ -5999,11 +6342,15 @@
         <v>0.47</v>
       </c>
       <c r="G144" t="str">
-        <f>RIGHT(A144,5)</f>
+        <f t="shared" ref="G144:G153" si="7">RIGHT(A144,5)</f>
         <v>19:00</v>
       </c>
-    </row>
-    <row r="145" spans="1:7">
+      <c r="H144" t="str">
+        <f t="shared" si="6"/>
+        <v>19:00</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
       <c r="A145" s="1" t="s">
         <v>128</v>
       </c>
@@ -6017,11 +6364,15 @@
         <v>0.7</v>
       </c>
       <c r="G145" t="str">
-        <f>RIGHT(A145,5)</f>
+        <f t="shared" si="7"/>
         <v>19:00</v>
       </c>
-    </row>
-    <row r="146" spans="1:7">
+      <c r="H145" t="str">
+        <f t="shared" si="6"/>
+        <v>19:00</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
       <c r="A146" s="1" t="s">
         <v>129</v>
       </c>
@@ -6032,11 +6383,15 @@
         <v>0.4</v>
       </c>
       <c r="G146" t="str">
-        <f>RIGHT(A146,5)</f>
+        <f t="shared" si="7"/>
         <v>20:00</v>
       </c>
-    </row>
-    <row r="147" spans="1:7">
+      <c r="H146" t="str">
+        <f t="shared" si="6"/>
+        <v>20:00</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
       <c r="A147" s="1" t="s">
         <v>130</v>
       </c>
@@ -6047,11 +6402,15 @@
         <v>0.49</v>
       </c>
       <c r="G147" t="str">
-        <f>RIGHT(A147,5)</f>
+        <f t="shared" si="7"/>
         <v>22:00</v>
       </c>
-    </row>
-    <row r="148" spans="1:7">
+      <c r="H147" t="str">
+        <f t="shared" si="6"/>
+        <v>22:00</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
       <c r="A148" s="1" t="s">
         <v>130</v>
       </c>
@@ -6065,11 +6424,15 @@
         <v>0.24</v>
       </c>
       <c r="G148" t="str">
-        <f>RIGHT(A148,5)</f>
+        <f t="shared" si="7"/>
         <v>22:00</v>
       </c>
-    </row>
-    <row r="149" spans="1:7">
+      <c r="H148" t="str">
+        <f t="shared" si="6"/>
+        <v>22:00</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
       <c r="A149" s="1" t="s">
         <v>131</v>
       </c>
@@ -6083,11 +6446,15 @@
         <v>0.69</v>
       </c>
       <c r="G149" t="str">
-        <f>RIGHT(A149,5)</f>
+        <f t="shared" si="7"/>
         <v>00:00</v>
       </c>
-    </row>
-    <row r="150" spans="1:7">
+      <c r="H149" t="str">
+        <f t="shared" si="6"/>
+        <v>00:00</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
       <c r="A150" s="1" t="s">
         <v>132</v>
       </c>
@@ -6101,26 +6468,34 @@
         <v>0.46</v>
       </c>
       <c r="G150" t="str">
-        <f>RIGHT(A150,5)</f>
+        <f t="shared" si="7"/>
         <v>06:00</v>
       </c>
-    </row>
-    <row r="151" spans="1:7">
+      <c r="H150" t="str">
+        <f t="shared" si="6"/>
+        <v>06:00</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
       <c r="A151" s="1" t="s">
         <v>133</v>
       </c>
       <c r="D151" s="1">
-        <v>4.77</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="F151" s="1">
         <v>0.88</v>
       </c>
       <c r="G151" t="str">
-        <f>RIGHT(A151,5)</f>
+        <f t="shared" si="7"/>
         <v>07:00</v>
       </c>
-    </row>
-    <row r="152" spans="1:7">
+      <c r="H151" t="str">
+        <f t="shared" si="6"/>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
       <c r="A152" s="1" t="s">
         <v>133</v>
       </c>
@@ -6131,11 +6506,15 @@
         <v>0.66</v>
       </c>
       <c r="G152" t="str">
-        <f>RIGHT(A152,5)</f>
+        <f t="shared" si="7"/>
         <v>07:00</v>
       </c>
-    </row>
-    <row r="153" spans="1:7">
+      <c r="H152" t="str">
+        <f t="shared" si="6"/>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
       <c r="A153" s="1" t="s">
         <v>134</v>
       </c>
@@ -6149,11 +6528,15 @@
         <v>0.4</v>
       </c>
       <c r="G153" t="str">
-        <f>RIGHT(A153,5)</f>
+        <f t="shared" si="7"/>
         <v>07:30</v>
       </c>
-    </row>
-    <row r="154" spans="1:7">
+      <c r="H153" t="str">
+        <f t="shared" si="6"/>
+        <v>07:30</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
       <c r="A154" s="1" t="s">
         <v>135</v>
       </c>
@@ -6164,11 +6547,15 @@
         <v>0.84</v>
       </c>
       <c r="G154" t="str">
-        <f t="shared" ref="G154:G169" si="4">RIGHT(A154,5)</f>
+        <f t="shared" ref="G154:G169" si="8">RIGHT(A154,5)</f>
         <v>08:00</v>
       </c>
-    </row>
-    <row r="155" spans="1:7">
+      <c r="H154" t="str">
+        <f t="shared" si="6"/>
+        <v>08:00</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
       <c r="A155" s="1" t="s">
         <v>136</v>
       </c>
@@ -6179,11 +6566,15 @@
         <v>0.24</v>
       </c>
       <c r="G155" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>09:00</v>
       </c>
-    </row>
-    <row r="156" spans="1:7">
+      <c r="H155" t="str">
+        <f t="shared" si="6"/>
+        <v>09:00</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
       <c r="A156" s="1" t="s">
         <v>137</v>
       </c>
@@ -6197,11 +6588,15 @@
         <v>0.54</v>
       </c>
       <c r="G156" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>10:00</v>
       </c>
-    </row>
-    <row r="157" spans="1:7">
+      <c r="H156" t="str">
+        <f t="shared" si="6"/>
+        <v>10:00</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
       <c r="A157" s="1" t="s">
         <v>138</v>
       </c>
@@ -6212,11 +6607,15 @@
         <v>0.52</v>
       </c>
       <c r="G157" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>12:00</v>
       </c>
-    </row>
-    <row r="158" spans="1:7">
+      <c r="H157" t="str">
+        <f t="shared" si="6"/>
+        <v>12:00</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
       <c r="A158" s="1" t="s">
         <v>138</v>
       </c>
@@ -6230,11 +6629,15 @@
         <v>0.93</v>
       </c>
       <c r="G158" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>12:00</v>
       </c>
-    </row>
-    <row r="159" spans="1:7">
+      <c r="H158" t="str">
+        <f t="shared" si="6"/>
+        <v>12:00</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
       <c r="A159" s="1" t="s">
         <v>139</v>
       </c>
@@ -6245,11 +6648,15 @@
         <v>0.85</v>
       </c>
       <c r="G159" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>13:00</v>
       </c>
-    </row>
-    <row r="160" spans="1:7">
+      <c r="H159" t="str">
+        <f t="shared" si="6"/>
+        <v>13:00</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
       <c r="A160" s="1" t="s">
         <v>139</v>
       </c>
@@ -6263,11 +6670,15 @@
         <v>0.71</v>
       </c>
       <c r="G160" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>13:00</v>
       </c>
-    </row>
-    <row r="161" spans="1:7">
+      <c r="H160" t="str">
+        <f t="shared" si="6"/>
+        <v>13:00</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8">
       <c r="A161" s="1" t="s">
         <v>140</v>
       </c>
@@ -6278,11 +6689,15 @@
         <v>0.65</v>
       </c>
       <c r="G161" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>14:00</v>
       </c>
-    </row>
-    <row r="162" spans="1:7">
+      <c r="H161" t="str">
+        <f t="shared" si="6"/>
+        <v>14:00</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8">
       <c r="A162" s="1" t="s">
         <v>141</v>
       </c>
@@ -6293,29 +6708,37 @@
         <v>62</v>
       </c>
       <c r="F162" s="1">
-        <v>0.29</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="G162" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>16:00</v>
       </c>
-    </row>
-    <row r="163" spans="1:7">
+      <c r="H162" t="str">
+        <f t="shared" si="6"/>
+        <v>16:00</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8">
       <c r="A163" s="1" t="s">
         <v>142</v>
       </c>
       <c r="D163" s="1">
-        <v>4.77</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="F163" s="1">
         <v>0.42</v>
       </c>
       <c r="G163" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>18:00</v>
       </c>
-    </row>
-    <row r="164" spans="1:7">
+      <c r="H163" t="str">
+        <f t="shared" si="6"/>
+        <v>18:00</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8">
       <c r="A164" s="1" t="s">
         <v>142</v>
       </c>
@@ -6329,11 +6752,15 @@
         <v>0.34</v>
       </c>
       <c r="G164" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>18:00</v>
       </c>
-    </row>
-    <row r="165" spans="1:7">
+      <c r="H164" t="str">
+        <f t="shared" si="6"/>
+        <v>18:00</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8">
       <c r="A165" s="1" t="s">
         <v>143</v>
       </c>
@@ -6344,11 +6771,15 @@
         <v>0.54</v>
       </c>
       <c r="G165" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>19:00</v>
       </c>
-    </row>
-    <row r="166" spans="1:7">
+      <c r="H165" t="str">
+        <f t="shared" si="6"/>
+        <v>19:00</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8">
       <c r="A166" s="1" t="s">
         <v>143</v>
       </c>
@@ -6362,11 +6793,15 @@
         <v>0.69</v>
       </c>
       <c r="G166" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>19:00</v>
       </c>
-    </row>
-    <row r="167" spans="1:7">
+      <c r="H166" t="str">
+        <f t="shared" si="6"/>
+        <v>19:00</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8">
       <c r="A167" s="1" t="s">
         <v>144</v>
       </c>
@@ -6377,11 +6812,15 @@
         <v>0.27</v>
       </c>
       <c r="G167" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>20:00</v>
       </c>
-    </row>
-    <row r="168" spans="1:7">
+      <c r="H167" t="str">
+        <f t="shared" si="6"/>
+        <v>20:00</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8">
       <c r="A168" s="1" t="s">
         <v>145</v>
       </c>
@@ -6392,11 +6831,15 @@
         <v>0.46</v>
       </c>
       <c r="G168" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>22:00</v>
       </c>
-    </row>
-    <row r="169" spans="1:7">
+      <c r="H168" t="str">
+        <f t="shared" si="6"/>
+        <v>22:00</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
       <c r="A169" s="1" t="s">
         <v>145</v>
       </c>
@@ -6410,19 +6853,21 @@
         <v>0.6</v>
       </c>
       <c r="G169" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>22:00</v>
       </c>
+      <c r="H169" t="str">
+        <f t="shared" si="6"/>
+        <v>22:00</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O169" etc:filterBottomFollowUsedRange="0">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:O169"/>
   <sortState ref="A2:E161">
     <sortCondition ref="A2:A161"/>
   </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/3.1.4答案/智能健康监测系统数据集.xlsx
+++ b/3.1.4答案/智能健康监测系统数据集.xlsx
@@ -9,18 +9,18 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25605" windowHeight="10395"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25605" windowHeight="10395" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$F$169</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="152">
   <si>
     <t>时间戳</t>
   </si>
@@ -56,456 +56,453 @@
     <t>体脂分析</t>
   </si>
   <si>
+    <t>hour</t>
+  </si>
+  <si>
+    <t>2024-09-15 00:00</t>
+  </si>
+  <si>
+    <t>2024-09-15 06:00</t>
+  </si>
+  <si>
+    <t>2024-09-15 07:00</t>
+  </si>
+  <si>
+    <t>2024-09-15 07:30</t>
+  </si>
+  <si>
+    <t>2024-09-15 08:00</t>
+  </si>
+  <si>
+    <t>2024-09-15 09:00</t>
+  </si>
+  <si>
+    <t>2024-09-15 10:00</t>
+  </si>
+  <si>
+    <t>Average of 血糖</t>
+  </si>
+  <si>
+    <t>Average of 体脂分析</t>
+  </si>
+  <si>
+    <t>Average of 舒张压</t>
+  </si>
+  <si>
+    <t>2024-09-15 12:00</t>
+  </si>
+  <si>
+    <t>00:00</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>2024-09-15 13:00</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>2024-09-15 14:00</t>
+  </si>
+  <si>
+    <t>08:00</t>
+  </si>
+  <si>
+    <t>2024-09-15 16:00</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>2024-09-15 18:00</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>2024-09-15 19:00</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>2024-09-15 20:00</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>2024-09-15 22:00</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>2024-09-16 00:00</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>2024-09-16 06:00</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>2024-09-16 07:00</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>2024-09-16 07:30</t>
+  </si>
+  <si>
+    <t>2024-09-16 08:00</t>
+  </si>
+  <si>
+    <t>2024-09-16 09:00</t>
+  </si>
+  <si>
+    <t>2024-09-16 10:00</t>
+  </si>
+  <si>
+    <t>2024-09-16 12:00</t>
+  </si>
+  <si>
+    <t>2024-09-16 13:00</t>
+  </si>
+  <si>
+    <t>2024-09-16 14:00</t>
+  </si>
+  <si>
+    <t>2024-09-16 16:00</t>
+  </si>
+  <si>
+    <t>2024-09-16 18:00</t>
+  </si>
+  <si>
+    <t>2024-09-16 19:00</t>
+  </si>
+  <si>
+    <t>2024-09-16 20:00</t>
+  </si>
+  <si>
+    <t>2024-09-16 22:00</t>
+  </si>
+  <si>
+    <t>2024-09-17 00:00</t>
+  </si>
+  <si>
+    <t>2024-09-17 06:00</t>
+  </si>
+  <si>
+    <t>2024-09-17 07:00</t>
+  </si>
+  <si>
+    <t>2024-09-17 07:30</t>
+  </si>
+  <si>
+    <t>2024-09-17 08:00</t>
+  </si>
+  <si>
+    <t>2024-09-17 09:00</t>
+  </si>
+  <si>
+    <t>2024-09-17 10:00</t>
+  </si>
+  <si>
+    <t>2024-09-17 12:00</t>
+  </si>
+  <si>
+    <t>2024-09-17 13:00</t>
+  </si>
+  <si>
+    <t>2024-09-17 14:00</t>
+  </si>
+  <si>
+    <t>2024-09-17 16:00</t>
+  </si>
+  <si>
+    <t>2024-09-17 18:00</t>
+  </si>
+  <si>
+    <t>2024-09-17 19:00</t>
+  </si>
+  <si>
+    <t>2024-09-17 20:00</t>
+  </si>
+  <si>
+    <t>2024-09-17 22:00</t>
+  </si>
+  <si>
+    <t>2024-09-18 00:00</t>
+  </si>
+  <si>
+    <t>2024-09-18 06:00</t>
+  </si>
+  <si>
+    <t>2024-09-18 07:00</t>
+  </si>
+  <si>
+    <t>2024-09-18 07:30</t>
+  </si>
+  <si>
+    <t>2024-09-18 08:00</t>
+  </si>
+  <si>
+    <t>2024-09-18 09:00</t>
+  </si>
+  <si>
+    <t>2024-09-18 10:00</t>
+  </si>
+  <si>
+    <t>2024-09-18 12:00</t>
+  </si>
+  <si>
+    <t>2024-09-18 13:00</t>
+  </si>
+  <si>
+    <t>2024-09-18 14:00</t>
+  </si>
+  <si>
+    <t>2024-09-18 16:00</t>
+  </si>
+  <si>
+    <t>2024-09-18 18:00</t>
+  </si>
+  <si>
+    <t>2024-09-18 19:00</t>
+  </si>
+  <si>
+    <t>2024-09-18 20:00</t>
+  </si>
+  <si>
+    <t>2024-09-18 22:00</t>
+  </si>
+  <si>
+    <t>2024-09-19 00:00</t>
+  </si>
+  <si>
+    <t>2024-09-19 06:00</t>
+  </si>
+  <si>
+    <t>2024-09-19 07:00</t>
+  </si>
+  <si>
+    <t>2024-09-19 07:30</t>
+  </si>
+  <si>
+    <t>2024-09-19 08:00</t>
+  </si>
+  <si>
+    <t>2024-09-19 09:00</t>
+  </si>
+  <si>
+    <t>2024-09-19 10:00</t>
+  </si>
+  <si>
+    <t>2024-09-19 12:00</t>
+  </si>
+  <si>
+    <t>2024-09-19 13:00</t>
+  </si>
+  <si>
+    <t>2024-09-19 14:00</t>
+  </si>
+  <si>
+    <t>2024-09-19 16:00</t>
+  </si>
+  <si>
+    <t>2024-09-19 18:00</t>
+  </si>
+  <si>
+    <t>2024-09-19 19:00</t>
+  </si>
+  <si>
+    <t>2024-09-19 20:00</t>
+  </si>
+  <si>
+    <t>2024-09-19 22:00</t>
+  </si>
+  <si>
+    <t>2024-09-20 00:00</t>
+  </si>
+  <si>
+    <t>2024-09-20 06:00</t>
+  </si>
+  <si>
+    <t>2024-09-20 07:00</t>
+  </si>
+  <si>
+    <t>2024-09-20 07:30</t>
+  </si>
+  <si>
+    <t>2024-09-20 08:00</t>
+  </si>
+  <si>
+    <t>2024-09-20 09:00</t>
+  </si>
+  <si>
+    <t>2024-09-20 10:00</t>
+  </si>
+  <si>
+    <t>2024-09-20 12:00</t>
+  </si>
+  <si>
+    <t>2024-09-20 13:00</t>
+  </si>
+  <si>
+    <t>2024-09-20 14:00</t>
+  </si>
+  <si>
+    <t>2024-09-20 16:00</t>
+  </si>
+  <si>
+    <t>2024-09-20 18:00</t>
+  </si>
+  <si>
+    <t>2024-09-20 19:00</t>
+  </si>
+  <si>
+    <t>2024-09-20 20:00</t>
+  </si>
+  <si>
+    <t>2024-09-20 22:00</t>
+  </si>
+  <si>
+    <t>2024-09-21 00:00</t>
+  </si>
+  <si>
+    <t>2024-09-21 06:00</t>
+  </si>
+  <si>
+    <t>2024-09-21 07:00</t>
+  </si>
+  <si>
+    <t>2024-09-21 07:30</t>
+  </si>
+  <si>
+    <t>2024-09-21 08:00</t>
+  </si>
+  <si>
+    <t>2024-09-21 09:00</t>
+  </si>
+  <si>
+    <t>2024-09-21 10:00</t>
+  </si>
+  <si>
+    <t>2024-09-21 12:00</t>
+  </si>
+  <si>
+    <t>2024-09-21 13:00</t>
+  </si>
+  <si>
+    <t>2024-09-21 14:00</t>
+  </si>
+  <si>
+    <t>2024-09-21 16:00</t>
+  </si>
+  <si>
+    <t>2024-09-21 18:00</t>
+  </si>
+  <si>
+    <t>2024-09-21 19:00</t>
+  </si>
+  <si>
+    <t>2024-09-21 20:00</t>
+  </si>
+  <si>
+    <t>2024-09-21 22:00</t>
+  </si>
+  <si>
+    <t>2024-09-22 00:00</t>
+  </si>
+  <si>
+    <t>2024-09-22 06:00</t>
+  </si>
+  <si>
+    <t>2024-09-22 07:00</t>
+  </si>
+  <si>
+    <t>2024-09-22 07:30</t>
+  </si>
+  <si>
+    <t>2024-09-22 08:00</t>
+  </si>
+  <si>
+    <t>2024-09-22 09:00</t>
+  </si>
+  <si>
+    <t>2024-09-22 10:00</t>
+  </si>
+  <si>
+    <t>2024-09-22 12:00</t>
+  </si>
+  <si>
+    <t>2024-09-22 13:00</t>
+  </si>
+  <si>
+    <t>2024-09-22 14:00</t>
+  </si>
+  <si>
+    <t>2024-09-22 16:00</t>
+  </si>
+  <si>
+    <t>2024-09-22 18:00</t>
+  </si>
+  <si>
+    <t>2024-09-22 19:00</t>
+  </si>
+  <si>
+    <t>2024-09-22 20:00</t>
+  </si>
+  <si>
+    <t>2024-09-22 22:00</t>
+  </si>
+  <si>
+    <t>行标签</t>
+  </si>
+  <si>
+    <t>总计</t>
+  </si>
+  <si>
+    <t>平均值项:血糖</t>
+  </si>
+  <si>
+    <t>平均值项:体脂分析</t>
+  </si>
+  <si>
+    <t>平均值项:舒张压</t>
+  </si>
+  <si>
+    <t>平均值项:收缩压</t>
+  </si>
+  <si>
     <t>响应时间</t>
-  </si>
-  <si>
-    <t>hour</t>
-  </si>
-  <si>
-    <t>2024-09-15 00:00</t>
-  </si>
-  <si>
-    <t>2024-09-15 06:00</t>
-  </si>
-  <si>
-    <t>2024-09-15 07:00</t>
-  </si>
-  <si>
-    <t>2024-09-15 07:30</t>
-  </si>
-  <si>
-    <t>2024-09-15 08:00</t>
-  </si>
-  <si>
-    <t>2024-09-15 09:00</t>
-  </si>
-  <si>
-    <t>2024-09-15 10:00</t>
-  </si>
-  <si>
-    <t>Average of 血糖</t>
-  </si>
-  <si>
-    <t>Average of 体脂分析</t>
-  </si>
-  <si>
-    <t>Average of 舒张压</t>
-  </si>
-  <si>
-    <t>2024-09-15 12:00</t>
-  </si>
-  <si>
-    <t>00:00</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>2024-09-15 13:00</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>2024-09-15 14:00</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>2024-09-15 16:00</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>2024-09-15 18:00</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>2024-09-15 19:00</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>2024-09-15 20:00</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>2024-09-15 22:00</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>2024-09-16 00:00</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>2024-09-16 06:00</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>2024-09-16 07:00</t>
-  </si>
-  <si>
-    <t>Grand Total</t>
-  </si>
-  <si>
-    <t>2024-09-16 07:30</t>
-  </si>
-  <si>
-    <t>2024-09-16 08:00</t>
-  </si>
-  <si>
-    <t>2024-09-16 09:00</t>
-  </si>
-  <si>
-    <t>2024-09-16 10:00</t>
-  </si>
-  <si>
-    <t>2024-09-16 12:00</t>
-  </si>
-  <si>
-    <t>2024-09-16 13:00</t>
-  </si>
-  <si>
-    <t>2024-09-16 14:00</t>
-  </si>
-  <si>
-    <t>2024-09-16 16:00</t>
-  </si>
-  <si>
-    <t>2024-09-16 18:00</t>
-  </si>
-  <si>
-    <t>2024-09-16 19:00</t>
-  </si>
-  <si>
-    <t>2024-09-16 20:00</t>
-  </si>
-  <si>
-    <t>2024-09-16 22:00</t>
-  </si>
-  <si>
-    <t>2024-09-17 00:00</t>
-  </si>
-  <si>
-    <t>2024-09-17 06:00</t>
-  </si>
-  <si>
-    <t>2024-09-17 07:00</t>
-  </si>
-  <si>
-    <t>2024-09-17 07:30</t>
-  </si>
-  <si>
-    <t>2024-09-17 08:00</t>
-  </si>
-  <si>
-    <t>2024-09-17 09:00</t>
-  </si>
-  <si>
-    <t>2024-09-17 10:00</t>
-  </si>
-  <si>
-    <t>2024-09-17 12:00</t>
-  </si>
-  <si>
-    <t>2024-09-17 13:00</t>
-  </si>
-  <si>
-    <t>2024-09-17 14:00</t>
-  </si>
-  <si>
-    <t>2024-09-17 16:00</t>
-  </si>
-  <si>
-    <t>2024-09-17 18:00</t>
-  </si>
-  <si>
-    <t>2024-09-17 19:00</t>
-  </si>
-  <si>
-    <t>2024-09-17 20:00</t>
-  </si>
-  <si>
-    <t>2024-09-17 22:00</t>
-  </si>
-  <si>
-    <t>2024-09-18 00:00</t>
-  </si>
-  <si>
-    <t>2024-09-18 06:00</t>
-  </si>
-  <si>
-    <t>2024-09-18 07:00</t>
-  </si>
-  <si>
-    <t>2024-09-18 07:30</t>
-  </si>
-  <si>
-    <t>2024-09-18 08:00</t>
-  </si>
-  <si>
-    <t>2024-09-18 09:00</t>
-  </si>
-  <si>
-    <t>2024-09-18 10:00</t>
-  </si>
-  <si>
-    <t>2024-09-18 12:00</t>
-  </si>
-  <si>
-    <t>2024-09-18 13:00</t>
-  </si>
-  <si>
-    <t>2024-09-18 14:00</t>
-  </si>
-  <si>
-    <t>2024-09-18 16:00</t>
-  </si>
-  <si>
-    <t>2024-09-18 18:00</t>
-  </si>
-  <si>
-    <t>2024-09-18 19:00</t>
-  </si>
-  <si>
-    <t>2024-09-18 20:00</t>
-  </si>
-  <si>
-    <t>2024-09-18 22:00</t>
-  </si>
-  <si>
-    <t>2024-09-19 00:00</t>
-  </si>
-  <si>
-    <t>2024-09-19 06:00</t>
-  </si>
-  <si>
-    <t>2024-09-19 07:00</t>
-  </si>
-  <si>
-    <t>2024-09-19 07:30</t>
-  </si>
-  <si>
-    <t>2024-09-19 08:00</t>
-  </si>
-  <si>
-    <t>2024-09-19 09:00</t>
-  </si>
-  <si>
-    <t>2024-09-19 10:00</t>
-  </si>
-  <si>
-    <t>2024-09-19 12:00</t>
-  </si>
-  <si>
-    <t>2024-09-19 13:00</t>
-  </si>
-  <si>
-    <t>2024-09-19 14:00</t>
-  </si>
-  <si>
-    <t>2024-09-19 16:00</t>
-  </si>
-  <si>
-    <t>2024-09-19 18:00</t>
-  </si>
-  <si>
-    <t>2024-09-19 19:00</t>
-  </si>
-  <si>
-    <t>2024-09-19 20:00</t>
-  </si>
-  <si>
-    <t>2024-09-19 22:00</t>
-  </si>
-  <si>
-    <t>2024-09-20 00:00</t>
-  </si>
-  <si>
-    <t>2024-09-20 06:00</t>
-  </si>
-  <si>
-    <t>2024-09-20 07:00</t>
-  </si>
-  <si>
-    <t>2024-09-20 07:30</t>
-  </si>
-  <si>
-    <t>2024-09-20 08:00</t>
-  </si>
-  <si>
-    <t>2024-09-20 09:00</t>
-  </si>
-  <si>
-    <t>2024-09-20 10:00</t>
-  </si>
-  <si>
-    <t>2024-09-20 12:00</t>
-  </si>
-  <si>
-    <t>2024-09-20 13:00</t>
-  </si>
-  <si>
-    <t>2024-09-20 14:00</t>
-  </si>
-  <si>
-    <t>2024-09-20 16:00</t>
-  </si>
-  <si>
-    <t>2024-09-20 18:00</t>
-  </si>
-  <si>
-    <t>2024-09-20 19:00</t>
-  </si>
-  <si>
-    <t>2024-09-20 20:00</t>
-  </si>
-  <si>
-    <t>2024-09-20 22:00</t>
-  </si>
-  <si>
-    <t>2024-09-21 00:00</t>
-  </si>
-  <si>
-    <t>2024-09-21 06:00</t>
-  </si>
-  <si>
-    <t>2024-09-21 07:00</t>
-  </si>
-  <si>
-    <t>2024-09-21 07:30</t>
-  </si>
-  <si>
-    <t>2024-09-21 08:00</t>
-  </si>
-  <si>
-    <t>2024-09-21 09:00</t>
-  </si>
-  <si>
-    <t>2024-09-21 10:00</t>
-  </si>
-  <si>
-    <t>2024-09-21 12:00</t>
-  </si>
-  <si>
-    <t>2024-09-21 13:00</t>
-  </si>
-  <si>
-    <t>2024-09-21 14:00</t>
-  </si>
-  <si>
-    <t>2024-09-21 16:00</t>
-  </si>
-  <si>
-    <t>2024-09-21 18:00</t>
-  </si>
-  <si>
-    <t>2024-09-21 19:00</t>
-  </si>
-  <si>
-    <t>2024-09-21 20:00</t>
-  </si>
-  <si>
-    <t>2024-09-21 22:00</t>
-  </si>
-  <si>
-    <t>2024-09-22 00:00</t>
-  </si>
-  <si>
-    <t>2024-09-22 06:00</t>
-  </si>
-  <si>
-    <t>2024-09-22 07:00</t>
-  </si>
-  <si>
-    <t>2024-09-22 07:30</t>
-  </si>
-  <si>
-    <t>2024-09-22 08:00</t>
-  </si>
-  <si>
-    <t>2024-09-22 09:00</t>
-  </si>
-  <si>
-    <t>2024-09-22 10:00</t>
-  </si>
-  <si>
-    <t>2024-09-22 12:00</t>
-  </si>
-  <si>
-    <t>2024-09-22 13:00</t>
-  </si>
-  <si>
-    <t>2024-09-22 14:00</t>
-  </si>
-  <si>
-    <t>2024-09-22 16:00</t>
-  </si>
-  <si>
-    <t>2024-09-22 18:00</t>
-  </si>
-  <si>
-    <t>2024-09-22 19:00</t>
-  </si>
-  <si>
-    <t>2024-09-22 20:00</t>
-  </si>
-  <si>
-    <t>2024-09-22 22:00</t>
-  </si>
-  <si>
-    <t>hour</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>行标签</t>
-  </si>
-  <si>
-    <t>总计</t>
-  </si>
-  <si>
-    <t>平均值项:血糖</t>
-  </si>
-  <si>
-    <t>平均值项:体脂分析</t>
-  </si>
-  <si>
-    <t>平均值项:舒张压</t>
-  </si>
-  <si>
-    <t>平均值项:收缩压</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -532,6 +529,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -553,7 +557,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -567,6 +571,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2501,7 +2508,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="数据透视表1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="数据透视表1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="5" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:E19" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField showAll="0"/>
@@ -2617,8 +2624,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" createdVersion="5" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0">
-  <location ref="L9:O25" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" createdVersion="5" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0">
+  <location ref="K9:N25" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField compact="0" showAll="0"/>
     <pivotField compact="0" showAll="0"/>
@@ -3025,24 +3032,24 @@
   <sheetData>
     <row r="3" spans="1:5">
       <c r="A3" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B3" t="s">
         <v>147</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" t="s">
         <v>149</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>150</v>
-      </c>
-      <c r="D3" t="s">
-        <v>151</v>
-      </c>
-      <c r="E3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -3055,7 +3062,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -3068,7 +3075,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" s="6">
         <v>4.4824999999999999</v>
@@ -3081,7 +3088,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -3094,7 +3101,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" s="6">
         <v>6.8949999999999996</v>
@@ -3105,7 +3112,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B9" s="6">
         <v>5.9312499999999995</v>
@@ -3116,7 +3123,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -3129,7 +3136,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B11" s="6">
         <v>4.6387499999999999</v>
@@ -3144,7 +3151,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="6">
         <v>6.8125</v>
@@ -3159,7 +3166,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="6">
         <v>6.1987500000000013</v>
@@ -3170,7 +3177,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -3183,7 +3190,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B15" s="6">
         <v>4.2712500000000002</v>
@@ -3198,7 +3205,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B16" s="6">
         <v>6.8087499999999999</v>
@@ -3213,7 +3220,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" s="6">
         <v>5.8325000000000005</v>
@@ -3224,7 +3231,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B18" s="6">
         <v>4.5887500000000001</v>
@@ -3239,7 +3246,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B19" s="6">
         <v>5.6459999999999981</v>
@@ -3262,16 +3269,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O169"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:N169"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.375" style="1" customWidth="1"/>
     <col min="2" max="6" width="8.75" style="1"/>
-    <col min="12" max="12" width="11.625"/>
-    <col min="13" max="15" width="20.125"/>
+    <col min="11" max="11" width="11.625"/>
+    <col min="12" max="14" width="20.125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3287,19 +3295,16 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:14" hidden="1">
+      <c r="A2" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="B2" s="1">
         <v>111</v>
@@ -3314,14 +3319,10 @@
         <f>RIGHT(A2,5)</f>
         <v>00:00</v>
       </c>
-      <c r="H2" t="str">
-        <f>TEXT(A2,"HH:MM")</f>
-        <v>00:00</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+    </row>
+    <row r="3" spans="1:14" hidden="1">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1">
         <v>128</v>
@@ -3336,14 +3337,10 @@
         <f t="shared" ref="G3:G47" si="0">RIGHT(A3,5)</f>
         <v>06:00</v>
       </c>
-      <c r="H3" t="str">
-        <f t="shared" ref="H3:H66" si="1">TEXT(A3,"HH:MM")</f>
-        <v>06:00</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1">
         <v>4.37</v>
@@ -3355,14 +3352,10 @@
         <f t="shared" si="0"/>
         <v>07:00</v>
       </c>
-      <c r="H4" t="str">
-        <f t="shared" si="1"/>
-        <v>07:00</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+    </row>
+    <row r="5" spans="1:14" hidden="1">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" s="1">
         <v>0.17</v>
@@ -3374,14 +3367,10 @@
         <f t="shared" si="0"/>
         <v>07:00</v>
       </c>
-      <c r="H5" t="str">
-        <f t="shared" si="1"/>
-        <v>07:00</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+    </row>
+    <row r="6" spans="1:14" hidden="1">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1">
         <v>128</v>
@@ -3396,14 +3385,10 @@
         <f t="shared" si="0"/>
         <v>07:30</v>
       </c>
-      <c r="H6" t="str">
-        <f t="shared" si="1"/>
-        <v>07:30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="1">
         <v>7.71</v>
@@ -3415,14 +3400,10 @@
         <f t="shared" si="0"/>
         <v>08:00</v>
       </c>
-      <c r="H7" t="str">
-        <f t="shared" si="1"/>
-        <v>08:00</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D8" s="1">
         <v>6.46</v>
@@ -3434,14 +3415,10 @@
         <f t="shared" si="0"/>
         <v>09:00</v>
       </c>
-      <c r="H8" t="str">
-        <f t="shared" si="1"/>
-        <v>09:00</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+    </row>
+    <row r="9" spans="1:14" hidden="1">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1">
         <v>132</v>
@@ -3456,12 +3433,11 @@
         <f t="shared" si="0"/>
         <v>10:00</v>
       </c>
-      <c r="H9" t="str">
-        <f t="shared" si="1"/>
-        <v>10:00</v>
+      <c r="K9" t="s">
+        <v>5</v>
       </c>
       <c r="L9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M9" t="s">
         <v>14</v>
@@ -3469,13 +3445,10 @@
       <c r="N9" t="s">
         <v>15</v>
       </c>
-      <c r="O9" t="s">
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="1" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="D10" s="1">
         <v>4.5999999999999996</v>
@@ -3487,20 +3460,16 @@
         <f t="shared" si="0"/>
         <v>12:00</v>
       </c>
-      <c r="H10" t="str">
-        <f t="shared" si="1"/>
-        <v>12:00</v>
-      </c>
-      <c r="L10" t="s">
-        <v>18</v>
-      </c>
-      <c r="O10">
+      <c r="K10" t="s">
+        <v>17</v>
+      </c>
+      <c r="N10">
         <v>79.875</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:14" hidden="1">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1">
         <v>110</v>
@@ -3515,20 +3484,16 @@
         <f t="shared" si="0"/>
         <v>12:00</v>
       </c>
-      <c r="H11" t="str">
-        <f t="shared" si="1"/>
-        <v>12:00</v>
-      </c>
-      <c r="L11" t="s">
+      <c r="K11" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11">
+        <v>81.375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="O11">
-        <v>81.375</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="D12" s="1">
         <v>6.28</v>
@@ -3540,23 +3505,19 @@
         <f t="shared" si="0"/>
         <v>13:00</v>
       </c>
-      <c r="H12" t="str">
-        <f t="shared" si="1"/>
-        <v>13:00</v>
-      </c>
-      <c r="L12" t="s">
-        <v>21</v>
+      <c r="K12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L12">
+        <v>4.4824999999999999</v>
       </c>
       <c r="M12">
-        <v>4.4824999999999999</v>
-      </c>
-      <c r="N12">
         <v>0.17</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:14" hidden="1">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1">
         <v>108</v>
@@ -3571,20 +3532,16 @@
         <f t="shared" si="0"/>
         <v>13:00</v>
       </c>
-      <c r="H13" t="str">
-        <f t="shared" si="1"/>
-        <v>13:00</v>
-      </c>
-      <c r="L13" t="s">
+      <c r="K13" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13">
+        <v>72.375</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="O13">
-        <v>72.375</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
-      <c r="A14" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="D14" s="1">
         <v>5.31</v>
@@ -3596,20 +3553,16 @@
         <f t="shared" si="0"/>
         <v>14:00</v>
       </c>
-      <c r="H14" t="str">
-        <f t="shared" si="1"/>
-        <v>14:00</v>
-      </c>
-      <c r="L14" t="s">
+      <c r="K14" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14">
+        <v>6.8949999999999996</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" hidden="1">
+      <c r="A15" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="M14">
-        <v>6.8949999999999996</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
-      <c r="A15" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="B15" s="1">
         <v>100</v>
@@ -3624,20 +3577,16 @@
         <f t="shared" si="0"/>
         <v>16:00</v>
       </c>
-      <c r="H15" t="str">
-        <f t="shared" si="1"/>
-        <v>16:00</v>
-      </c>
-      <c r="L15" t="s">
+      <c r="K15" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15">
+        <v>5.9312500000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="M15">
-        <v>5.9312500000000004</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
-      <c r="A16" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="D16" s="1">
         <v>4.0599999999999996</v>
@@ -3649,20 +3598,16 @@
         <f t="shared" si="0"/>
         <v>18:00</v>
       </c>
-      <c r="H16" t="str">
-        <f t="shared" si="1"/>
-        <v>18:00</v>
-      </c>
-      <c r="L16" t="s">
-        <v>28</v>
-      </c>
-      <c r="O16">
+      <c r="K16" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16">
         <v>72.5</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:14" hidden="1">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1">
         <v>113</v>
@@ -3677,23 +3622,19 @@
         <f t="shared" si="0"/>
         <v>18:00</v>
       </c>
-      <c r="H17" t="str">
-        <f t="shared" si="1"/>
-        <v>18:00</v>
-      </c>
-      <c r="L17" t="s">
+      <c r="K17" t="s">
+        <v>28</v>
+      </c>
+      <c r="L17">
+        <v>4.6387499999999999</v>
+      </c>
+      <c r="N17">
+        <v>70.25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="M17">
-        <v>4.6387499999999999</v>
-      </c>
-      <c r="O17">
-        <v>70.25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
-      <c r="A18" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="D18" s="1">
         <v>7.56</v>
@@ -3705,23 +3646,19 @@
         <f t="shared" si="0"/>
         <v>19:00</v>
       </c>
-      <c r="H18" t="str">
-        <f t="shared" si="1"/>
-        <v>19:00</v>
-      </c>
-      <c r="L18" t="s">
-        <v>31</v>
-      </c>
-      <c r="M18">
+      <c r="K18" t="s">
+        <v>30</v>
+      </c>
+      <c r="L18">
         <v>6.8125</v>
       </c>
-      <c r="O18">
+      <c r="N18">
         <v>72.5</v>
       </c>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:14" hidden="1">
       <c r="A19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" s="1">
         <v>125</v>
@@ -3736,20 +3673,16 @@
         <f t="shared" si="0"/>
         <v>19:00</v>
       </c>
-      <c r="H19" t="str">
-        <f t="shared" si="1"/>
-        <v>19:00</v>
-      </c>
-      <c r="L19" t="s">
+      <c r="K19" t="s">
+        <v>31</v>
+      </c>
+      <c r="L19">
+        <v>6.1987500000000004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="M19">
-        <v>6.1987500000000004</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="A20" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="D20" s="1">
         <v>6.2</v>
@@ -3761,20 +3694,16 @@
         <f t="shared" si="0"/>
         <v>20:00</v>
       </c>
-      <c r="H20" t="str">
-        <f t="shared" si="1"/>
-        <v>20:00</v>
-      </c>
-      <c r="L20" t="s">
+      <c r="K20" t="s">
+        <v>33</v>
+      </c>
+      <c r="N20">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="O20">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
-      <c r="A21" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="D21" s="1">
         <v>4.91</v>
@@ -3786,23 +3715,19 @@
         <f t="shared" si="0"/>
         <v>22:00</v>
       </c>
-      <c r="H21" t="str">
-        <f t="shared" si="1"/>
-        <v>22:00</v>
-      </c>
-      <c r="L21" t="s">
-        <v>36</v>
-      </c>
-      <c r="M21">
+      <c r="K21" t="s">
+        <v>35</v>
+      </c>
+      <c r="L21">
         <v>4.2712500000000002</v>
       </c>
-      <c r="O21">
+      <c r="N21">
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:14" hidden="1">
       <c r="A22" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" s="1">
         <v>113</v>
@@ -3817,23 +3742,19 @@
         <f t="shared" si="0"/>
         <v>22:00</v>
       </c>
-      <c r="H22" t="str">
-        <f t="shared" si="1"/>
-        <v>22:00</v>
-      </c>
-      <c r="L22" t="s">
+      <c r="K22" t="s">
+        <v>36</v>
+      </c>
+      <c r="L22">
+        <v>6.8087499999999999</v>
+      </c>
+      <c r="N22">
+        <v>74.375</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" hidden="1">
+      <c r="A23" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="M22">
-        <v>6.8087499999999999</v>
-      </c>
-      <c r="O22">
-        <v>74.375</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
-      <c r="A23" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="B23" s="1">
         <v>105</v>
@@ -3848,20 +3769,16 @@
         <f t="shared" si="0"/>
         <v>00:00</v>
       </c>
-      <c r="H23" t="str">
-        <f t="shared" si="1"/>
-        <v>00:00</v>
-      </c>
-      <c r="L23" t="s">
+      <c r="K23" t="s">
+        <v>38</v>
+      </c>
+      <c r="L23">
+        <v>5.8324999999999996</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" hidden="1">
+      <c r="A24" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="M23">
-        <v>5.8324999999999996</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="B24" s="1">
         <v>91</v>
@@ -3876,23 +3793,19 @@
         <f t="shared" si="0"/>
         <v>06:00</v>
       </c>
-      <c r="H24" t="str">
-        <f t="shared" si="1"/>
-        <v>06:00</v>
-      </c>
-      <c r="L24" t="s">
+      <c r="K24" t="s">
+        <v>40</v>
+      </c>
+      <c r="L24">
+        <v>4.5887500000000001</v>
+      </c>
+      <c r="N24">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="M24">
-        <v>4.5887500000000001</v>
-      </c>
-      <c r="O24">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
-      <c r="A25" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="D25" s="1">
         <v>4.0199999999999996</v>
@@ -3904,26 +3817,22 @@
         <f t="shared" si="0"/>
         <v>07:00</v>
       </c>
-      <c r="H25" t="str">
-        <f t="shared" si="1"/>
-        <v>07:00</v>
-      </c>
-      <c r="L25" t="s">
-        <v>43</v>
+      <c r="K25" t="s">
+        <v>42</v>
+      </c>
+      <c r="L25">
+        <v>5.6459999999999999</v>
       </c>
       <c r="M25">
-        <v>5.6459999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="N25">
-        <v>0.17</v>
-      </c>
-      <c r="O25">
         <v>74.525000000000006</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:14" hidden="1">
       <c r="A26" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E26" s="1">
         <v>0.17</v>
@@ -3935,14 +3844,10 @@
         <f t="shared" si="0"/>
         <v>07:00</v>
       </c>
-      <c r="H26" t="str">
-        <f t="shared" si="1"/>
-        <v>07:00</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15">
+    </row>
+    <row r="27" spans="1:14" hidden="1">
       <c r="A27" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B27" s="1">
         <v>143</v>
@@ -3957,14 +3862,10 @@
         <f t="shared" si="0"/>
         <v>07:30</v>
       </c>
-      <c r="H27" t="str">
-        <f t="shared" si="1"/>
-        <v>07:30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15">
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D28" s="1">
         <v>7.75</v>
@@ -3976,14 +3877,10 @@
         <f t="shared" si="0"/>
         <v>08:00</v>
       </c>
-      <c r="H28" t="str">
-        <f t="shared" si="1"/>
-        <v>08:00</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15">
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D29" s="1">
         <v>6.66</v>
@@ -3995,14 +3892,10 @@
         <f t="shared" si="0"/>
         <v>09:00</v>
       </c>
-      <c r="H29" t="str">
-        <f t="shared" si="1"/>
-        <v>09:00</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15">
+    </row>
+    <row r="30" spans="1:14" hidden="1">
       <c r="A30" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B30" s="1">
         <v>127</v>
@@ -4017,14 +3910,10 @@
         <f t="shared" si="0"/>
         <v>10:00</v>
       </c>
-      <c r="H30" t="str">
-        <f t="shared" si="1"/>
-        <v>10:00</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15">
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D31" s="1">
         <v>4.21</v>
@@ -4036,14 +3925,10 @@
         <f t="shared" si="0"/>
         <v>12:00</v>
       </c>
-      <c r="H31" t="str">
-        <f t="shared" si="1"/>
-        <v>12:00</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15">
+    </row>
+    <row r="32" spans="1:14" hidden="1">
       <c r="A32" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B32" s="1">
         <v>110</v>
@@ -4058,14 +3943,10 @@
         <f t="shared" si="0"/>
         <v>12:00</v>
       </c>
-      <c r="H32" t="str">
-        <f t="shared" si="1"/>
-        <v>12:00</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D33" s="1">
         <v>6.33</v>
@@ -4077,14 +3958,10 @@
         <f t="shared" si="0"/>
         <v>13:00</v>
       </c>
-      <c r="H33" t="str">
-        <f t="shared" si="1"/>
-        <v>13:00</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+    </row>
+    <row r="34" spans="1:7" hidden="1">
       <c r="A34" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B34" s="1">
         <v>101</v>
@@ -4099,14 +3976,10 @@
         <f t="shared" si="0"/>
         <v>13:00</v>
       </c>
-      <c r="H34" t="str">
-        <f t="shared" si="1"/>
-        <v>13:00</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D35" s="1">
         <v>5.37</v>
@@ -4118,14 +3991,10 @@
         <f t="shared" si="0"/>
         <v>14:00</v>
       </c>
-      <c r="H35" t="str">
-        <f t="shared" si="1"/>
-        <v>14:00</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+    </row>
+    <row r="36" spans="1:7" hidden="1">
       <c r="A36" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B36" s="1">
         <v>111</v>
@@ -4140,14 +4009,10 @@
         <f t="shared" si="0"/>
         <v>16:00</v>
       </c>
-      <c r="H36" t="str">
-        <f t="shared" si="1"/>
-        <v>16:00</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D37" s="1">
         <v>4.3</v>
@@ -4159,14 +4024,10 @@
         <f t="shared" si="0"/>
         <v>18:00</v>
       </c>
-      <c r="H37" t="str">
-        <f t="shared" si="1"/>
-        <v>18:00</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+    </row>
+    <row r="38" spans="1:7" hidden="1">
       <c r="A38" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B38" s="1">
         <v>133</v>
@@ -4181,14 +4042,10 @@
         <f t="shared" si="0"/>
         <v>18:00</v>
       </c>
-      <c r="H38" t="str">
-        <f t="shared" si="1"/>
-        <v>18:00</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D39" s="1">
         <v>6.94</v>
@@ -4200,14 +4057,10 @@
         <f t="shared" si="0"/>
         <v>19:00</v>
       </c>
-      <c r="H39" t="str">
-        <f t="shared" si="1"/>
-        <v>19:00</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+    </row>
+    <row r="40" spans="1:7" hidden="1">
       <c r="A40" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B40" s="1">
         <v>138</v>
@@ -4222,14 +4075,10 @@
         <f t="shared" si="0"/>
         <v>19:00</v>
       </c>
-      <c r="H40" t="str">
-        <f t="shared" si="1"/>
-        <v>19:00</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D41" s="1">
         <v>5.86</v>
@@ -4241,14 +4090,10 @@
         <f t="shared" si="0"/>
         <v>20:00</v>
       </c>
-      <c r="H41" t="str">
-        <f t="shared" si="1"/>
-        <v>20:00</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D42" s="1">
         <v>4.49</v>
@@ -4260,14 +4105,10 @@
         <f t="shared" si="0"/>
         <v>22:00</v>
       </c>
-      <c r="H42" t="str">
-        <f t="shared" si="1"/>
-        <v>22:00</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+    </row>
+    <row r="43" spans="1:7" hidden="1">
       <c r="A43" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B43" s="1">
         <v>131</v>
@@ -4282,14 +4123,10 @@
         <f t="shared" si="0"/>
         <v>22:00</v>
       </c>
-      <c r="H43" t="str">
-        <f t="shared" si="1"/>
-        <v>22:00</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+    </row>
+    <row r="44" spans="1:7" hidden="1">
       <c r="A44" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B44" s="1">
         <v>91</v>
@@ -4304,14 +4141,10 @@
         <f t="shared" si="0"/>
         <v>00:00</v>
       </c>
-      <c r="H44" t="str">
-        <f t="shared" si="1"/>
-        <v>00:00</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+    </row>
+    <row r="45" spans="1:7" hidden="1">
       <c r="A45" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B45" s="1">
         <v>136</v>
@@ -4326,14 +4159,10 @@
         <f t="shared" si="0"/>
         <v>06:00</v>
       </c>
-      <c r="H45" t="str">
-        <f t="shared" si="1"/>
-        <v>06:00</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D46" s="1">
         <v>4.6100000000000003</v>
@@ -4345,14 +4174,10 @@
         <f t="shared" si="0"/>
         <v>07:00</v>
       </c>
-      <c r="H46" t="str">
-        <f t="shared" si="1"/>
-        <v>07:00</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+    </row>
+    <row r="47" spans="1:7" hidden="1">
       <c r="A47" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E47" s="1">
         <v>0.17</v>
@@ -4364,2505 +4189,2019 @@
         <f t="shared" si="0"/>
         <v>07:00</v>
       </c>
-      <c r="H47" t="str">
+    </row>
+    <row r="48" spans="1:7" hidden="1">
+      <c r="A48" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" s="1">
+        <v>150</v>
+      </c>
+      <c r="C48" s="1">
+        <v>71</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="G48" t="str">
+        <f t="shared" ref="G48:G79" si="1">RIGHT(A48,5)</f>
+        <v>07:30</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D49" s="1">
+        <v>6.25</v>
+      </c>
+      <c r="F49" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="G49" t="str">
+        <f t="shared" si="1"/>
+        <v>08:00</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D50" s="1">
+        <v>5.58</v>
+      </c>
+      <c r="F50" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="G50" t="str">
+        <f t="shared" si="1"/>
+        <v>09:00</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" hidden="1">
+      <c r="A51" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" s="1">
+        <v>92</v>
+      </c>
+      <c r="C51" s="1">
+        <v>64</v>
+      </c>
+      <c r="F51" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="G51" t="str">
+        <f t="shared" si="1"/>
+        <v>10:00</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D52" s="1">
+        <v>4.37</v>
+      </c>
+      <c r="F52" s="1">
+        <v>0.52</v>
+      </c>
+      <c r="G52" t="str">
+        <f t="shared" si="1"/>
+        <v>12:00</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" hidden="1">
+      <c r="A53" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B53" s="1">
+        <v>140</v>
+      </c>
+      <c r="C53" s="1">
+        <v>66</v>
+      </c>
+      <c r="F53" s="1">
+        <v>0.53</v>
+      </c>
+      <c r="G53" t="str">
+        <f t="shared" si="1"/>
+        <v>12:00</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D54" s="1">
+        <v>6.82</v>
+      </c>
+      <c r="F54" s="1">
+        <v>0.79</v>
+      </c>
+      <c r="G54" t="str">
+        <f t="shared" si="1"/>
+        <v>13:00</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" hidden="1">
+      <c r="A55" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" s="1">
+        <v>110</v>
+      </c>
+      <c r="C55" s="1">
+        <v>68</v>
+      </c>
+      <c r="F55" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="G55" t="str">
+        <f t="shared" si="1"/>
+        <v>13:00</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D56" s="1">
+        <v>6.57</v>
+      </c>
+      <c r="F56" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="G56" t="str">
+        <f t="shared" si="1"/>
+        <v>14:00</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" hidden="1">
+      <c r="A57" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" s="1">
+        <v>128</v>
+      </c>
+      <c r="C57" s="1">
+        <v>77</v>
+      </c>
+      <c r="F57" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="G57" t="str">
+        <f t="shared" si="1"/>
+        <v>16:00</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D58" s="1">
+        <v>4.2</v>
+      </c>
+      <c r="F58" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="G58" t="str">
+        <f t="shared" si="1"/>
+        <v>18:00</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" hidden="1">
+      <c r="A59" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="1">
+        <v>93</v>
+      </c>
+      <c r="C59" s="1">
+        <v>84</v>
+      </c>
+      <c r="F59" s="1">
+        <v>0.61</v>
+      </c>
+      <c r="G59" t="str">
+        <f t="shared" si="1"/>
+        <v>18:00</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D60" s="1">
+        <v>6.93</v>
+      </c>
+      <c r="F60" s="1">
+        <v>0.94</v>
+      </c>
+      <c r="G60" t="str">
+        <f t="shared" si="1"/>
+        <v>19:00</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" hidden="1">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1">
+        <v>103</v>
+      </c>
+      <c r="C61" s="1">
+        <v>77</v>
+      </c>
+      <c r="F61" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="G61" t="str">
+        <f t="shared" si="1"/>
+        <v>19:00</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D62" s="1">
+        <v>6.18</v>
+      </c>
+      <c r="F62" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="G62" t="str">
+        <f t="shared" si="1"/>
+        <v>20:00</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D63" s="1">
+        <v>4.25</v>
+      </c>
+      <c r="F63" s="1">
+        <v>0.51</v>
+      </c>
+      <c r="G63" t="str">
+        <f t="shared" si="1"/>
+        <v>22:00</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" hidden="1">
+      <c r="A64" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64" s="1">
+        <v>98</v>
+      </c>
+      <c r="C64" s="1">
+        <v>85</v>
+      </c>
+      <c r="F64" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="G64" t="str">
+        <f t="shared" si="1"/>
+        <v>22:00</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" hidden="1">
+      <c r="A65" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B65" s="1">
+        <v>118</v>
+      </c>
+      <c r="C65" s="1">
+        <v>90</v>
+      </c>
+      <c r="F65" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="G65" t="str">
+        <f t="shared" si="1"/>
+        <v>00:00</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" hidden="1">
+      <c r="A66" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="1">
+        <v>117</v>
+      </c>
+      <c r="C66" s="1">
+        <v>74</v>
+      </c>
+      <c r="F66" s="1">
+        <v>0.53</v>
+      </c>
+      <c r="G66" t="str">
+        <f t="shared" si="1"/>
+        <v>06:00</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D67" s="1">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="F67" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="G67" t="str">
         <f t="shared" si="1"/>
         <v>07:00</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B48" s="1">
-        <v>150</v>
-      </c>
-      <c r="C48" s="1">
+    <row r="68" spans="1:7" hidden="1">
+      <c r="A68" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E68" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="F68" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="G68" t="str">
+        <f t="shared" si="1"/>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" hidden="1">
+      <c r="A69" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" s="1">
+        <v>106</v>
+      </c>
+      <c r="C69" s="1">
         <v>71</v>
       </c>
-      <c r="F48" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="G48" t="str">
-        <f t="shared" ref="G48:G79" si="2">RIGHT(A48,5)</f>
-        <v>07:30</v>
-      </c>
-      <c r="H48" t="str">
+      <c r="F69" s="1">
+        <v>0.62</v>
+      </c>
+      <c r="G69" t="str">
         <f t="shared" si="1"/>
         <v>07:30</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
-      <c r="A49" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D49" s="1">
-        <v>6.25</v>
-      </c>
-      <c r="F49" s="1">
-        <v>0.76</v>
-      </c>
-      <c r="G49" t="str">
+    <row r="70" spans="1:7">
+      <c r="A70" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D70" s="1">
+        <v>6.31</v>
+      </c>
+      <c r="F70" s="1">
+        <v>0.48</v>
+      </c>
+      <c r="G70" t="str">
+        <f t="shared" si="1"/>
+        <v>08:00</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D71" s="1">
+        <v>5.13</v>
+      </c>
+      <c r="F71" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="G71" t="str">
+        <f t="shared" si="1"/>
+        <v>09:00</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" hidden="1">
+      <c r="A72" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B72" s="1">
+        <v>97</v>
+      </c>
+      <c r="C72" s="1">
+        <v>74</v>
+      </c>
+      <c r="F72" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="G72" t="str">
+        <f t="shared" si="1"/>
+        <v>10:00</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D73" s="1">
+        <v>4.95</v>
+      </c>
+      <c r="F73" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="G73" t="str">
+        <f t="shared" si="1"/>
+        <v>12:00</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" hidden="1">
+      <c r="A74" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B74" s="1">
+        <v>124</v>
+      </c>
+      <c r="C74" s="1">
+        <v>73</v>
+      </c>
+      <c r="F74" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="G74" t="str">
+        <f t="shared" si="1"/>
+        <v>12:00</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D75" s="1">
+        <v>7.74</v>
+      </c>
+      <c r="F75" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="G75" t="str">
+        <f t="shared" si="1"/>
+        <v>13:00</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" hidden="1">
+      <c r="A76" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B76" s="1">
+        <v>106</v>
+      </c>
+      <c r="C76" s="1">
+        <v>63</v>
+      </c>
+      <c r="F76" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="G76" t="str">
+        <f t="shared" si="1"/>
+        <v>13:00</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D77" s="1">
+        <v>6.62</v>
+      </c>
+      <c r="F77" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="G77" t="str">
+        <f t="shared" si="1"/>
+        <v>14:00</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" hidden="1">
+      <c r="A78" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B78" s="1">
+        <v>139</v>
+      </c>
+      <c r="C78" s="1">
+        <v>67</v>
+      </c>
+      <c r="F78" s="1">
+        <v>0.89</v>
+      </c>
+      <c r="G78" t="str">
+        <f t="shared" si="1"/>
+        <v>16:00</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D79" s="1">
+        <v>4.3</v>
+      </c>
+      <c r="F79" s="1">
+        <v>0.22</v>
+      </c>
+      <c r="G79" t="str">
+        <f t="shared" si="1"/>
+        <v>18:00</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" hidden="1">
+      <c r="A80" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B80" s="1">
+        <v>93</v>
+      </c>
+      <c r="C80" s="1">
+        <v>61</v>
+      </c>
+      <c r="F80" s="1">
+        <v>0.77</v>
+      </c>
+      <c r="G80" t="str">
+        <f t="shared" ref="G80:G111" si="2">RIGHT(A80,5)</f>
+        <v>18:00</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D81" s="1">
+        <v>6.18</v>
+      </c>
+      <c r="F81" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="G81" t="str">
+        <f t="shared" si="2"/>
+        <v>19:00</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" hidden="1">
+      <c r="A82" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B82" s="1">
+        <v>95</v>
+      </c>
+      <c r="C82" s="1">
+        <v>81</v>
+      </c>
+      <c r="F82" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="G82" t="str">
+        <f t="shared" si="2"/>
+        <v>19:00</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D83" s="1">
+        <v>6.37</v>
+      </c>
+      <c r="F83" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="G83" t="str">
+        <f t="shared" si="2"/>
+        <v>20:00</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D84" s="1">
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="F84" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="G84" t="str">
+        <f t="shared" si="2"/>
+        <v>22:00</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" hidden="1">
+      <c r="A85" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B85" s="1">
+        <v>131</v>
+      </c>
+      <c r="C85" s="1">
+        <v>63</v>
+      </c>
+      <c r="F85" s="1">
+        <v>0.73</v>
+      </c>
+      <c r="G85" t="str">
+        <f t="shared" si="2"/>
+        <v>22:00</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" hidden="1">
+      <c r="A86" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B86" s="1">
+        <v>107</v>
+      </c>
+      <c r="C86" s="1">
+        <v>74</v>
+      </c>
+      <c r="F86" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="G86" t="str">
+        <f t="shared" si="2"/>
+        <v>00:00</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" hidden="1">
+      <c r="A87" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B87" s="1">
+        <v>107</v>
+      </c>
+      <c r="C87" s="1">
+        <v>85</v>
+      </c>
+      <c r="F87" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="G87" t="str">
+        <f t="shared" si="2"/>
+        <v>06:00</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D88" s="1">
+        <v>4.12</v>
+      </c>
+      <c r="F88" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="G88" t="str">
+        <f t="shared" si="2"/>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" hidden="1">
+      <c r="A89" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E89" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="F89" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="G89" t="str">
+        <f t="shared" si="2"/>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" hidden="1">
+      <c r="A90" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B90" s="1">
+        <v>143</v>
+      </c>
+      <c r="C90" s="1">
+        <v>61</v>
+      </c>
+      <c r="F90" s="1">
+        <v>0.82</v>
+      </c>
+      <c r="G90" t="str">
+        <f t="shared" si="2"/>
+        <v>07:30</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D91" s="1">
+        <v>6.89</v>
+      </c>
+      <c r="F91" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="G91" t="str">
         <f t="shared" si="2"/>
         <v>08:00</v>
       </c>
-      <c r="H49" t="str">
-        <f t="shared" si="1"/>
-        <v>08:00</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D50" s="1">
-        <v>5.58</v>
-      </c>
-      <c r="F50" s="1">
-        <v>0.46</v>
-      </c>
-      <c r="G50" t="str">
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D92" s="1">
+        <v>5.07</v>
+      </c>
+      <c r="F92" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="G92" t="str">
         <f t="shared" si="2"/>
         <v>09:00</v>
       </c>
-      <c r="H50" t="str">
-        <f t="shared" si="1"/>
-        <v>09:00</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B51" s="1">
-        <v>92</v>
-      </c>
-      <c r="C51" s="1">
-        <v>64</v>
-      </c>
-      <c r="F51" s="1">
-        <v>0.61</v>
-      </c>
-      <c r="G51" t="str">
+    </row>
+    <row r="93" spans="1:7" hidden="1">
+      <c r="A93" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B93" s="1">
+        <v>99</v>
+      </c>
+      <c r="C93" s="1">
+        <v>89</v>
+      </c>
+      <c r="F93" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="G93" t="str">
         <f t="shared" si="2"/>
         <v>10:00</v>
       </c>
-      <c r="H51" t="str">
-        <f t="shared" si="1"/>
-        <v>10:00</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
-      <c r="A52" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D52" s="1">
-        <v>4.37</v>
-      </c>
-      <c r="F52" s="1">
-        <v>0.52</v>
-      </c>
-      <c r="G52" t="str">
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D94" s="1">
+        <v>4.91</v>
+      </c>
+      <c r="F94" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="G94" t="str">
         <f t="shared" si="2"/>
         <v>12:00</v>
       </c>
-      <c r="H52" t="str">
-        <f t="shared" si="1"/>
-        <v>12:00</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
-      <c r="A53" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B53" s="1">
-        <v>140</v>
-      </c>
-      <c r="C53" s="1">
-        <v>66</v>
-      </c>
-      <c r="F53" s="1">
-        <v>0.53</v>
-      </c>
-      <c r="G53" t="str">
+    </row>
+    <row r="95" spans="1:7" hidden="1">
+      <c r="A95" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B95" s="1">
+        <v>125</v>
+      </c>
+      <c r="C95" s="1">
+        <v>73</v>
+      </c>
+      <c r="F95" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="G95" t="str">
         <f t="shared" si="2"/>
         <v>12:00</v>
       </c>
-      <c r="H53" t="str">
-        <f t="shared" si="1"/>
-        <v>12:00</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
-      <c r="A54" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D54" s="1">
-        <v>6.82</v>
-      </c>
-      <c r="F54" s="1">
-        <v>0.79</v>
-      </c>
-      <c r="G54" t="str">
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D96" s="1">
+        <v>6.47</v>
+      </c>
+      <c r="F96" s="1">
+        <v>0.82</v>
+      </c>
+      <c r="G96" t="str">
         <f t="shared" si="2"/>
         <v>13:00</v>
       </c>
-      <c r="H54" t="str">
-        <f t="shared" si="1"/>
-        <v>13:00</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B55" s="1">
-        <v>110</v>
-      </c>
-      <c r="C55" s="1">
-        <v>68</v>
-      </c>
-      <c r="F55" s="1">
-        <v>0.44</v>
-      </c>
-      <c r="G55" t="str">
+    </row>
+    <row r="97" spans="1:7" hidden="1">
+      <c r="A97" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B97" s="1">
+        <v>120</v>
+      </c>
+      <c r="C97" s="1">
+        <v>75</v>
+      </c>
+      <c r="F97" s="1">
+        <v>0.21</v>
+      </c>
+      <c r="G97" t="str">
         <f t="shared" si="2"/>
         <v>13:00</v>
       </c>
-      <c r="H55" t="str">
-        <f t="shared" si="1"/>
-        <v>13:00</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
-      <c r="A56" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D56" s="1">
-        <v>6.57</v>
-      </c>
-      <c r="F56" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="G56" t="str">
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D98" s="1">
+        <v>6.33</v>
+      </c>
+      <c r="F98" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="G98" t="str">
         <f t="shared" si="2"/>
         <v>14:00</v>
       </c>
-      <c r="H56" t="str">
-        <f t="shared" si="1"/>
-        <v>14:00</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
-      <c r="A57" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B57" s="1">
-        <v>128</v>
-      </c>
-      <c r="C57" s="1">
-        <v>77</v>
-      </c>
-      <c r="F57" s="1">
-        <v>0.45</v>
-      </c>
-      <c r="G57" t="str">
+    </row>
+    <row r="99" spans="1:7" hidden="1">
+      <c r="A99" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B99" s="1">
+        <v>104</v>
+      </c>
+      <c r="C99" s="1">
+        <v>67</v>
+      </c>
+      <c r="F99" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="G99" t="str">
         <f t="shared" si="2"/>
         <v>16:00</v>
       </c>
-      <c r="H57" t="str">
-        <f t="shared" si="1"/>
-        <v>16:00</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D58" s="1">
-        <v>4.2</v>
-      </c>
-      <c r="F58" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="G58" t="str">
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D100" s="1">
+        <v>4.3099999999999996</v>
+      </c>
+      <c r="F100" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="G100" t="str">
         <f t="shared" si="2"/>
         <v>18:00</v>
       </c>
-      <c r="H58" t="str">
-        <f t="shared" si="1"/>
-        <v>18:00</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B59" s="1">
-        <v>93</v>
-      </c>
-      <c r="C59" s="1">
-        <v>84</v>
-      </c>
-      <c r="F59" s="1">
-        <v>0.61</v>
-      </c>
-      <c r="G59" t="str">
+    </row>
+    <row r="101" spans="1:7" hidden="1">
+      <c r="A101" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B101" s="1">
+        <v>103</v>
+      </c>
+      <c r="C101" s="1">
+        <v>82</v>
+      </c>
+      <c r="F101" s="1">
+        <v>0.64</v>
+      </c>
+      <c r="G101" t="str">
         <f t="shared" si="2"/>
         <v>18:00</v>
       </c>
-      <c r="H59" t="str">
-        <f t="shared" si="1"/>
-        <v>18:00</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D60" s="1">
-        <v>6.93</v>
-      </c>
-      <c r="F60" s="1">
-        <v>0.94</v>
-      </c>
-      <c r="G60" t="str">
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D102" s="1">
+        <v>6.94</v>
+      </c>
+      <c r="F102" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="G102" t="str">
         <f t="shared" si="2"/>
         <v>19:00</v>
       </c>
-      <c r="H60" t="str">
-        <f t="shared" si="1"/>
-        <v>19:00</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B61" s="1">
-        <v>103</v>
-      </c>
-      <c r="C61" s="1">
-        <v>77</v>
-      </c>
-      <c r="F61" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="G61" t="str">
+    </row>
+    <row r="103" spans="1:7" hidden="1">
+      <c r="A103" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B103" s="1">
+        <v>129</v>
+      </c>
+      <c r="C103" s="1">
+        <v>80</v>
+      </c>
+      <c r="F103" s="1">
+        <v>0.38</v>
+      </c>
+      <c r="G103" t="str">
         <f t="shared" si="2"/>
         <v>19:00</v>
       </c>
-      <c r="H61" t="str">
-        <f t="shared" si="1"/>
-        <v>19:00</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D62" s="1">
-        <v>6.18</v>
-      </c>
-      <c r="F62" s="1">
-        <v>0.76</v>
-      </c>
-      <c r="G62" t="str">
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D104" s="1">
+        <v>6.09</v>
+      </c>
+      <c r="F104" s="1">
+        <v>0.93</v>
+      </c>
+      <c r="G104" t="str">
         <f t="shared" si="2"/>
         <v>20:00</v>
       </c>
-      <c r="H62" t="str">
-        <f t="shared" si="1"/>
-        <v>20:00</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="A63" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D63" s="1">
-        <v>4.25</v>
-      </c>
-      <c r="F63" s="1">
-        <v>0.51</v>
-      </c>
-      <c r="G63" t="str">
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D105" s="1">
+        <v>4.38</v>
+      </c>
+      <c r="F105" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="G105" t="str">
         <f t="shared" si="2"/>
         <v>22:00</v>
       </c>
-      <c r="H63" t="str">
-        <f t="shared" si="1"/>
-        <v>22:00</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B64" s="1">
-        <v>98</v>
-      </c>
-      <c r="C64" s="1">
-        <v>85</v>
-      </c>
-      <c r="F64" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="G64" t="str">
+    </row>
+    <row r="106" spans="1:7" hidden="1">
+      <c r="A106" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B106" s="1">
+        <v>105</v>
+      </c>
+      <c r="C106" s="1">
+        <v>72</v>
+      </c>
+      <c r="F106" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="G106" t="str">
         <f t="shared" si="2"/>
         <v>22:00</v>
       </c>
-      <c r="H64" t="str">
-        <f t="shared" si="1"/>
-        <v>22:00</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
-      <c r="A65" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B65" s="1">
-        <v>118</v>
-      </c>
-      <c r="C65" s="1">
-        <v>90</v>
-      </c>
-      <c r="F65" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="G65" t="str">
+    </row>
+    <row r="107" spans="1:7" hidden="1">
+      <c r="A107" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B107" s="1">
+        <v>100</v>
+      </c>
+      <c r="C107" s="1">
+        <v>78</v>
+      </c>
+      <c r="F107" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="G107" t="str">
         <f t="shared" si="2"/>
         <v>00:00</v>
       </c>
-      <c r="H65" t="str">
-        <f t="shared" si="1"/>
-        <v>00:00</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B66" s="1">
-        <v>117</v>
-      </c>
-      <c r="C66" s="1">
-        <v>74</v>
-      </c>
-      <c r="F66" s="1">
-        <v>0.53</v>
-      </c>
-      <c r="G66" t="str">
+    </row>
+    <row r="108" spans="1:7" hidden="1">
+      <c r="A108" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B108" s="1">
+        <v>113</v>
+      </c>
+      <c r="C108" s="1">
+        <v>85</v>
+      </c>
+      <c r="F108" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="G108" t="str">
         <f t="shared" si="2"/>
         <v>06:00</v>
       </c>
-      <c r="H66" t="str">
-        <f t="shared" si="1"/>
-        <v>06:00</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="A67" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D67" s="1">
-        <v>4.6100000000000003</v>
-      </c>
-      <c r="F67" s="1">
-        <v>0.42</v>
-      </c>
-      <c r="G67" t="str">
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D109" s="1">
+        <v>4.97</v>
+      </c>
+      <c r="F109" s="1">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="G109" t="str">
         <f t="shared" si="2"/>
         <v>07:00</v>
       </c>
-      <c r="H67" t="str">
-        <f t="shared" ref="H67:H130" si="3">TEXT(A67,"HH:MM")</f>
-        <v>07:00</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="E68" s="1">
+    </row>
+    <row r="110" spans="1:7" hidden="1">
+      <c r="A110" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E110" s="1">
         <v>0.17</v>
       </c>
-      <c r="F68" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="G68" t="str">
+      <c r="F110" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="G110" t="str">
         <f t="shared" si="2"/>
         <v>07:00</v>
       </c>
-      <c r="H68" t="str">
+    </row>
+    <row r="111" spans="1:7" hidden="1">
+      <c r="A111" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B111" s="1">
+        <v>124</v>
+      </c>
+      <c r="C111" s="1">
+        <v>87</v>
+      </c>
+      <c r="F111" s="1">
+        <v>0.36</v>
+      </c>
+      <c r="G111" t="str">
+        <f t="shared" si="2"/>
+        <v>07:30</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D112" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="F112" s="1">
+        <v>0.59</v>
+      </c>
+      <c r="G112" t="str">
+        <f t="shared" ref="G112:G143" si="3">RIGHT(A112,5)</f>
+        <v>08:00</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D113" s="1">
+        <v>6.88</v>
+      </c>
+      <c r="F113" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="G113" t="str">
+        <f t="shared" si="3"/>
+        <v>09:00</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" hidden="1">
+      <c r="A114" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B114" s="1">
+        <v>134</v>
+      </c>
+      <c r="C114" s="1">
+        <v>68</v>
+      </c>
+      <c r="F114" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="G114" t="str">
+        <f t="shared" si="3"/>
+        <v>10:00</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D115" s="1">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="F115" s="1">
+        <v>0.76</v>
+      </c>
+      <c r="G115" t="str">
+        <f t="shared" si="3"/>
+        <v>12:00</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" hidden="1">
+      <c r="A116" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B116" s="1">
+        <v>118</v>
+      </c>
+      <c r="C116" s="1">
+        <v>74</v>
+      </c>
+      <c r="F116" s="1">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G116" t="str">
+        <f t="shared" si="3"/>
+        <v>12:00</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D117" s="1">
+        <v>7.08</v>
+      </c>
+      <c r="F117" s="1">
+        <v>0.48</v>
+      </c>
+      <c r="G117" t="str">
+        <f t="shared" si="3"/>
+        <v>13:00</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" hidden="1">
+      <c r="A118" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B118" s="1">
+        <v>134</v>
+      </c>
+      <c r="C118" s="1">
+        <v>60</v>
+      </c>
+      <c r="F118" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="G118" t="str">
+        <f t="shared" si="3"/>
+        <v>13:00</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D119" s="1">
+        <v>6.84</v>
+      </c>
+      <c r="F119" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="G119" t="str">
+        <f t="shared" si="3"/>
+        <v>14:00</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" hidden="1">
+      <c r="A120" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B120" s="1">
+        <v>114</v>
+      </c>
+      <c r="C120" s="1">
+        <v>66</v>
+      </c>
+      <c r="F120" s="1">
+        <v>0.98</v>
+      </c>
+      <c r="G120" t="str">
+        <f t="shared" si="3"/>
+        <v>16:00</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D121" s="1">
+        <v>4.09</v>
+      </c>
+      <c r="F121" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="G121" t="str">
+        <f t="shared" si="3"/>
+        <v>18:00</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" hidden="1">
+      <c r="A122" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B122" s="1">
+        <v>98</v>
+      </c>
+      <c r="C122" s="1">
+        <v>83</v>
+      </c>
+      <c r="F122" s="1">
+        <v>0.35</v>
+      </c>
+      <c r="G122" t="str">
+        <f t="shared" si="3"/>
+        <v>18:00</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D123" s="1">
+        <v>6.35</v>
+      </c>
+      <c r="F123" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="G123" t="str">
+        <f t="shared" si="3"/>
+        <v>19:00</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" hidden="1">
+      <c r="A124" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B124" s="1">
+        <v>90</v>
+      </c>
+      <c r="C124" s="1">
+        <v>71</v>
+      </c>
+      <c r="F124" s="1">
+        <v>0.94</v>
+      </c>
+      <c r="G124" t="str">
+        <f t="shared" si="3"/>
+        <v>19:00</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D125" s="1">
+        <v>5.09</v>
+      </c>
+      <c r="F125" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="G125" t="str">
+        <f t="shared" si="3"/>
+        <v>20:00</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D126" s="1">
+        <v>4.53</v>
+      </c>
+      <c r="F126" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="G126" t="str">
+        <f t="shared" si="3"/>
+        <v>22:00</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" hidden="1">
+      <c r="A127" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B127" s="1">
+        <v>97</v>
+      </c>
+      <c r="C127" s="1">
+        <v>83</v>
+      </c>
+      <c r="F127" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="G127" t="str">
+        <f t="shared" si="3"/>
+        <v>22:00</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" hidden="1">
+      <c r="A128" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B128" s="1">
+        <v>137</v>
+      </c>
+      <c r="C128" s="1">
+        <v>82</v>
+      </c>
+      <c r="F128" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="G128" t="str">
+        <f t="shared" si="3"/>
+        <v>00:00</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" hidden="1">
+      <c r="A129" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B129" s="1">
+        <v>106</v>
+      </c>
+      <c r="C129" s="1">
+        <v>67</v>
+      </c>
+      <c r="F129" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="G129" t="str">
+        <f t="shared" si="3"/>
+        <v>06:00</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D130" s="1">
+        <v>4.3899999999999997</v>
+      </c>
+      <c r="F130" s="1">
+        <v>0.78</v>
+      </c>
+      <c r="G130" t="str">
         <f t="shared" si="3"/>
         <v>07:00</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
-      <c r="A69" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B69" s="1">
-        <v>106</v>
-      </c>
-      <c r="C69" s="1">
-        <v>71</v>
-      </c>
-      <c r="F69" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="G69" t="str">
-        <f t="shared" si="2"/>
-        <v>07:30</v>
-      </c>
-      <c r="H69" t="str">
+    <row r="131" spans="1:7" hidden="1">
+      <c r="A131" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E131" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="F131" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="G131" t="str">
+        <f t="shared" si="3"/>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" hidden="1">
+      <c r="A132" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B132" s="1">
+        <v>134</v>
+      </c>
+      <c r="C132" s="1">
+        <v>62</v>
+      </c>
+      <c r="F132" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="G132" t="str">
         <f t="shared" si="3"/>
         <v>07:30</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
-      <c r="A70" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D70" s="1">
-        <v>6.31</v>
-      </c>
-      <c r="F70" s="1">
-        <v>0.48</v>
-      </c>
-      <c r="G70" t="str">
-        <f t="shared" si="2"/>
-        <v>08:00</v>
-      </c>
-      <c r="H70" t="str">
+    <row r="133" spans="1:7">
+      <c r="A133" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D133" s="1">
+        <v>6.49</v>
+      </c>
+      <c r="F133" s="1">
+        <v>0.32</v>
+      </c>
+      <c r="G133" t="str">
         <f t="shared" si="3"/>
         <v>08:00</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D71" s="1">
-        <v>5.13</v>
-      </c>
-      <c r="F71" s="1">
-        <v>0.98</v>
-      </c>
-      <c r="G71" t="str">
-        <f t="shared" si="2"/>
-        <v>09:00</v>
-      </c>
-      <c r="H71" t="str">
+    <row r="134" spans="1:7">
+      <c r="A134" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D134" s="1">
+        <v>6.66</v>
+      </c>
+      <c r="F134" s="1">
+        <v>0.63</v>
+      </c>
+      <c r="G134" t="str">
         <f t="shared" si="3"/>
         <v>09:00</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
-      <c r="A72" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B72" s="1">
-        <v>97</v>
-      </c>
-      <c r="C72" s="1">
-        <v>74</v>
-      </c>
-      <c r="F72" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="G72" t="str">
-        <f t="shared" si="2"/>
-        <v>10:00</v>
-      </c>
-      <c r="H72" t="str">
+    <row r="135" spans="1:7" hidden="1">
+      <c r="A135" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B135" s="1">
+        <v>122</v>
+      </c>
+      <c r="C135" s="1">
+        <v>86</v>
+      </c>
+      <c r="F135" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="G135" t="str">
         <f t="shared" si="3"/>
         <v>10:00</v>
       </c>
     </row>
-    <row r="73" spans="1:8">
-      <c r="A73" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D73" s="1">
-        <v>4.95</v>
-      </c>
-      <c r="F73" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="G73" t="str">
-        <f t="shared" si="2"/>
-        <v>12:00</v>
-      </c>
-      <c r="H73" t="str">
+    <row r="136" spans="1:7">
+      <c r="A136" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D136" s="1">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="F136" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="G136" t="str">
         <f t="shared" si="3"/>
         <v>12:00</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
-      <c r="A74" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B74" s="1">
-        <v>124</v>
-      </c>
-      <c r="C74" s="1">
-        <v>73</v>
-      </c>
-      <c r="F74" s="1">
-        <v>0.49</v>
-      </c>
-      <c r="G74" t="str">
-        <f t="shared" si="2"/>
-        <v>12:00</v>
-      </c>
-      <c r="H74" t="str">
+    <row r="137" spans="1:7" hidden="1">
+      <c r="A137" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B137" s="1">
+        <v>94</v>
+      </c>
+      <c r="C137" s="1">
+        <v>69</v>
+      </c>
+      <c r="F137" s="1">
+        <v>0.91</v>
+      </c>
+      <c r="G137" t="str">
         <f t="shared" si="3"/>
         <v>12:00</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
-      <c r="A75" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D75" s="1">
-        <v>7.74</v>
-      </c>
-      <c r="F75" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="G75" t="str">
-        <f t="shared" si="2"/>
-        <v>13:00</v>
-      </c>
-      <c r="H75" t="str">
+    <row r="138" spans="1:7">
+      <c r="A138" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D138" s="1">
+        <v>6.51</v>
+      </c>
+      <c r="F138" s="1">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G138" t="str">
         <f t="shared" si="3"/>
         <v>13:00</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B76" s="1">
-        <v>106</v>
-      </c>
-      <c r="C76" s="1">
-        <v>63</v>
-      </c>
-      <c r="F76" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="G76" t="str">
-        <f t="shared" si="2"/>
-        <v>13:00</v>
-      </c>
-      <c r="H76" t="str">
+    <row r="139" spans="1:7" hidden="1">
+      <c r="A139" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B139" s="1">
+        <v>128</v>
+      </c>
+      <c r="C139" s="1">
+        <v>85</v>
+      </c>
+      <c r="F139" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="G139" t="str">
         <f t="shared" si="3"/>
         <v>13:00</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
-      <c r="A77" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D77" s="1">
-        <v>6.62</v>
-      </c>
-      <c r="F77" s="1">
-        <v>0.95</v>
-      </c>
-      <c r="G77" t="str">
-        <f t="shared" si="2"/>
-        <v>14:00</v>
-      </c>
-      <c r="H77" t="str">
+    <row r="140" spans="1:7">
+      <c r="A140" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D140" s="1">
+        <v>6.09</v>
+      </c>
+      <c r="F140" s="1">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="G140" t="str">
         <f t="shared" si="3"/>
         <v>14:00</v>
       </c>
     </row>
-    <row r="78" spans="1:8">
-      <c r="A78" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B78" s="1">
-        <v>139</v>
-      </c>
-      <c r="C78" s="1">
-        <v>67</v>
-      </c>
-      <c r="F78" s="1">
+    <row r="141" spans="1:7" hidden="1">
+      <c r="A141" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B141" s="1">
+        <v>130</v>
+      </c>
+      <c r="C141" s="1">
+        <v>87</v>
+      </c>
+      <c r="F141" s="1">
         <v>0.89</v>
       </c>
-      <c r="G78" t="str">
-        <f t="shared" si="2"/>
-        <v>16:00</v>
-      </c>
-      <c r="H78" t="str">
+      <c r="G141" t="str">
         <f t="shared" si="3"/>
         <v>16:00</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
-      <c r="A79" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D79" s="1">
-        <v>4.3</v>
-      </c>
-      <c r="F79" s="1">
-        <v>0.22</v>
-      </c>
-      <c r="G79" t="str">
-        <f t="shared" si="2"/>
-        <v>18:00</v>
-      </c>
-      <c r="H79" t="str">
+    <row r="142" spans="1:7">
+      <c r="A142" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D142" s="1">
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="F142" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="G142" t="str">
         <f t="shared" si="3"/>
         <v>18:00</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
-      <c r="A80" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B80" s="1">
-        <v>93</v>
-      </c>
-      <c r="C80" s="1">
-        <v>61</v>
-      </c>
-      <c r="F80" s="1">
-        <v>0.77</v>
-      </c>
-      <c r="G80" t="str">
-        <f t="shared" ref="G80:G111" si="4">RIGHT(A80,5)</f>
-        <v>18:00</v>
-      </c>
-      <c r="H80" t="str">
+    <row r="143" spans="1:7" hidden="1">
+      <c r="A143" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B143" s="1">
+        <v>96</v>
+      </c>
+      <c r="C143" s="1">
+        <v>68</v>
+      </c>
+      <c r="F143" s="1">
+        <v>0.82</v>
+      </c>
+      <c r="G143" t="str">
         <f t="shared" si="3"/>
         <v>18:00</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
-      <c r="A81" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D81" s="1">
-        <v>6.18</v>
-      </c>
-      <c r="F81" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="G81" t="str">
+    <row r="144" spans="1:7">
+      <c r="A144" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D144" s="1">
+        <v>7.44</v>
+      </c>
+      <c r="F144" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="G144" t="str">
+        <f t="shared" ref="G144:G153" si="4">RIGHT(A144,5)</f>
+        <v>19:00</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" hidden="1">
+      <c r="A145" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B145" s="1">
+        <v>97</v>
+      </c>
+      <c r="C145" s="1">
+        <v>71</v>
+      </c>
+      <c r="F145" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="G145" t="str">
         <f t="shared" si="4"/>
         <v>19:00</v>
       </c>
-      <c r="H81" t="str">
-        <f t="shared" si="3"/>
-        <v>19:00</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
-      <c r="A82" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B82" s="1">
-        <v>95</v>
-      </c>
-      <c r="C82" s="1">
-        <v>81</v>
-      </c>
-      <c r="F82" s="1">
-        <v>0.95</v>
-      </c>
-      <c r="G82" t="str">
-        <f t="shared" si="4"/>
-        <v>19:00</v>
-      </c>
-      <c r="H82" t="str">
-        <f t="shared" si="3"/>
-        <v>19:00</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8">
-      <c r="A83" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D83" s="1">
-        <v>6.37</v>
-      </c>
-      <c r="F83" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="G83" t="str">
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D146" s="1">
+        <v>5.15</v>
+      </c>
+      <c r="F146" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="G146" t="str">
         <f t="shared" si="4"/>
         <v>20:00</v>
       </c>
-      <c r="H83" t="str">
-        <f t="shared" si="3"/>
-        <v>20:00</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
-      <c r="A84" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D84" s="1">
-        <v>4.6399999999999997</v>
-      </c>
-      <c r="F84" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="G84" t="str">
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D147" s="1">
+        <v>5.19</v>
+      </c>
+      <c r="F147" s="1">
+        <v>0.49</v>
+      </c>
+      <c r="G147" t="str">
         <f t="shared" si="4"/>
         <v>22:00</v>
       </c>
-      <c r="H84" t="str">
-        <f t="shared" si="3"/>
-        <v>22:00</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="A85" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B85" s="1">
-        <v>131</v>
-      </c>
-      <c r="C85" s="1">
-        <v>63</v>
-      </c>
-      <c r="F85" s="1">
-        <v>0.73</v>
-      </c>
-      <c r="G85" t="str">
+    </row>
+    <row r="148" spans="1:7" hidden="1">
+      <c r="A148" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B148" s="1">
+        <v>123</v>
+      </c>
+      <c r="C148" s="1">
+        <v>60</v>
+      </c>
+      <c r="F148" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="G148" t="str">
         <f t="shared" si="4"/>
         <v>22:00</v>
       </c>
-      <c r="H85" t="str">
-        <f t="shared" si="3"/>
-        <v>22:00</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="A86" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B86" s="1">
-        <v>107</v>
-      </c>
-      <c r="C86" s="1">
-        <v>74</v>
-      </c>
-      <c r="F86" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="G86" t="str">
+    </row>
+    <row r="149" spans="1:7" hidden="1">
+      <c r="A149" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B149" s="1">
+        <v>115</v>
+      </c>
+      <c r="C149" s="1">
+        <v>82</v>
+      </c>
+      <c r="F149" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="G149" t="str">
         <f t="shared" si="4"/>
         <v>00:00</v>
       </c>
-      <c r="H86" t="str">
-        <f t="shared" si="3"/>
-        <v>00:00</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
-      <c r="A87" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B87" s="1">
-        <v>107</v>
-      </c>
-      <c r="C87" s="1">
-        <v>85</v>
-      </c>
-      <c r="F87" s="1">
-        <v>0.92</v>
-      </c>
-      <c r="G87" t="str">
+    </row>
+    <row r="150" spans="1:7" hidden="1">
+      <c r="A150" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B150" s="1">
+        <v>112</v>
+      </c>
+      <c r="C150" s="1">
+        <v>89</v>
+      </c>
+      <c r="F150" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="G150" t="str">
         <f t="shared" si="4"/>
         <v>06:00</v>
       </c>
-      <c r="H87" t="str">
-        <f t="shared" si="3"/>
-        <v>06:00</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D88" s="1">
-        <v>4.12</v>
-      </c>
-      <c r="F88" s="1">
-        <v>0.78</v>
-      </c>
-      <c r="G88" t="str">
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D151" s="1">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="F151" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="G151" t="str">
         <f t="shared" si="4"/>
         <v>07:00</v>
       </c>
-      <c r="H88" t="str">
-        <f t="shared" si="3"/>
-        <v>07:00</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
-      <c r="A89" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E89" s="1">
+    </row>
+    <row r="152" spans="1:7" hidden="1">
+      <c r="A152" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E152" s="1">
         <v>0.17</v>
       </c>
-      <c r="F89" s="1">
+      <c r="F152" s="1">
         <v>0.66</v>
       </c>
-      <c r="G89" t="str">
+      <c r="G152" t="str">
         <f t="shared" si="4"/>
         <v>07:00</v>
       </c>
-      <c r="H89" t="str">
-        <f t="shared" si="3"/>
-        <v>07:00</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8">
-      <c r="A90" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B90" s="1">
-        <v>143</v>
-      </c>
-      <c r="C90" s="1">
-        <v>61</v>
-      </c>
-      <c r="F90" s="1">
-        <v>0.82</v>
-      </c>
-      <c r="G90" t="str">
+    </row>
+    <row r="153" spans="1:7" hidden="1">
+      <c r="A153" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B153" s="1">
+        <v>123</v>
+      </c>
+      <c r="C153" s="1">
+        <v>64</v>
+      </c>
+      <c r="F153" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="G153" t="str">
         <f t="shared" si="4"/>
         <v>07:30</v>
       </c>
-      <c r="H90" t="str">
-        <f t="shared" si="3"/>
-        <v>07:30</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8">
-      <c r="A91" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D91" s="1">
-        <v>6.89</v>
-      </c>
-      <c r="F91" s="1">
-        <v>0.39</v>
-      </c>
-      <c r="G91" t="str">
-        <f t="shared" si="4"/>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D154" s="1">
+        <v>6.36</v>
+      </c>
+      <c r="F154" s="1">
+        <v>0.84</v>
+      </c>
+      <c r="G154" t="str">
+        <f t="shared" ref="G154:G169" si="5">RIGHT(A154,5)</f>
         <v>08:00</v>
       </c>
-      <c r="H91" t="str">
-        <f t="shared" si="3"/>
-        <v>08:00</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8">
-      <c r="A92" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D92" s="1">
-        <v>5.07</v>
-      </c>
-      <c r="F92" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="G92" t="str">
-        <f t="shared" si="4"/>
-        <v>09:00</v>
-      </c>
-      <c r="H92" t="str">
-        <f t="shared" si="3"/>
-        <v>09:00</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8">
-      <c r="A93" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B93" s="1">
-        <v>99</v>
-      </c>
-      <c r="C93" s="1">
-        <v>89</v>
-      </c>
-      <c r="F93" s="1">
-        <v>0.27</v>
-      </c>
-      <c r="G93" t="str">
-        <f t="shared" si="4"/>
-        <v>10:00</v>
-      </c>
-      <c r="H93" t="str">
-        <f t="shared" si="3"/>
-        <v>10:00</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8">
-      <c r="A94" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D94" s="1">
-        <v>4.91</v>
-      </c>
-      <c r="F94" s="1">
-        <v>0.74</v>
-      </c>
-      <c r="G94" t="str">
-        <f t="shared" si="4"/>
-        <v>12:00</v>
-      </c>
-      <c r="H94" t="str">
-        <f t="shared" si="3"/>
-        <v>12:00</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8">
-      <c r="A95" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B95" s="1">
-        <v>125</v>
-      </c>
-      <c r="C95" s="1">
-        <v>73</v>
-      </c>
-      <c r="F95" s="1">
-        <v>0.92</v>
-      </c>
-      <c r="G95" t="str">
-        <f t="shared" si="4"/>
-        <v>12:00</v>
-      </c>
-      <c r="H95" t="str">
-        <f t="shared" si="3"/>
-        <v>12:00</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8">
-      <c r="A96" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D96" s="1">
-        <v>6.47</v>
-      </c>
-      <c r="F96" s="1">
-        <v>0.82</v>
-      </c>
-      <c r="G96" t="str">
-        <f t="shared" si="4"/>
-        <v>13:00</v>
-      </c>
-      <c r="H96" t="str">
-        <f t="shared" si="3"/>
-        <v>13:00</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
-      <c r="A97" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B97" s="1">
-        <v>120</v>
-      </c>
-      <c r="C97" s="1">
-        <v>75</v>
-      </c>
-      <c r="F97" s="1">
-        <v>0.21</v>
-      </c>
-      <c r="G97" t="str">
-        <f t="shared" si="4"/>
-        <v>13:00</v>
-      </c>
-      <c r="H97" t="str">
-        <f t="shared" si="3"/>
-        <v>13:00</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8">
-      <c r="A98" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D98" s="1">
-        <v>6.33</v>
-      </c>
-      <c r="F98" s="1">
-        <v>0.27</v>
-      </c>
-      <c r="G98" t="str">
-        <f t="shared" si="4"/>
-        <v>14:00</v>
-      </c>
-      <c r="H98" t="str">
-        <f t="shared" si="3"/>
-        <v>14:00</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
-      <c r="A99" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B99" s="1">
-        <v>104</v>
-      </c>
-      <c r="C99" s="1">
-        <v>67</v>
-      </c>
-      <c r="F99" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="G99" t="str">
-        <f t="shared" si="4"/>
-        <v>16:00</v>
-      </c>
-      <c r="H99" t="str">
-        <f t="shared" si="3"/>
-        <v>16:00</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8">
-      <c r="A100" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D100" s="1">
-        <v>4.3099999999999996</v>
-      </c>
-      <c r="F100" s="1">
-        <v>0.76</v>
-      </c>
-      <c r="G100" t="str">
-        <f t="shared" si="4"/>
-        <v>18:00</v>
-      </c>
-      <c r="H100" t="str">
-        <f t="shared" si="3"/>
-        <v>18:00</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8">
-      <c r="A101" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B101" s="1">
-        <v>103</v>
-      </c>
-      <c r="C101" s="1">
-        <v>82</v>
-      </c>
-      <c r="F101" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="G101" t="str">
-        <f t="shared" si="4"/>
-        <v>18:00</v>
-      </c>
-      <c r="H101" t="str">
-        <f t="shared" si="3"/>
-        <v>18:00</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8">
-      <c r="A102" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D102" s="1">
-        <v>6.94</v>
-      </c>
-      <c r="F102" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="G102" t="str">
-        <f t="shared" si="4"/>
-        <v>19:00</v>
-      </c>
-      <c r="H102" t="str">
-        <f t="shared" si="3"/>
-        <v>19:00</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8">
-      <c r="A103" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B103" s="1">
-        <v>129</v>
-      </c>
-      <c r="C103" s="1">
-        <v>80</v>
-      </c>
-      <c r="F103" s="1">
-        <v>0.38</v>
-      </c>
-      <c r="G103" t="str">
-        <f t="shared" si="4"/>
-        <v>19:00</v>
-      </c>
-      <c r="H103" t="str">
-        <f t="shared" si="3"/>
-        <v>19:00</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8">
-      <c r="A104" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D104" s="1">
-        <v>6.09</v>
-      </c>
-      <c r="F104" s="1">
-        <v>0.93</v>
-      </c>
-      <c r="G104" t="str">
-        <f t="shared" si="4"/>
-        <v>20:00</v>
-      </c>
-      <c r="H104" t="str">
-        <f t="shared" si="3"/>
-        <v>20:00</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8">
-      <c r="A105" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D105" s="1">
-        <v>4.38</v>
-      </c>
-      <c r="F105" s="1">
-        <v>0.76</v>
-      </c>
-      <c r="G105" t="str">
-        <f t="shared" si="4"/>
-        <v>22:00</v>
-      </c>
-      <c r="H105" t="str">
-        <f t="shared" si="3"/>
-        <v>22:00</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8">
-      <c r="A106" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B106" s="1">
-        <v>105</v>
-      </c>
-      <c r="C106" s="1">
-        <v>72</v>
-      </c>
-      <c r="F106" s="1">
-        <v>0.49</v>
-      </c>
-      <c r="G106" t="str">
-        <f t="shared" si="4"/>
-        <v>22:00</v>
-      </c>
-      <c r="H106" t="str">
-        <f t="shared" si="3"/>
-        <v>22:00</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8">
-      <c r="A107" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B107" s="1">
-        <v>100</v>
-      </c>
-      <c r="C107" s="1">
-        <v>78</v>
-      </c>
-      <c r="F107" s="1">
-        <v>0.88</v>
-      </c>
-      <c r="G107" t="str">
-        <f t="shared" si="4"/>
-        <v>00:00</v>
-      </c>
-      <c r="H107" t="str">
-        <f t="shared" si="3"/>
-        <v>00:00</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8">
-      <c r="A108" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B108" s="1">
-        <v>113</v>
-      </c>
-      <c r="C108" s="1">
-        <v>85</v>
-      </c>
-      <c r="F108" s="1">
-        <v>0.92</v>
-      </c>
-      <c r="G108" t="str">
-        <f t="shared" si="4"/>
-        <v>06:00</v>
-      </c>
-      <c r="H108" t="str">
-        <f t="shared" si="3"/>
-        <v>06:00</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8">
-      <c r="A109" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D109" s="1">
-        <v>4.97</v>
-      </c>
-      <c r="F109" s="1">
-        <v>0.56999999999999995</v>
-      </c>
-      <c r="G109" t="str">
-        <f t="shared" si="4"/>
-        <v>07:00</v>
-      </c>
-      <c r="H109" t="str">
-        <f t="shared" si="3"/>
-        <v>07:00</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8">
-      <c r="A110" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E110" s="1">
-        <v>0.17</v>
-      </c>
-      <c r="F110" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="G110" t="str">
-        <f t="shared" si="4"/>
-        <v>07:00</v>
-      </c>
-      <c r="H110" t="str">
-        <f t="shared" si="3"/>
-        <v>07:00</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8">
-      <c r="A111" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B111" s="1">
-        <v>124</v>
-      </c>
-      <c r="C111" s="1">
-        <v>87</v>
-      </c>
-      <c r="F111" s="1">
-        <v>0.36</v>
-      </c>
-      <c r="G111" t="str">
-        <f t="shared" si="4"/>
-        <v>07:30</v>
-      </c>
-      <c r="H111" t="str">
-        <f t="shared" si="3"/>
-        <v>07:30</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8">
-      <c r="A112" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D112" s="1">
-        <v>7.4</v>
-      </c>
-      <c r="F112" s="1">
-        <v>0.59</v>
-      </c>
-      <c r="G112" t="str">
-        <f t="shared" ref="G112:G143" si="5">RIGHT(A112,5)</f>
-        <v>08:00</v>
-      </c>
-      <c r="H112" t="str">
-        <f t="shared" si="3"/>
-        <v>08:00</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8">
-      <c r="A113" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D113" s="1">
-        <v>6.88</v>
-      </c>
-      <c r="F113" s="1">
-        <v>0.76</v>
-      </c>
-      <c r="G113" t="str">
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D155" s="1">
+        <v>5.01</v>
+      </c>
+      <c r="F155" s="1">
+        <v>0.24</v>
+      </c>
+      <c r="G155" t="str">
         <f t="shared" si="5"/>
         <v>09:00</v>
       </c>
-      <c r="H113" t="str">
-        <f t="shared" si="3"/>
-        <v>09:00</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8">
-      <c r="A114" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B114" s="1">
-        <v>134</v>
-      </c>
-      <c r="C114" s="1">
-        <v>68</v>
-      </c>
-      <c r="F114" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="G114" t="str">
+    </row>
+    <row r="156" spans="1:7" hidden="1">
+      <c r="A156" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B156" s="1">
+        <v>124</v>
+      </c>
+      <c r="C156" s="1">
+        <v>71</v>
+      </c>
+      <c r="F156" s="1">
+        <v>0.54</v>
+      </c>
+      <c r="G156" t="str">
         <f t="shared" si="5"/>
         <v>10:00</v>
       </c>
-      <c r="H114" t="str">
-        <f t="shared" si="3"/>
-        <v>10:00</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8">
-      <c r="A115" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D115" s="1">
-        <v>4.8899999999999997</v>
-      </c>
-      <c r="F115" s="1">
-        <v>0.76</v>
-      </c>
-      <c r="G115" t="str">
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D157" s="1">
+        <v>4.82</v>
+      </c>
+      <c r="F157" s="1">
+        <v>0.52</v>
+      </c>
+      <c r="G157" t="str">
         <f t="shared" si="5"/>
         <v>12:00</v>
       </c>
-      <c r="H115" t="str">
-        <f t="shared" si="3"/>
-        <v>12:00</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8">
-      <c r="A116" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B116" s="1">
-        <v>118</v>
-      </c>
-      <c r="C116" s="1">
-        <v>74</v>
-      </c>
-      <c r="F116" s="1">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="G116" t="str">
+    </row>
+    <row r="158" spans="1:7" hidden="1">
+      <c r="A158" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B158" s="1">
+        <v>129</v>
+      </c>
+      <c r="C158" s="1">
+        <v>81</v>
+      </c>
+      <c r="F158" s="1">
+        <v>0.93</v>
+      </c>
+      <c r="G158" t="str">
         <f t="shared" si="5"/>
         <v>12:00</v>
       </c>
-      <c r="H116" t="str">
-        <f t="shared" si="3"/>
-        <v>12:00</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8">
-      <c r="A117" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D117" s="1">
-        <v>7.08</v>
-      </c>
-      <c r="F117" s="1">
-        <v>0.48</v>
-      </c>
-      <c r="G117" t="str">
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D159" s="1">
+        <v>7.27</v>
+      </c>
+      <c r="F159" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="G159" t="str">
         <f t="shared" si="5"/>
         <v>13:00</v>
       </c>
-      <c r="H117" t="str">
-        <f t="shared" si="3"/>
-        <v>13:00</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8">
-      <c r="A118" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B118" s="1">
-        <v>134</v>
-      </c>
-      <c r="C118" s="1">
-        <v>60</v>
-      </c>
-      <c r="F118" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="G118" t="str">
+    </row>
+    <row r="160" spans="1:7" hidden="1">
+      <c r="A160" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B160" s="1">
+        <v>116</v>
+      </c>
+      <c r="C160" s="1">
+        <v>62</v>
+      </c>
+      <c r="F160" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="G160" t="str">
         <f t="shared" si="5"/>
         <v>13:00</v>
       </c>
-      <c r="H118" t="str">
-        <f t="shared" si="3"/>
-        <v>13:00</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8">
-      <c r="A119" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D119" s="1">
-        <v>6.84</v>
-      </c>
-      <c r="F119" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="G119" t="str">
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D161" s="1">
+        <v>6.46</v>
+      </c>
+      <c r="F161" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="G161" t="str">
         <f t="shared" si="5"/>
         <v>14:00</v>
       </c>
-      <c r="H119" t="str">
-        <f t="shared" si="3"/>
-        <v>14:00</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8">
-      <c r="A120" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B120" s="1">
-        <v>114</v>
-      </c>
-      <c r="C120" s="1">
-        <v>66</v>
-      </c>
-      <c r="F120" s="1">
-        <v>0.98</v>
-      </c>
-      <c r="G120" t="str">
+    </row>
+    <row r="162" spans="1:7" hidden="1">
+      <c r="A162" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B162" s="1">
+        <v>90</v>
+      </c>
+      <c r="C162" s="1">
+        <v>62</v>
+      </c>
+      <c r="F162" s="1">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="G162" t="str">
         <f t="shared" si="5"/>
         <v>16:00</v>
       </c>
-      <c r="H120" t="str">
-        <f t="shared" si="3"/>
-        <v>16:00</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8">
-      <c r="A121" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D121" s="1">
-        <v>4.09</v>
-      </c>
-      <c r="F121" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="G121" t="str">
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D163" s="1">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="F163" s="1">
+        <v>0.42</v>
+      </c>
+      <c r="G163" t="str">
         <f t="shared" si="5"/>
         <v>18:00</v>
       </c>
-      <c r="H121" t="str">
-        <f t="shared" si="3"/>
-        <v>18:00</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8">
-      <c r="A122" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B122" s="1">
-        <v>98</v>
-      </c>
-      <c r="C122" s="1">
-        <v>83</v>
-      </c>
-      <c r="F122" s="1">
-        <v>0.35</v>
-      </c>
-      <c r="G122" t="str">
+    </row>
+    <row r="164" spans="1:7" hidden="1">
+      <c r="A164" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B164" s="1">
+        <v>126</v>
+      </c>
+      <c r="C164" s="1">
+        <v>74</v>
+      </c>
+      <c r="F164" s="1">
+        <v>0.34</v>
+      </c>
+      <c r="G164" t="str">
         <f t="shared" si="5"/>
         <v>18:00</v>
       </c>
-      <c r="H122" t="str">
-        <f t="shared" si="3"/>
-        <v>18:00</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8">
-      <c r="A123" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D123" s="1">
-        <v>6.35</v>
-      </c>
-      <c r="F123" s="1">
-        <v>0.27</v>
-      </c>
-      <c r="G123" t="str">
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D165" s="1">
+        <v>6.13</v>
+      </c>
+      <c r="F165" s="1">
+        <v>0.54</v>
+      </c>
+      <c r="G165" t="str">
         <f t="shared" si="5"/>
         <v>19:00</v>
       </c>
-      <c r="H123" t="str">
-        <f t="shared" si="3"/>
-        <v>19:00</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8">
-      <c r="A124" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B124" s="1">
-        <v>90</v>
-      </c>
-      <c r="C124" s="1">
-        <v>71</v>
-      </c>
-      <c r="F124" s="1">
-        <v>0.94</v>
-      </c>
-      <c r="G124" t="str">
+    </row>
+    <row r="166" spans="1:7" hidden="1">
+      <c r="A166" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B166" s="1">
+        <v>103</v>
+      </c>
+      <c r="C166" s="1">
+        <v>62</v>
+      </c>
+      <c r="F166" s="1">
+        <v>0.69</v>
+      </c>
+      <c r="G166" t="str">
         <f t="shared" si="5"/>
         <v>19:00</v>
       </c>
-      <c r="H124" t="str">
-        <f t="shared" si="3"/>
-        <v>19:00</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8">
-      <c r="A125" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D125" s="1">
-        <v>5.09</v>
-      </c>
-      <c r="F125" s="1">
-        <v>0.8</v>
-      </c>
-      <c r="G125" t="str">
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D167" s="1">
+        <v>5.72</v>
+      </c>
+      <c r="F167" s="1">
+        <v>0.27</v>
+      </c>
+      <c r="G167" t="str">
         <f t="shared" si="5"/>
         <v>20:00</v>
       </c>
-      <c r="H125" t="str">
-        <f t="shared" si="3"/>
-        <v>20:00</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8">
-      <c r="A126" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D126" s="1">
-        <v>4.53</v>
-      </c>
-      <c r="F126" s="1">
-        <v>0.39</v>
-      </c>
-      <c r="G126" t="str">
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D168" s="1">
+        <v>4.32</v>
+      </c>
+      <c r="F168" s="1">
+        <v>0.46</v>
+      </c>
+      <c r="G168" t="str">
         <f t="shared" si="5"/>
         <v>22:00</v>
       </c>
-      <c r="H126" t="str">
-        <f t="shared" si="3"/>
-        <v>22:00</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8">
-      <c r="A127" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B127" s="1">
-        <v>97</v>
-      </c>
-      <c r="C127" s="1">
-        <v>83</v>
-      </c>
-      <c r="F127" s="1">
-        <v>0.37</v>
-      </c>
-      <c r="G127" t="str">
+    </row>
+    <row r="169" spans="1:7" hidden="1">
+      <c r="A169" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B169" s="1">
+        <v>90</v>
+      </c>
+      <c r="C169" s="1">
+        <v>64</v>
+      </c>
+      <c r="F169" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="G169" t="str">
         <f t="shared" si="5"/>
         <v>22:00</v>
       </c>
-      <c r="H127" t="str">
-        <f t="shared" si="3"/>
-        <v>22:00</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8">
-      <c r="A128" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B128" s="1">
-        <v>137</v>
-      </c>
-      <c r="C128" s="1">
-        <v>82</v>
-      </c>
-      <c r="F128" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="G128" t="str">
-        <f t="shared" si="5"/>
-        <v>00:00</v>
-      </c>
-      <c r="H128" t="str">
-        <f t="shared" si="3"/>
-        <v>00:00</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8">
-      <c r="A129" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B129" s="1">
-        <v>106</v>
-      </c>
-      <c r="C129" s="1">
-        <v>67</v>
-      </c>
-      <c r="F129" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="G129" t="str">
-        <f t="shared" si="5"/>
-        <v>06:00</v>
-      </c>
-      <c r="H129" t="str">
-        <f t="shared" si="3"/>
-        <v>06:00</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8">
-      <c r="A130" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D130" s="1">
-        <v>4.3899999999999997</v>
-      </c>
-      <c r="F130" s="1">
-        <v>0.78</v>
-      </c>
-      <c r="G130" t="str">
-        <f t="shared" si="5"/>
-        <v>07:00</v>
-      </c>
-      <c r="H130" t="str">
-        <f t="shared" si="3"/>
-        <v>07:00</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8">
-      <c r="A131" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E131" s="1">
-        <v>0.17</v>
-      </c>
-      <c r="F131" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="G131" t="str">
-        <f t="shared" si="5"/>
-        <v>07:00</v>
-      </c>
-      <c r="H131" t="str">
-        <f t="shared" ref="H131:H169" si="6">TEXT(A131,"HH:MM")</f>
-        <v>07:00</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8">
-      <c r="A132" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B132" s="1">
-        <v>134</v>
-      </c>
-      <c r="C132" s="1">
-        <v>62</v>
-      </c>
-      <c r="F132" s="1">
-        <v>0.2</v>
-      </c>
-      <c r="G132" t="str">
-        <f t="shared" si="5"/>
-        <v>07:30</v>
-      </c>
-      <c r="H132" t="str">
-        <f t="shared" si="6"/>
-        <v>07:30</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8">
-      <c r="A133" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D133" s="1">
-        <v>6.49</v>
-      </c>
-      <c r="F133" s="1">
-        <v>0.32</v>
-      </c>
-      <c r="G133" t="str">
-        <f t="shared" si="5"/>
-        <v>08:00</v>
-      </c>
-      <c r="H133" t="str">
-        <f t="shared" si="6"/>
-        <v>08:00</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8">
-      <c r="A134" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D134" s="1">
-        <v>6.66</v>
-      </c>
-      <c r="F134" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="G134" t="str">
-        <f t="shared" si="5"/>
-        <v>09:00</v>
-      </c>
-      <c r="H134" t="str">
-        <f t="shared" si="6"/>
-        <v>09:00</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8">
-      <c r="A135" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B135" s="1">
-        <v>122</v>
-      </c>
-      <c r="C135" s="1">
-        <v>86</v>
-      </c>
-      <c r="F135" s="1">
-        <v>0.26</v>
-      </c>
-      <c r="G135" t="str">
-        <f t="shared" si="5"/>
-        <v>10:00</v>
-      </c>
-      <c r="H135" t="str">
-        <f t="shared" si="6"/>
-        <v>10:00</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8">
-      <c r="A136" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D136" s="1">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="F136" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="G136" t="str">
-        <f t="shared" si="5"/>
-        <v>12:00</v>
-      </c>
-      <c r="H136" t="str">
-        <f t="shared" si="6"/>
-        <v>12:00</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8">
-      <c r="A137" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B137" s="1">
-        <v>94</v>
-      </c>
-      <c r="C137" s="1">
-        <v>69</v>
-      </c>
-      <c r="F137" s="1">
-        <v>0.91</v>
-      </c>
-      <c r="G137" t="str">
-        <f t="shared" si="5"/>
-        <v>12:00</v>
-      </c>
-      <c r="H137" t="str">
-        <f t="shared" si="6"/>
-        <v>12:00</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8">
-      <c r="A138" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D138" s="1">
-        <v>6.51</v>
-      </c>
-      <c r="F138" s="1">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="G138" t="str">
-        <f t="shared" si="5"/>
-        <v>13:00</v>
-      </c>
-      <c r="H138" t="str">
-        <f t="shared" si="6"/>
-        <v>13:00</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8">
-      <c r="A139" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B139" s="1">
-        <v>128</v>
-      </c>
-      <c r="C139" s="1">
-        <v>85</v>
-      </c>
-      <c r="F139" s="1">
-        <v>0.99</v>
-      </c>
-      <c r="G139" t="str">
-        <f t="shared" si="5"/>
-        <v>13:00</v>
-      </c>
-      <c r="H139" t="str">
-        <f t="shared" si="6"/>
-        <v>13:00</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8">
-      <c r="A140" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="D140" s="1">
-        <v>6.09</v>
-      </c>
-      <c r="F140" s="1">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="G140" t="str">
-        <f t="shared" si="5"/>
-        <v>14:00</v>
-      </c>
-      <c r="H140" t="str">
-        <f t="shared" si="6"/>
-        <v>14:00</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8">
-      <c r="A141" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B141" s="1">
-        <v>130</v>
-      </c>
-      <c r="C141" s="1">
-        <v>87</v>
-      </c>
-      <c r="F141" s="1">
-        <v>0.89</v>
-      </c>
-      <c r="G141" t="str">
-        <f t="shared" si="5"/>
-        <v>16:00</v>
-      </c>
-      <c r="H141" t="str">
-        <f t="shared" si="6"/>
-        <v>16:00</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8">
-      <c r="A142" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D142" s="1">
-        <v>4.1399999999999997</v>
-      </c>
-      <c r="F142" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="G142" t="str">
-        <f t="shared" si="5"/>
-        <v>18:00</v>
-      </c>
-      <c r="H142" t="str">
-        <f t="shared" si="6"/>
-        <v>18:00</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8">
-      <c r="A143" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B143" s="1">
-        <v>96</v>
-      </c>
-      <c r="C143" s="1">
-        <v>68</v>
-      </c>
-      <c r="F143" s="1">
-        <v>0.82</v>
-      </c>
-      <c r="G143" t="str">
-        <f t="shared" si="5"/>
-        <v>18:00</v>
-      </c>
-      <c r="H143" t="str">
-        <f t="shared" si="6"/>
-        <v>18:00</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8">
-      <c r="A144" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="D144" s="1">
-        <v>7.44</v>
-      </c>
-      <c r="F144" s="1">
-        <v>0.47</v>
-      </c>
-      <c r="G144" t="str">
-        <f t="shared" ref="G144:G153" si="7">RIGHT(A144,5)</f>
-        <v>19:00</v>
-      </c>
-      <c r="H144" t="str">
-        <f t="shared" si="6"/>
-        <v>19:00</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8">
-      <c r="A145" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B145" s="1">
-        <v>97</v>
-      </c>
-      <c r="C145" s="1">
-        <v>71</v>
-      </c>
-      <c r="F145" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="G145" t="str">
-        <f t="shared" si="7"/>
-        <v>19:00</v>
-      </c>
-      <c r="H145" t="str">
-        <f t="shared" si="6"/>
-        <v>19:00</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8">
-      <c r="A146" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D146" s="1">
-        <v>5.15</v>
-      </c>
-      <c r="F146" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="G146" t="str">
-        <f t="shared" si="7"/>
-        <v>20:00</v>
-      </c>
-      <c r="H146" t="str">
-        <f t="shared" si="6"/>
-        <v>20:00</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8">
-      <c r="A147" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D147" s="1">
-        <v>5.19</v>
-      </c>
-      <c r="F147" s="1">
-        <v>0.49</v>
-      </c>
-      <c r="G147" t="str">
-        <f t="shared" si="7"/>
-        <v>22:00</v>
-      </c>
-      <c r="H147" t="str">
-        <f t="shared" si="6"/>
-        <v>22:00</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8">
-      <c r="A148" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B148" s="1">
-        <v>123</v>
-      </c>
-      <c r="C148" s="1">
-        <v>60</v>
-      </c>
-      <c r="F148" s="1">
-        <v>0.24</v>
-      </c>
-      <c r="G148" t="str">
-        <f t="shared" si="7"/>
-        <v>22:00</v>
-      </c>
-      <c r="H148" t="str">
-        <f t="shared" si="6"/>
-        <v>22:00</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8">
-      <c r="A149" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B149" s="1">
-        <v>115</v>
-      </c>
-      <c r="C149" s="1">
-        <v>82</v>
-      </c>
-      <c r="F149" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="G149" t="str">
-        <f t="shared" si="7"/>
-        <v>00:00</v>
-      </c>
-      <c r="H149" t="str">
-        <f t="shared" si="6"/>
-        <v>00:00</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8">
-      <c r="A150" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="B150" s="1">
-        <v>112</v>
-      </c>
-      <c r="C150" s="1">
-        <v>89</v>
-      </c>
-      <c r="F150" s="1">
-        <v>0.46</v>
-      </c>
-      <c r="G150" t="str">
-        <f t="shared" si="7"/>
-        <v>06:00</v>
-      </c>
-      <c r="H150" t="str">
-        <f t="shared" si="6"/>
-        <v>06:00</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8">
-      <c r="A151" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D151" s="1">
-        <v>4.7699999999999996</v>
-      </c>
-      <c r="F151" s="1">
-        <v>0.88</v>
-      </c>
-      <c r="G151" t="str">
-        <f t="shared" si="7"/>
-        <v>07:00</v>
-      </c>
-      <c r="H151" t="str">
-        <f t="shared" si="6"/>
-        <v>07:00</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8">
-      <c r="A152" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E152" s="1">
-        <v>0.17</v>
-      </c>
-      <c r="F152" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="G152" t="str">
-        <f t="shared" si="7"/>
-        <v>07:00</v>
-      </c>
-      <c r="H152" t="str">
-        <f t="shared" si="6"/>
-        <v>07:00</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8">
-      <c r="A153" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B153" s="1">
-        <v>123</v>
-      </c>
-      <c r="C153" s="1">
-        <v>64</v>
-      </c>
-      <c r="F153" s="1">
-        <v>0.4</v>
-      </c>
-      <c r="G153" t="str">
-        <f t="shared" si="7"/>
-        <v>07:30</v>
-      </c>
-      <c r="H153" t="str">
-        <f t="shared" si="6"/>
-        <v>07:30</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8">
-      <c r="A154" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D154" s="1">
-        <v>6.36</v>
-      </c>
-      <c r="F154" s="1">
-        <v>0.84</v>
-      </c>
-      <c r="G154" t="str">
-        <f t="shared" ref="G154:G169" si="8">RIGHT(A154,5)</f>
-        <v>08:00</v>
-      </c>
-      <c r="H154" t="str">
-        <f t="shared" si="6"/>
-        <v>08:00</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8">
-      <c r="A155" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D155" s="1">
-        <v>5.01</v>
-      </c>
-      <c r="F155" s="1">
-        <v>0.24</v>
-      </c>
-      <c r="G155" t="str">
-        <f t="shared" si="8"/>
-        <v>09:00</v>
-      </c>
-      <c r="H155" t="str">
-        <f t="shared" si="6"/>
-        <v>09:00</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8">
-      <c r="A156" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B156" s="1">
-        <v>124</v>
-      </c>
-      <c r="C156" s="1">
-        <v>71</v>
-      </c>
-      <c r="F156" s="1">
-        <v>0.54</v>
-      </c>
-      <c r="G156" t="str">
-        <f t="shared" si="8"/>
-        <v>10:00</v>
-      </c>
-      <c r="H156" t="str">
-        <f t="shared" si="6"/>
-        <v>10:00</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8">
-      <c r="A157" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D157" s="1">
-        <v>4.82</v>
-      </c>
-      <c r="F157" s="1">
-        <v>0.52</v>
-      </c>
-      <c r="G157" t="str">
-        <f t="shared" si="8"/>
-        <v>12:00</v>
-      </c>
-      <c r="H157" t="str">
-        <f t="shared" si="6"/>
-        <v>12:00</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8">
-      <c r="A158" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B158" s="1">
-        <v>129</v>
-      </c>
-      <c r="C158" s="1">
-        <v>81</v>
-      </c>
-      <c r="F158" s="1">
-        <v>0.93</v>
-      </c>
-      <c r="G158" t="str">
-        <f t="shared" si="8"/>
-        <v>12:00</v>
-      </c>
-      <c r="H158" t="str">
-        <f t="shared" si="6"/>
-        <v>12:00</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8">
-      <c r="A159" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D159" s="1">
-        <v>7.27</v>
-      </c>
-      <c r="F159" s="1">
-        <v>0.85</v>
-      </c>
-      <c r="G159" t="str">
-        <f t="shared" si="8"/>
-        <v>13:00</v>
-      </c>
-      <c r="H159" t="str">
-        <f t="shared" si="6"/>
-        <v>13:00</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8">
-      <c r="A160" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B160" s="1">
-        <v>116</v>
-      </c>
-      <c r="C160" s="1">
-        <v>62</v>
-      </c>
-      <c r="F160" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="G160" t="str">
-        <f t="shared" si="8"/>
-        <v>13:00</v>
-      </c>
-      <c r="H160" t="str">
-        <f t="shared" si="6"/>
-        <v>13:00</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8">
-      <c r="A161" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D161" s="1">
-        <v>6.46</v>
-      </c>
-      <c r="F161" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="G161" t="str">
-        <f t="shared" si="8"/>
-        <v>14:00</v>
-      </c>
-      <c r="H161" t="str">
-        <f t="shared" si="6"/>
-        <v>14:00</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8">
-      <c r="A162" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B162" s="1">
-        <v>90</v>
-      </c>
-      <c r="C162" s="1">
-        <v>62</v>
-      </c>
-      <c r="F162" s="1">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="G162" t="str">
-        <f t="shared" si="8"/>
-        <v>16:00</v>
-      </c>
-      <c r="H162" t="str">
-        <f t="shared" si="6"/>
-        <v>16:00</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8">
-      <c r="A163" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D163" s="1">
-        <v>4.7699999999999996</v>
-      </c>
-      <c r="F163" s="1">
-        <v>0.42</v>
-      </c>
-      <c r="G163" t="str">
-        <f t="shared" si="8"/>
-        <v>18:00</v>
-      </c>
-      <c r="H163" t="str">
-        <f t="shared" si="6"/>
-        <v>18:00</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8">
-      <c r="A164" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B164" s="1">
-        <v>126</v>
-      </c>
-      <c r="C164" s="1">
-        <v>74</v>
-      </c>
-      <c r="F164" s="1">
-        <v>0.34</v>
-      </c>
-      <c r="G164" t="str">
-        <f t="shared" si="8"/>
-        <v>18:00</v>
-      </c>
-      <c r="H164" t="str">
-        <f t="shared" si="6"/>
-        <v>18:00</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8">
-      <c r="A165" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D165" s="1">
-        <v>6.13</v>
-      </c>
-      <c r="F165" s="1">
-        <v>0.54</v>
-      </c>
-      <c r="G165" t="str">
-        <f t="shared" si="8"/>
-        <v>19:00</v>
-      </c>
-      <c r="H165" t="str">
-        <f t="shared" si="6"/>
-        <v>19:00</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8">
-      <c r="A166" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B166" s="1">
-        <v>103</v>
-      </c>
-      <c r="C166" s="1">
-        <v>62</v>
-      </c>
-      <c r="F166" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="G166" t="str">
-        <f t="shared" si="8"/>
-        <v>19:00</v>
-      </c>
-      <c r="H166" t="str">
-        <f t="shared" si="6"/>
-        <v>19:00</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8">
-      <c r="A167" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D167" s="1">
-        <v>5.72</v>
-      </c>
-      <c r="F167" s="1">
-        <v>0.27</v>
-      </c>
-      <c r="G167" t="str">
-        <f t="shared" si="8"/>
-        <v>20:00</v>
-      </c>
-      <c r="H167" t="str">
-        <f t="shared" si="6"/>
-        <v>20:00</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8">
-      <c r="A168" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D168" s="1">
-        <v>4.32</v>
-      </c>
-      <c r="F168" s="1">
-        <v>0.46</v>
-      </c>
-      <c r="G168" t="str">
-        <f t="shared" si="8"/>
-        <v>22:00</v>
-      </c>
-      <c r="H168" t="str">
-        <f t="shared" si="6"/>
-        <v>22:00</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8">
-      <c r="A169" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B169" s="1">
-        <v>90</v>
-      </c>
-      <c r="C169" s="1">
-        <v>64</v>
-      </c>
-      <c r="F169" s="1">
-        <v>0.6</v>
-      </c>
-      <c r="G169" t="str">
-        <f t="shared" si="8"/>
-        <v>22:00</v>
-      </c>
-      <c r="H169" t="str">
-        <f t="shared" si="6"/>
-        <v>22:00</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:F169">
+    <filterColumn colId="3">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <sortState ref="A2:E161">
     <sortCondition ref="A2:A161"/>
   </sortState>

--- a/3.1.4答案/智能健康监测系统数据集.xlsx
+++ b/3.1.4答案/智能健康监测系统数据集.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="153">
   <si>
     <t>时间戳</t>
   </si>
@@ -495,6 +495,10 @@
   </si>
   <si>
     <t>响应时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HOUR</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -594,7 +598,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="hello" refreshedDate="45785.924756944398" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" recordCount="168">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:G169" sheet="Sheet1"/>
+    <worksheetSource ref="A1:F169" sheet="Sheet1"/>
   </cacheSource>
   <cacheFields count="7">
     <cacheField name="时间戳" numFmtId="0">
@@ -2625,7 +2629,7 @@
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" useAutoFormatting="1" createdVersion="5" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0">
-  <location ref="K9:N25" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <location ref="J9:M25" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
     <pivotField compact="0" showAll="0"/>
     <pivotField compact="0" showAll="0"/>
@@ -3270,16 +3274,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:N169"/>
+  <dimension ref="A1:M169"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.375" style="1" customWidth="1"/>
     <col min="2" max="6" width="8.75" style="1"/>
-    <col min="11" max="11" width="11.625"/>
-    <col min="12" max="14" width="20.125"/>
+    <col min="10" max="10" width="11.625"/>
+    <col min="11" max="13" width="20.125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3298,11 +3302,11 @@
       <c r="F1" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" hidden="1">
+      <c r="G1" s="7" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" hidden="1">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -3315,12 +3319,8 @@
       <c r="F2" s="1">
         <v>0.8</v>
       </c>
-      <c r="G2" t="str">
-        <f>RIGHT(A2,5)</f>
-        <v>00:00</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" hidden="1">
+    </row>
+    <row r="3" spans="1:13" hidden="1">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -3333,12 +3333,8 @@
       <c r="F3" s="1">
         <v>0.5</v>
       </c>
-      <c r="G3" t="str">
-        <f t="shared" ref="G3:G47" si="0">RIGHT(A3,5)</f>
-        <v>06:00</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -3349,11 +3345,11 @@
         <v>0.89</v>
       </c>
       <c r="G4" t="str">
-        <f t="shared" si="0"/>
-        <v>07:00</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" hidden="1">
+        <f>TEXT(A2,"HH:MM")</f>
+        <v>00:00</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" hidden="1">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -3363,12 +3359,8 @@
       <c r="F5" s="1">
         <v>0.69</v>
       </c>
-      <c r="G5" t="str">
-        <f t="shared" si="0"/>
-        <v>07:00</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" hidden="1">
+    </row>
+    <row r="6" spans="1:13" hidden="1">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -3381,42 +3373,38 @@
       <c r="F6" s="1">
         <v>0.56999999999999995</v>
       </c>
-      <c r="G6" t="str">
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1">
+        <v>7.71</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="G7" t="str">
+        <f t="shared" ref="G7:G8" si="0">TEXT(A5,"HH:MM")</f>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="1">
+        <v>6.46</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="G8" t="str">
         <f t="shared" si="0"/>
         <v>07:30</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="1">
-        <v>7.71</v>
-      </c>
-      <c r="F7" s="1">
-        <v>0.74</v>
-      </c>
-      <c r="G7" t="str">
-        <f t="shared" si="0"/>
-        <v>08:00</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="1">
-        <v>6.46</v>
-      </c>
-      <c r="F8" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="G8" t="str">
-        <f t="shared" si="0"/>
-        <v>09:00</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" hidden="1">
+    <row r="9" spans="1:13" hidden="1">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -3429,24 +3417,20 @@
       <c r="F9" s="1">
         <v>0.78</v>
       </c>
-      <c r="G9" t="str">
-        <f t="shared" si="0"/>
-        <v>10:00</v>
+      <c r="J9" t="s">
+        <v>5</v>
       </c>
       <c r="K9" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M9" t="s">
-        <v>14</v>
-      </c>
-      <c r="N9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:13">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -3457,17 +3441,17 @@
         <v>0.47</v>
       </c>
       <c r="G10" t="str">
-        <f t="shared" si="0"/>
-        <v>12:00</v>
-      </c>
-      <c r="K10" t="s">
+        <f>TEXT(A8,"HH:MM")</f>
+        <v>09:00</v>
+      </c>
+      <c r="J10" t="s">
         <v>17</v>
       </c>
-      <c r="N10">
+      <c r="M10">
         <v>79.875</v>
       </c>
     </row>
-    <row r="11" spans="1:14" hidden="1">
+    <row r="11" spans="1:13" hidden="1">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -3480,18 +3464,14 @@
       <c r="F11" s="1">
         <v>0.99</v>
       </c>
-      <c r="G11" t="str">
-        <f t="shared" si="0"/>
-        <v>12:00</v>
-      </c>
-      <c r="K11" t="s">
+      <c r="J11" t="s">
         <v>18</v>
       </c>
-      <c r="N11">
+      <c r="M11">
         <v>81.375</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:13">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -3502,20 +3482,20 @@
         <v>0.51</v>
       </c>
       <c r="G12" t="str">
-        <f t="shared" si="0"/>
-        <v>13:00</v>
-      </c>
-      <c r="K12" t="s">
+        <f>TEXT(A10,"HH:MM")</f>
+        <v>12:00</v>
+      </c>
+      <c r="J12" t="s">
         <v>20</v>
       </c>
+      <c r="K12">
+        <v>4.4824999999999999</v>
+      </c>
       <c r="L12">
-        <v>4.4824999999999999</v>
-      </c>
-      <c r="M12">
         <v>0.17</v>
       </c>
     </row>
-    <row r="13" spans="1:14" hidden="1">
+    <row r="13" spans="1:13" hidden="1">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -3528,18 +3508,14 @@
       <c r="F13" s="1">
         <v>0.99</v>
       </c>
-      <c r="G13" t="str">
-        <f t="shared" si="0"/>
-        <v>13:00</v>
-      </c>
-      <c r="K13" t="s">
+      <c r="J13" t="s">
         <v>21</v>
       </c>
-      <c r="N13">
+      <c r="M13">
         <v>72.375</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:13">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -3550,17 +3526,17 @@
         <v>0.41</v>
       </c>
       <c r="G14" t="str">
-        <f t="shared" si="0"/>
-        <v>14:00</v>
-      </c>
-      <c r="K14" t="s">
+        <f>TEXT(A12,"HH:MM")</f>
+        <v>13:00</v>
+      </c>
+      <c r="J14" t="s">
         <v>23</v>
       </c>
-      <c r="L14">
+      <c r="K14">
         <v>6.8949999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:14" hidden="1">
+    <row r="15" spans="1:13" hidden="1">
       <c r="A15" s="1" t="s">
         <v>24</v>
       </c>
@@ -3573,18 +3549,14 @@
       <c r="F15" s="1">
         <v>0.95</v>
       </c>
-      <c r="G15" t="str">
-        <f t="shared" si="0"/>
-        <v>16:00</v>
-      </c>
-      <c r="K15" t="s">
+      <c r="J15" t="s">
         <v>25</v>
       </c>
-      <c r="L15">
+      <c r="K15">
         <v>5.9312500000000004</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:13">
       <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
@@ -3595,17 +3567,17 @@
         <v>0.97</v>
       </c>
       <c r="G16" t="str">
-        <f t="shared" si="0"/>
-        <v>18:00</v>
-      </c>
-      <c r="K16" t="s">
+        <f>TEXT(A14,"HH:MM")</f>
+        <v>14:00</v>
+      </c>
+      <c r="J16" t="s">
         <v>27</v>
       </c>
-      <c r="N16">
+      <c r="M16">
         <v>72.5</v>
       </c>
     </row>
-    <row r="17" spans="1:14" hidden="1">
+    <row r="17" spans="1:13" hidden="1">
       <c r="A17" s="1" t="s">
         <v>26</v>
       </c>
@@ -3618,21 +3590,17 @@
       <c r="F17" s="1">
         <v>0.51</v>
       </c>
-      <c r="G17" t="str">
-        <f t="shared" si="0"/>
-        <v>18:00</v>
-      </c>
-      <c r="K17" t="s">
+      <c r="J17" t="s">
         <v>28</v>
       </c>
-      <c r="L17">
+      <c r="K17">
         <v>4.6387499999999999</v>
       </c>
-      <c r="N17">
+      <c r="M17">
         <v>70.25</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:13">
       <c r="A18" s="1" t="s">
         <v>29</v>
       </c>
@@ -3643,20 +3611,20 @@
         <v>0.54</v>
       </c>
       <c r="G18" t="str">
-        <f t="shared" si="0"/>
-        <v>19:00</v>
-      </c>
-      <c r="K18" t="s">
+        <f>TEXT(A16,"HH:MM")</f>
+        <v>18:00</v>
+      </c>
+      <c r="J18" t="s">
         <v>30</v>
       </c>
-      <c r="L18">
+      <c r="K18">
         <v>6.8125</v>
       </c>
-      <c r="N18">
+      <c r="M18">
         <v>72.5</v>
       </c>
     </row>
-    <row r="19" spans="1:14" hidden="1">
+    <row r="19" spans="1:13" hidden="1">
       <c r="A19" s="1" t="s">
         <v>29</v>
       </c>
@@ -3669,18 +3637,14 @@
       <c r="F19" s="1">
         <v>0.39</v>
       </c>
-      <c r="G19" t="str">
-        <f t="shared" si="0"/>
-        <v>19:00</v>
-      </c>
-      <c r="K19" t="s">
+      <c r="J19" t="s">
         <v>31</v>
       </c>
-      <c r="L19">
+      <c r="K19">
         <v>6.1987500000000004</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:13">
       <c r="A20" s="1" t="s">
         <v>32</v>
       </c>
@@ -3691,17 +3655,17 @@
         <v>0.66</v>
       </c>
       <c r="G20" t="str">
-        <f t="shared" si="0"/>
-        <v>20:00</v>
-      </c>
-      <c r="K20" t="s">
+        <f t="shared" ref="G20:G21" si="1">TEXT(A18,"HH:MM")</f>
+        <v>19:00</v>
+      </c>
+      <c r="J20" t="s">
         <v>33</v>
       </c>
-      <c r="N20">
+      <c r="M20">
         <v>73</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:13">
       <c r="A21" s="1" t="s">
         <v>34</v>
       </c>
@@ -3712,20 +3676,20 @@
         <v>0.66</v>
       </c>
       <c r="G21" t="str">
-        <f t="shared" si="0"/>
-        <v>22:00</v>
-      </c>
-      <c r="K21" t="s">
+        <f t="shared" si="1"/>
+        <v>19:00</v>
+      </c>
+      <c r="J21" t="s">
         <v>35</v>
       </c>
-      <c r="L21">
+      <c r="K21">
         <v>4.2712500000000002</v>
       </c>
-      <c r="N21">
+      <c r="M21">
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="1:14" hidden="1">
+    <row r="22" spans="1:13" hidden="1">
       <c r="A22" s="1" t="s">
         <v>34</v>
       </c>
@@ -3738,21 +3702,17 @@
       <c r="F22" s="1">
         <v>0.87</v>
       </c>
-      <c r="G22" t="str">
-        <f t="shared" si="0"/>
-        <v>22:00</v>
-      </c>
-      <c r="K22" t="s">
+      <c r="J22" t="s">
         <v>36</v>
       </c>
-      <c r="L22">
+      <c r="K22">
         <v>6.8087499999999999</v>
       </c>
-      <c r="N22">
+      <c r="M22">
         <v>74.375</v>
       </c>
     </row>
-    <row r="23" spans="1:14" hidden="1">
+    <row r="23" spans="1:13" hidden="1">
       <c r="A23" s="1" t="s">
         <v>37</v>
       </c>
@@ -3765,18 +3725,14 @@
       <c r="F23" s="1">
         <v>0.28000000000000003</v>
       </c>
-      <c r="G23" t="str">
-        <f t="shared" si="0"/>
-        <v>00:00</v>
-      </c>
-      <c r="K23" t="s">
+      <c r="J23" t="s">
         <v>38</v>
       </c>
-      <c r="L23">
+      <c r="K23">
         <v>5.8324999999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:14" hidden="1">
+    <row r="24" spans="1:13" hidden="1">
       <c r="A24" s="1" t="s">
         <v>39</v>
       </c>
@@ -3789,21 +3745,17 @@
       <c r="F24" s="1">
         <v>0.37</v>
       </c>
-      <c r="G24" t="str">
-        <f t="shared" si="0"/>
-        <v>06:00</v>
-      </c>
-      <c r="K24" t="s">
+      <c r="J24" t="s">
         <v>40</v>
       </c>
-      <c r="L24">
+      <c r="K24">
         <v>4.5887500000000001</v>
       </c>
-      <c r="N24">
+      <c r="M24">
         <v>72</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:13">
       <c r="A25" s="1" t="s">
         <v>41</v>
       </c>
@@ -3814,23 +3766,23 @@
         <v>0.8</v>
       </c>
       <c r="G25" t="str">
-        <f t="shared" si="0"/>
-        <v>07:00</v>
-      </c>
-      <c r="K25" t="s">
+        <f>TEXT(A23,"HH:MM")</f>
+        <v>00:00</v>
+      </c>
+      <c r="J25" t="s">
         <v>42</v>
       </c>
+      <c r="K25">
+        <v>5.6459999999999999</v>
+      </c>
       <c r="L25">
-        <v>5.6459999999999999</v>
+        <v>0.17</v>
       </c>
       <c r="M25">
-        <v>0.17</v>
-      </c>
-      <c r="N25">
         <v>74.525000000000006</v>
       </c>
     </row>
-    <row r="26" spans="1:14" hidden="1">
+    <row r="26" spans="1:13" hidden="1">
       <c r="A26" s="1" t="s">
         <v>41</v>
       </c>
@@ -3840,12 +3792,8 @@
       <c r="F26" s="1">
         <v>0.65</v>
       </c>
-      <c r="G26" t="str">
-        <f t="shared" si="0"/>
-        <v>07:00</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" hidden="1">
+    </row>
+    <row r="27" spans="1:13" hidden="1">
       <c r="A27" s="1" t="s">
         <v>43</v>
       </c>
@@ -3858,12 +3806,8 @@
       <c r="F27" s="1">
         <v>0.23</v>
       </c>
-      <c r="G27" t="str">
-        <f t="shared" si="0"/>
-        <v>07:30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" s="1" t="s">
         <v>44</v>
       </c>
@@ -3874,11 +3818,11 @@
         <v>0.86</v>
       </c>
       <c r="G28" t="str">
-        <f t="shared" si="0"/>
-        <v>08:00</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+        <f t="shared" ref="G28:G29" si="2">TEXT(A26,"HH:MM")</f>
+        <v>07:00</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" s="1" t="s">
         <v>45</v>
       </c>
@@ -3889,11 +3833,11 @@
         <v>0.51</v>
       </c>
       <c r="G29" t="str">
-        <f t="shared" si="0"/>
-        <v>09:00</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" hidden="1">
+        <f t="shared" si="2"/>
+        <v>07:30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" hidden="1">
       <c r="A30" s="1" t="s">
         <v>46</v>
       </c>
@@ -3906,12 +3850,8 @@
       <c r="F30" s="1">
         <v>0.56000000000000005</v>
       </c>
-      <c r="G30" t="str">
-        <f t="shared" si="0"/>
-        <v>10:00</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" s="1" t="s">
         <v>47</v>
       </c>
@@ -3922,11 +3862,11 @@
         <v>0.27</v>
       </c>
       <c r="G31" t="str">
-        <f t="shared" si="0"/>
-        <v>12:00</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" hidden="1">
+        <f>TEXT(A29,"HH:MM")</f>
+        <v>09:00</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" hidden="1">
       <c r="A32" s="1" t="s">
         <v>47</v>
       </c>
@@ -3938,10 +3878,6 @@
       </c>
       <c r="F32" s="1">
         <v>0.78</v>
-      </c>
-      <c r="G32" t="str">
-        <f t="shared" si="0"/>
-        <v>12:00</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -3955,8 +3891,8 @@
         <v>0.27</v>
       </c>
       <c r="G33" t="str">
-        <f t="shared" si="0"/>
-        <v>13:00</v>
+        <f>TEXT(A31,"HH:MM")</f>
+        <v>12:00</v>
       </c>
     </row>
     <row r="34" spans="1:7" hidden="1">
@@ -3972,10 +3908,6 @@
       <c r="F34" s="1">
         <v>0.8</v>
       </c>
-      <c r="G34" t="str">
-        <f t="shared" si="0"/>
-        <v>13:00</v>
-      </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="1" t="s">
@@ -3988,8 +3920,8 @@
         <v>0.37</v>
       </c>
       <c r="G35" t="str">
-        <f t="shared" si="0"/>
-        <v>14:00</v>
+        <f>TEXT(A33,"HH:MM")</f>
+        <v>13:00</v>
       </c>
     </row>
     <row r="36" spans="1:7" hidden="1">
@@ -4005,10 +3937,6 @@
       <c r="F36" s="1">
         <v>0.33</v>
       </c>
-      <c r="G36" t="str">
-        <f t="shared" si="0"/>
-        <v>16:00</v>
-      </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="1" t="s">
@@ -4021,8 +3949,8 @@
         <v>0.64</v>
       </c>
       <c r="G37" t="str">
-        <f t="shared" si="0"/>
-        <v>18:00</v>
+        <f>TEXT(A35,"HH:MM")</f>
+        <v>14:00</v>
       </c>
     </row>
     <row r="38" spans="1:7" hidden="1">
@@ -4038,10 +3966,6 @@
       <c r="F38" s="1">
         <v>0.85</v>
       </c>
-      <c r="G38" t="str">
-        <f t="shared" si="0"/>
-        <v>18:00</v>
-      </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="1" t="s">
@@ -4054,8 +3978,8 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="G39" t="str">
-        <f t="shared" si="0"/>
-        <v>19:00</v>
+        <f>TEXT(A37,"HH:MM")</f>
+        <v>18:00</v>
       </c>
     </row>
     <row r="40" spans="1:7" hidden="1">
@@ -4071,10 +3995,6 @@
       <c r="F40" s="1">
         <v>0.94</v>
       </c>
-      <c r="G40" t="str">
-        <f t="shared" si="0"/>
-        <v>19:00</v>
-      </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="1" t="s">
@@ -4087,8 +4007,8 @@
         <v>0.32</v>
       </c>
       <c r="G41" t="str">
-        <f t="shared" si="0"/>
-        <v>20:00</v>
+        <f t="shared" ref="G41:G42" si="3">TEXT(A39,"HH:MM")</f>
+        <v>19:00</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -4102,8 +4022,8 @@
         <v>0.67</v>
       </c>
       <c r="G42" t="str">
-        <f t="shared" si="0"/>
-        <v>22:00</v>
+        <f t="shared" si="3"/>
+        <v>19:00</v>
       </c>
     </row>
     <row r="43" spans="1:7" hidden="1">
@@ -4119,10 +4039,6 @@
       <c r="F43" s="1">
         <v>0.88</v>
       </c>
-      <c r="G43" t="str">
-        <f t="shared" si="0"/>
-        <v>22:00</v>
-      </c>
     </row>
     <row r="44" spans="1:7" hidden="1">
       <c r="A44" s="1" t="s">
@@ -4137,10 +4053,6 @@
       <c r="F44" s="1">
         <v>0.41</v>
       </c>
-      <c r="G44" t="str">
-        <f t="shared" si="0"/>
-        <v>00:00</v>
-      </c>
     </row>
     <row r="45" spans="1:7" hidden="1">
       <c r="A45" s="1" t="s">
@@ -4155,10 +4067,6 @@
       <c r="F45" s="1">
         <v>0.65</v>
       </c>
-      <c r="G45" t="str">
-        <f t="shared" si="0"/>
-        <v>06:00</v>
-      </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="1" t="s">
@@ -4171,8 +4079,8 @@
         <v>0.59</v>
       </c>
       <c r="G46" t="str">
-        <f t="shared" si="0"/>
-        <v>07:00</v>
+        <f>TEXT(A44,"HH:MM")</f>
+        <v>00:00</v>
       </c>
     </row>
     <row r="47" spans="1:7" hidden="1">
@@ -4185,10 +4093,6 @@
       <c r="F47" s="1">
         <v>0.68</v>
       </c>
-      <c r="G47" t="str">
-        <f t="shared" si="0"/>
-        <v>07:00</v>
-      </c>
     </row>
     <row r="48" spans="1:7" hidden="1">
       <c r="A48" s="1" t="s">
@@ -4203,10 +4107,6 @@
       <c r="F48" s="1">
         <v>0.6</v>
       </c>
-      <c r="G48" t="str">
-        <f t="shared" ref="G48:G79" si="1">RIGHT(A48,5)</f>
-        <v>07:30</v>
-      </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="1" t="s">
@@ -4219,8 +4119,8 @@
         <v>0.76</v>
       </c>
       <c r="G49" t="str">
-        <f t="shared" si="1"/>
-        <v>08:00</v>
+        <f t="shared" ref="G49:G50" si="4">TEXT(A47,"HH:MM")</f>
+        <v>07:00</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -4234,8 +4134,8 @@
         <v>0.46</v>
       </c>
       <c r="G50" t="str">
-        <f t="shared" si="1"/>
-        <v>09:00</v>
+        <f t="shared" si="4"/>
+        <v>07:30</v>
       </c>
     </row>
     <row r="51" spans="1:7" hidden="1">
@@ -4251,10 +4151,6 @@
       <c r="F51" s="1">
         <v>0.61</v>
       </c>
-      <c r="G51" t="str">
-        <f t="shared" si="1"/>
-        <v>10:00</v>
-      </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="1" t="s">
@@ -4267,8 +4163,8 @@
         <v>0.52</v>
       </c>
       <c r="G52" t="str">
-        <f t="shared" si="1"/>
-        <v>12:00</v>
+        <f>TEXT(A50,"HH:MM")</f>
+        <v>09:00</v>
       </c>
     </row>
     <row r="53" spans="1:7" hidden="1">
@@ -4284,10 +4180,6 @@
       <c r="F53" s="1">
         <v>0.53</v>
       </c>
-      <c r="G53" t="str">
-        <f t="shared" si="1"/>
-        <v>12:00</v>
-      </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="1" t="s">
@@ -4300,8 +4192,8 @@
         <v>0.79</v>
       </c>
       <c r="G54" t="str">
-        <f t="shared" si="1"/>
-        <v>13:00</v>
+        <f>TEXT(A52,"HH:MM")</f>
+        <v>12:00</v>
       </c>
     </row>
     <row r="55" spans="1:7" hidden="1">
@@ -4317,10 +4209,6 @@
       <c r="F55" s="1">
         <v>0.44</v>
       </c>
-      <c r="G55" t="str">
-        <f t="shared" si="1"/>
-        <v>13:00</v>
-      </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="1" t="s">
@@ -4333,8 +4221,8 @@
         <v>0.8</v>
       </c>
       <c r="G56" t="str">
-        <f t="shared" si="1"/>
-        <v>14:00</v>
+        <f>TEXT(A54,"HH:MM")</f>
+        <v>13:00</v>
       </c>
     </row>
     <row r="57" spans="1:7" hidden="1">
@@ -4350,10 +4238,6 @@
       <c r="F57" s="1">
         <v>0.45</v>
       </c>
-      <c r="G57" t="str">
-        <f t="shared" si="1"/>
-        <v>16:00</v>
-      </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="1" t="s">
@@ -4366,8 +4250,8 @@
         <v>0.62</v>
       </c>
       <c r="G58" t="str">
-        <f t="shared" si="1"/>
-        <v>18:00</v>
+        <f>TEXT(A56,"HH:MM")</f>
+        <v>14:00</v>
       </c>
     </row>
     <row r="59" spans="1:7" hidden="1">
@@ -4383,10 +4267,6 @@
       <c r="F59" s="1">
         <v>0.61</v>
       </c>
-      <c r="G59" t="str">
-        <f t="shared" si="1"/>
-        <v>18:00</v>
-      </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="1" t="s">
@@ -4399,8 +4279,8 @@
         <v>0.94</v>
       </c>
       <c r="G60" t="str">
-        <f t="shared" si="1"/>
-        <v>19:00</v>
+        <f>TEXT(A58,"HH:MM")</f>
+        <v>18:00</v>
       </c>
     </row>
     <row r="61" spans="1:7" hidden="1">
@@ -4416,10 +4296,6 @@
       <c r="F61" s="1">
         <v>0.65</v>
       </c>
-      <c r="G61" t="str">
-        <f t="shared" si="1"/>
-        <v>19:00</v>
-      </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="1" t="s">
@@ -4432,8 +4308,8 @@
         <v>0.76</v>
       </c>
       <c r="G62" t="str">
-        <f t="shared" si="1"/>
-        <v>20:00</v>
+        <f t="shared" ref="G62:G63" si="5">TEXT(A60,"HH:MM")</f>
+        <v>19:00</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -4447,8 +4323,8 @@
         <v>0.51</v>
       </c>
       <c r="G63" t="str">
-        <f t="shared" si="1"/>
-        <v>22:00</v>
+        <f t="shared" si="5"/>
+        <v>19:00</v>
       </c>
     </row>
     <row r="64" spans="1:7" hidden="1">
@@ -4464,10 +4340,6 @@
       <c r="F64" s="1">
         <v>0.4</v>
       </c>
-      <c r="G64" t="str">
-        <f t="shared" si="1"/>
-        <v>22:00</v>
-      </c>
     </row>
     <row r="65" spans="1:7" hidden="1">
       <c r="A65" s="1" t="s">
@@ -4482,10 +4354,6 @@
       <c r="F65" s="1">
         <v>0.62</v>
       </c>
-      <c r="G65" t="str">
-        <f t="shared" si="1"/>
-        <v>00:00</v>
-      </c>
     </row>
     <row r="66" spans="1:7" hidden="1">
       <c r="A66" s="1" t="s">
@@ -4500,10 +4368,6 @@
       <c r="F66" s="1">
         <v>0.53</v>
       </c>
-      <c r="G66" t="str">
-        <f t="shared" si="1"/>
-        <v>06:00</v>
-      </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="1" t="s">
@@ -4516,8 +4380,8 @@
         <v>0.42</v>
       </c>
       <c r="G67" t="str">
-        <f t="shared" si="1"/>
-        <v>07:00</v>
+        <f>TEXT(A65,"HH:MM")</f>
+        <v>00:00</v>
       </c>
     </row>
     <row r="68" spans="1:7" hidden="1">
@@ -4530,10 +4394,6 @@
       <c r="F68" s="1">
         <v>0.64</v>
       </c>
-      <c r="G68" t="str">
-        <f t="shared" si="1"/>
-        <v>07:00</v>
-      </c>
     </row>
     <row r="69" spans="1:7" hidden="1">
       <c r="A69" s="1" t="s">
@@ -4548,10 +4408,6 @@
       <c r="F69" s="1">
         <v>0.62</v>
       </c>
-      <c r="G69" t="str">
-        <f t="shared" si="1"/>
-        <v>07:30</v>
-      </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" s="1" t="s">
@@ -4564,8 +4420,8 @@
         <v>0.48</v>
       </c>
       <c r="G70" t="str">
-        <f t="shared" si="1"/>
-        <v>08:00</v>
+        <f t="shared" ref="G70:G71" si="6">TEXT(A68,"HH:MM")</f>
+        <v>07:00</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -4579,8 +4435,8 @@
         <v>0.98</v>
       </c>
       <c r="G71" t="str">
-        <f t="shared" si="1"/>
-        <v>09:00</v>
+        <f t="shared" si="6"/>
+        <v>07:30</v>
       </c>
     </row>
     <row r="72" spans="1:7" hidden="1">
@@ -4596,10 +4452,6 @@
       <c r="F72" s="1">
         <v>0.64</v>
       </c>
-      <c r="G72" t="str">
-        <f t="shared" si="1"/>
-        <v>10:00</v>
-      </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="1" t="s">
@@ -4612,8 +4464,8 @@
         <v>0.63</v>
       </c>
       <c r="G73" t="str">
-        <f t="shared" si="1"/>
-        <v>12:00</v>
+        <f>TEXT(A71,"HH:MM")</f>
+        <v>09:00</v>
       </c>
     </row>
     <row r="74" spans="1:7" hidden="1">
@@ -4629,10 +4481,6 @@
       <c r="F74" s="1">
         <v>0.49</v>
       </c>
-      <c r="G74" t="str">
-        <f t="shared" si="1"/>
-        <v>12:00</v>
-      </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="1" t="s">
@@ -4645,8 +4493,8 @@
         <v>0.69</v>
       </c>
       <c r="G75" t="str">
-        <f t="shared" si="1"/>
-        <v>13:00</v>
+        <f>TEXT(A73,"HH:MM")</f>
+        <v>12:00</v>
       </c>
     </row>
     <row r="76" spans="1:7" hidden="1">
@@ -4662,10 +4510,6 @@
       <c r="F76" s="1">
         <v>0.71</v>
       </c>
-      <c r="G76" t="str">
-        <f t="shared" si="1"/>
-        <v>13:00</v>
-      </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="1" t="s">
@@ -4678,8 +4522,8 @@
         <v>0.95</v>
       </c>
       <c r="G77" t="str">
-        <f t="shared" si="1"/>
-        <v>14:00</v>
+        <f>TEXT(A75,"HH:MM")</f>
+        <v>13:00</v>
       </c>
     </row>
     <row r="78" spans="1:7" hidden="1">
@@ -4695,10 +4539,6 @@
       <c r="F78" s="1">
         <v>0.89</v>
       </c>
-      <c r="G78" t="str">
-        <f t="shared" si="1"/>
-        <v>16:00</v>
-      </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="1" t="s">
@@ -4711,8 +4551,8 @@
         <v>0.22</v>
       </c>
       <c r="G79" t="str">
-        <f t="shared" si="1"/>
-        <v>18:00</v>
+        <f>TEXT(A77,"HH:MM")</f>
+        <v>14:00</v>
       </c>
     </row>
     <row r="80" spans="1:7" hidden="1">
@@ -4728,10 +4568,6 @@
       <c r="F80" s="1">
         <v>0.77</v>
       </c>
-      <c r="G80" t="str">
-        <f t="shared" ref="G80:G111" si="2">RIGHT(A80,5)</f>
-        <v>18:00</v>
-      </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="1" t="s">
@@ -4744,8 +4580,8 @@
         <v>0.8</v>
       </c>
       <c r="G81" t="str">
-        <f t="shared" si="2"/>
-        <v>19:00</v>
+        <f>TEXT(A79,"HH:MM")</f>
+        <v>18:00</v>
       </c>
     </row>
     <row r="82" spans="1:7" hidden="1">
@@ -4761,10 +4597,6 @@
       <c r="F82" s="1">
         <v>0.95</v>
       </c>
-      <c r="G82" t="str">
-        <f t="shared" si="2"/>
-        <v>19:00</v>
-      </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="1" t="s">
@@ -4777,8 +4609,8 @@
         <v>0.23</v>
       </c>
       <c r="G83" t="str">
-        <f t="shared" si="2"/>
-        <v>20:00</v>
+        <f t="shared" ref="G83:G84" si="7">TEXT(A81,"HH:MM")</f>
+        <v>19:00</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -4792,8 +4624,8 @@
         <v>0.63</v>
       </c>
       <c r="G84" t="str">
-        <f t="shared" si="2"/>
-        <v>22:00</v>
+        <f t="shared" si="7"/>
+        <v>19:00</v>
       </c>
     </row>
     <row r="85" spans="1:7" hidden="1">
@@ -4809,10 +4641,6 @@
       <c r="F85" s="1">
         <v>0.73</v>
       </c>
-      <c r="G85" t="str">
-        <f t="shared" si="2"/>
-        <v>22:00</v>
-      </c>
     </row>
     <row r="86" spans="1:7" hidden="1">
       <c r="A86" s="1" t="s">
@@ -4827,10 +4655,6 @@
       <c r="F86" s="1">
         <v>0.63</v>
       </c>
-      <c r="G86" t="str">
-        <f t="shared" si="2"/>
-        <v>00:00</v>
-      </c>
     </row>
     <row r="87" spans="1:7" hidden="1">
       <c r="A87" s="1" t="s">
@@ -4845,10 +4669,6 @@
       <c r="F87" s="1">
         <v>0.92</v>
       </c>
-      <c r="G87" t="str">
-        <f t="shared" si="2"/>
-        <v>06:00</v>
-      </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="1" t="s">
@@ -4861,8 +4681,8 @@
         <v>0.78</v>
       </c>
       <c r="G88" t="str">
-        <f t="shared" si="2"/>
-        <v>07:00</v>
+        <f>TEXT(A86,"HH:MM")</f>
+        <v>00:00</v>
       </c>
     </row>
     <row r="89" spans="1:7" hidden="1">
@@ -4875,10 +4695,6 @@
       <c r="F89" s="1">
         <v>0.66</v>
       </c>
-      <c r="G89" t="str">
-        <f t="shared" si="2"/>
-        <v>07:00</v>
-      </c>
     </row>
     <row r="90" spans="1:7" hidden="1">
       <c r="A90" s="1" t="s">
@@ -4893,10 +4709,6 @@
       <c r="F90" s="1">
         <v>0.82</v>
       </c>
-      <c r="G90" t="str">
-        <f t="shared" si="2"/>
-        <v>07:30</v>
-      </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="1" t="s">
@@ -4909,8 +4721,8 @@
         <v>0.39</v>
       </c>
       <c r="G91" t="str">
-        <f t="shared" si="2"/>
-        <v>08:00</v>
+        <f t="shared" ref="G91:G92" si="8">TEXT(A89,"HH:MM")</f>
+        <v>07:00</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -4924,8 +4736,8 @@
         <v>0.69</v>
       </c>
       <c r="G92" t="str">
-        <f t="shared" si="2"/>
-        <v>09:00</v>
+        <f t="shared" si="8"/>
+        <v>07:30</v>
       </c>
     </row>
     <row r="93" spans="1:7" hidden="1">
@@ -4941,10 +4753,6 @@
       <c r="F93" s="1">
         <v>0.27</v>
       </c>
-      <c r="G93" t="str">
-        <f t="shared" si="2"/>
-        <v>10:00</v>
-      </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="1" t="s">
@@ -4957,8 +4765,8 @@
         <v>0.74</v>
       </c>
       <c r="G94" t="str">
-        <f t="shared" si="2"/>
-        <v>12:00</v>
+        <f>TEXT(A92,"HH:MM")</f>
+        <v>09:00</v>
       </c>
     </row>
     <row r="95" spans="1:7" hidden="1">
@@ -4974,10 +4782,6 @@
       <c r="F95" s="1">
         <v>0.92</v>
       </c>
-      <c r="G95" t="str">
-        <f t="shared" si="2"/>
-        <v>12:00</v>
-      </c>
     </row>
     <row r="96" spans="1:7">
       <c r="A96" s="1" t="s">
@@ -4990,8 +4794,8 @@
         <v>0.82</v>
       </c>
       <c r="G96" t="str">
-        <f t="shared" si="2"/>
-        <v>13:00</v>
+        <f>TEXT(A94,"HH:MM")</f>
+        <v>12:00</v>
       </c>
     </row>
     <row r="97" spans="1:7" hidden="1">
@@ -5007,10 +4811,6 @@
       <c r="F97" s="1">
         <v>0.21</v>
       </c>
-      <c r="G97" t="str">
-        <f t="shared" si="2"/>
-        <v>13:00</v>
-      </c>
     </row>
     <row r="98" spans="1:7">
       <c r="A98" s="1" t="s">
@@ -5023,8 +4823,8 @@
         <v>0.27</v>
       </c>
       <c r="G98" t="str">
-        <f t="shared" si="2"/>
-        <v>14:00</v>
+        <f>TEXT(A96,"HH:MM")</f>
+        <v>13:00</v>
       </c>
     </row>
     <row r="99" spans="1:7" hidden="1">
@@ -5040,10 +4840,6 @@
       <c r="F99" s="1">
         <v>0.2</v>
       </c>
-      <c r="G99" t="str">
-        <f t="shared" si="2"/>
-        <v>16:00</v>
-      </c>
     </row>
     <row r="100" spans="1:7">
       <c r="A100" s="1" t="s">
@@ -5056,8 +4852,8 @@
         <v>0.76</v>
       </c>
       <c r="G100" t="str">
-        <f t="shared" si="2"/>
-        <v>18:00</v>
+        <f>TEXT(A98,"HH:MM")</f>
+        <v>14:00</v>
       </c>
     </row>
     <row r="101" spans="1:7" hidden="1">
@@ -5073,10 +4869,6 @@
       <c r="F101" s="1">
         <v>0.64</v>
       </c>
-      <c r="G101" t="str">
-        <f t="shared" si="2"/>
-        <v>18:00</v>
-      </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="1" t="s">
@@ -5089,8 +4881,8 @@
         <v>0.71</v>
       </c>
       <c r="G102" t="str">
-        <f t="shared" si="2"/>
-        <v>19:00</v>
+        <f>TEXT(A100,"HH:MM")</f>
+        <v>18:00</v>
       </c>
     </row>
     <row r="103" spans="1:7" hidden="1">
@@ -5106,10 +4898,6 @@
       <c r="F103" s="1">
         <v>0.38</v>
       </c>
-      <c r="G103" t="str">
-        <f t="shared" si="2"/>
-        <v>19:00</v>
-      </c>
     </row>
     <row r="104" spans="1:7">
       <c r="A104" s="1" t="s">
@@ -5122,8 +4910,8 @@
         <v>0.93</v>
       </c>
       <c r="G104" t="str">
-        <f t="shared" si="2"/>
-        <v>20:00</v>
+        <f t="shared" ref="G104:G105" si="9">TEXT(A102,"HH:MM")</f>
+        <v>19:00</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -5137,8 +4925,8 @@
         <v>0.76</v>
       </c>
       <c r="G105" t="str">
-        <f t="shared" si="2"/>
-        <v>22:00</v>
+        <f t="shared" si="9"/>
+        <v>19:00</v>
       </c>
     </row>
     <row r="106" spans="1:7" hidden="1">
@@ -5154,10 +4942,6 @@
       <c r="F106" s="1">
         <v>0.49</v>
       </c>
-      <c r="G106" t="str">
-        <f t="shared" si="2"/>
-        <v>22:00</v>
-      </c>
     </row>
     <row r="107" spans="1:7" hidden="1">
       <c r="A107" s="1" t="s">
@@ -5172,10 +4956,6 @@
       <c r="F107" s="1">
         <v>0.88</v>
       </c>
-      <c r="G107" t="str">
-        <f t="shared" si="2"/>
-        <v>00:00</v>
-      </c>
     </row>
     <row r="108" spans="1:7" hidden="1">
       <c r="A108" s="1" t="s">
@@ -5190,10 +4970,6 @@
       <c r="F108" s="1">
         <v>0.92</v>
       </c>
-      <c r="G108" t="str">
-        <f t="shared" si="2"/>
-        <v>06:00</v>
-      </c>
     </row>
     <row r="109" spans="1:7">
       <c r="A109" s="1" t="s">
@@ -5206,8 +4982,8 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="G109" t="str">
-        <f t="shared" si="2"/>
-        <v>07:00</v>
+        <f>TEXT(A107,"HH:MM")</f>
+        <v>00:00</v>
       </c>
     </row>
     <row r="110" spans="1:7" hidden="1">
@@ -5220,10 +4996,6 @@
       <c r="F110" s="1">
         <v>0.63</v>
       </c>
-      <c r="G110" t="str">
-        <f t="shared" si="2"/>
-        <v>07:00</v>
-      </c>
     </row>
     <row r="111" spans="1:7" hidden="1">
       <c r="A111" s="1" t="s">
@@ -5238,10 +5010,6 @@
       <c r="F111" s="1">
         <v>0.36</v>
       </c>
-      <c r="G111" t="str">
-        <f t="shared" si="2"/>
-        <v>07:30</v>
-      </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="1" t="s">
@@ -5254,8 +5022,8 @@
         <v>0.59</v>
       </c>
       <c r="G112" t="str">
-        <f t="shared" ref="G112:G143" si="3">RIGHT(A112,5)</f>
-        <v>08:00</v>
+        <f t="shared" ref="G112:G113" si="10">TEXT(A110,"HH:MM")</f>
+        <v>07:00</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -5269,8 +5037,8 @@
         <v>0.76</v>
       </c>
       <c r="G113" t="str">
-        <f t="shared" si="3"/>
-        <v>09:00</v>
+        <f t="shared" si="10"/>
+        <v>07:30</v>
       </c>
     </row>
     <row r="114" spans="1:7" hidden="1">
@@ -5286,10 +5054,6 @@
       <c r="F114" s="1">
         <v>0.23</v>
       </c>
-      <c r="G114" t="str">
-        <f t="shared" si="3"/>
-        <v>10:00</v>
-      </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="1" t="s">
@@ -5302,8 +5066,8 @@
         <v>0.76</v>
       </c>
       <c r="G115" t="str">
-        <f t="shared" si="3"/>
-        <v>12:00</v>
+        <f>TEXT(A113,"HH:MM")</f>
+        <v>09:00</v>
       </c>
     </row>
     <row r="116" spans="1:7" hidden="1">
@@ -5319,10 +5083,6 @@
       <c r="F116" s="1">
         <v>0.57999999999999996</v>
       </c>
-      <c r="G116" t="str">
-        <f t="shared" si="3"/>
-        <v>12:00</v>
-      </c>
     </row>
     <row r="117" spans="1:7">
       <c r="A117" s="1" t="s">
@@ -5335,8 +5095,8 @@
         <v>0.48</v>
       </c>
       <c r="G117" t="str">
-        <f t="shared" si="3"/>
-        <v>13:00</v>
+        <f>TEXT(A115,"HH:MM")</f>
+        <v>12:00</v>
       </c>
     </row>
     <row r="118" spans="1:7" hidden="1">
@@ -5352,10 +5112,6 @@
       <c r="F118" s="1">
         <v>0.8</v>
       </c>
-      <c r="G118" t="str">
-        <f t="shared" si="3"/>
-        <v>13:00</v>
-      </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="1" t="s">
@@ -5368,8 +5124,8 @@
         <v>0.63</v>
       </c>
       <c r="G119" t="str">
-        <f t="shared" si="3"/>
-        <v>14:00</v>
+        <f>TEXT(A117,"HH:MM")</f>
+        <v>13:00</v>
       </c>
     </row>
     <row r="120" spans="1:7" hidden="1">
@@ -5385,10 +5141,6 @@
       <c r="F120" s="1">
         <v>0.98</v>
       </c>
-      <c r="G120" t="str">
-        <f t="shared" si="3"/>
-        <v>16:00</v>
-      </c>
     </row>
     <row r="121" spans="1:7">
       <c r="A121" s="1" t="s">
@@ -5401,8 +5153,8 @@
         <v>0.3</v>
       </c>
       <c r="G121" t="str">
-        <f t="shared" si="3"/>
-        <v>18:00</v>
+        <f>TEXT(A119,"HH:MM")</f>
+        <v>14:00</v>
       </c>
     </row>
     <row r="122" spans="1:7" hidden="1">
@@ -5418,10 +5170,6 @@
       <c r="F122" s="1">
         <v>0.35</v>
       </c>
-      <c r="G122" t="str">
-        <f t="shared" si="3"/>
-        <v>18:00</v>
-      </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="1" t="s">
@@ -5434,8 +5182,8 @@
         <v>0.27</v>
       </c>
       <c r="G123" t="str">
-        <f t="shared" si="3"/>
-        <v>19:00</v>
+        <f>TEXT(A121,"HH:MM")</f>
+        <v>18:00</v>
       </c>
     </row>
     <row r="124" spans="1:7" hidden="1">
@@ -5451,10 +5199,6 @@
       <c r="F124" s="1">
         <v>0.94</v>
       </c>
-      <c r="G124" t="str">
-        <f t="shared" si="3"/>
-        <v>19:00</v>
-      </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="1" t="s">
@@ -5467,8 +5211,8 @@
         <v>0.8</v>
       </c>
       <c r="G125" t="str">
-        <f t="shared" si="3"/>
-        <v>20:00</v>
+        <f t="shared" ref="G125:G126" si="11">TEXT(A123,"HH:MM")</f>
+        <v>19:00</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -5482,8 +5226,8 @@
         <v>0.39</v>
       </c>
       <c r="G126" t="str">
-        <f t="shared" si="3"/>
-        <v>22:00</v>
+        <f t="shared" si="11"/>
+        <v>19:00</v>
       </c>
     </row>
     <row r="127" spans="1:7" hidden="1">
@@ -5499,10 +5243,6 @@
       <c r="F127" s="1">
         <v>0.37</v>
       </c>
-      <c r="G127" t="str">
-        <f t="shared" si="3"/>
-        <v>22:00</v>
-      </c>
     </row>
     <row r="128" spans="1:7" hidden="1">
       <c r="A128" s="1" t="s">
@@ -5517,10 +5257,6 @@
       <c r="F128" s="1">
         <v>0.63</v>
       </c>
-      <c r="G128" t="str">
-        <f t="shared" si="3"/>
-        <v>00:00</v>
-      </c>
     </row>
     <row r="129" spans="1:7" hidden="1">
       <c r="A129" s="1" t="s">
@@ -5535,10 +5271,6 @@
       <c r="F129" s="1">
         <v>0.69</v>
       </c>
-      <c r="G129" t="str">
-        <f t="shared" si="3"/>
-        <v>06:00</v>
-      </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="1" t="s">
@@ -5551,8 +5283,8 @@
         <v>0.78</v>
       </c>
       <c r="G130" t="str">
-        <f t="shared" si="3"/>
-        <v>07:00</v>
+        <f>TEXT(A128,"HH:MM")</f>
+        <v>00:00</v>
       </c>
     </row>
     <row r="131" spans="1:7" hidden="1">
@@ -5565,10 +5297,6 @@
       <c r="F131" s="1">
         <v>0.68</v>
       </c>
-      <c r="G131" t="str">
-        <f t="shared" si="3"/>
-        <v>07:00</v>
-      </c>
     </row>
     <row r="132" spans="1:7" hidden="1">
       <c r="A132" s="1" t="s">
@@ -5583,10 +5311,6 @@
       <c r="F132" s="1">
         <v>0.2</v>
       </c>
-      <c r="G132" t="str">
-        <f t="shared" si="3"/>
-        <v>07:30</v>
-      </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="1" t="s">
@@ -5599,8 +5323,8 @@
         <v>0.32</v>
       </c>
       <c r="G133" t="str">
-        <f t="shared" si="3"/>
-        <v>08:00</v>
+        <f t="shared" ref="G133:G134" si="12">TEXT(A131,"HH:MM")</f>
+        <v>07:00</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -5614,8 +5338,8 @@
         <v>0.63</v>
       </c>
       <c r="G134" t="str">
-        <f t="shared" si="3"/>
-        <v>09:00</v>
+        <f t="shared" si="12"/>
+        <v>07:30</v>
       </c>
     </row>
     <row r="135" spans="1:7" hidden="1">
@@ -5631,10 +5355,6 @@
       <c r="F135" s="1">
         <v>0.26</v>
       </c>
-      <c r="G135" t="str">
-        <f t="shared" si="3"/>
-        <v>10:00</v>
-      </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="1" t="s">
@@ -5647,8 +5367,8 @@
         <v>0.65</v>
       </c>
       <c r="G136" t="str">
-        <f t="shared" si="3"/>
-        <v>12:00</v>
+        <f>TEXT(A134,"HH:MM")</f>
+        <v>09:00</v>
       </c>
     </row>
     <row r="137" spans="1:7" hidden="1">
@@ -5664,10 +5384,6 @@
       <c r="F137" s="1">
         <v>0.91</v>
       </c>
-      <c r="G137" t="str">
-        <f t="shared" si="3"/>
-        <v>12:00</v>
-      </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="1" t="s">
@@ -5680,8 +5396,8 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="G138" t="str">
-        <f t="shared" si="3"/>
-        <v>13:00</v>
+        <f>TEXT(A136,"HH:MM")</f>
+        <v>12:00</v>
       </c>
     </row>
     <row r="139" spans="1:7" hidden="1">
@@ -5697,10 +5413,6 @@
       <c r="F139" s="1">
         <v>0.99</v>
       </c>
-      <c r="G139" t="str">
-        <f t="shared" si="3"/>
-        <v>13:00</v>
-      </c>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="1" t="s">
@@ -5713,8 +5425,8 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="G140" t="str">
-        <f t="shared" si="3"/>
-        <v>14:00</v>
+        <f>TEXT(A138,"HH:MM")</f>
+        <v>13:00</v>
       </c>
     </row>
     <row r="141" spans="1:7" hidden="1">
@@ -5730,10 +5442,6 @@
       <c r="F141" s="1">
         <v>0.89</v>
       </c>
-      <c r="G141" t="str">
-        <f t="shared" si="3"/>
-        <v>16:00</v>
-      </c>
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="1" t="s">
@@ -5746,8 +5454,8 @@
         <v>0.65</v>
       </c>
       <c r="G142" t="str">
-        <f t="shared" si="3"/>
-        <v>18:00</v>
+        <f>TEXT(A140,"HH:MM")</f>
+        <v>14:00</v>
       </c>
     </row>
     <row r="143" spans="1:7" hidden="1">
@@ -5763,10 +5471,6 @@
       <c r="F143" s="1">
         <v>0.82</v>
       </c>
-      <c r="G143" t="str">
-        <f t="shared" si="3"/>
-        <v>18:00</v>
-      </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="1" t="s">
@@ -5779,8 +5483,8 @@
         <v>0.47</v>
       </c>
       <c r="G144" t="str">
-        <f t="shared" ref="G144:G153" si="4">RIGHT(A144,5)</f>
-        <v>19:00</v>
+        <f>TEXT(A142,"HH:MM")</f>
+        <v>18:00</v>
       </c>
     </row>
     <row r="145" spans="1:7" hidden="1">
@@ -5796,10 +5500,6 @@
       <c r="F145" s="1">
         <v>0.7</v>
       </c>
-      <c r="G145" t="str">
-        <f t="shared" si="4"/>
-        <v>19:00</v>
-      </c>
     </row>
     <row r="146" spans="1:7">
       <c r="A146" s="1" t="s">
@@ -5812,8 +5512,8 @@
         <v>0.4</v>
       </c>
       <c r="G146" t="str">
-        <f t="shared" si="4"/>
-        <v>20:00</v>
+        <f t="shared" ref="G146:G147" si="13">TEXT(A144,"HH:MM")</f>
+        <v>19:00</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5827,8 +5527,8 @@
         <v>0.49</v>
       </c>
       <c r="G147" t="str">
-        <f t="shared" si="4"/>
-        <v>22:00</v>
+        <f t="shared" si="13"/>
+        <v>19:00</v>
       </c>
     </row>
     <row r="148" spans="1:7" hidden="1">
@@ -5844,10 +5544,6 @@
       <c r="F148" s="1">
         <v>0.24</v>
       </c>
-      <c r="G148" t="str">
-        <f t="shared" si="4"/>
-        <v>22:00</v>
-      </c>
     </row>
     <row r="149" spans="1:7" hidden="1">
       <c r="A149" s="1" t="s">
@@ -5862,10 +5558,6 @@
       <c r="F149" s="1">
         <v>0.69</v>
       </c>
-      <c r="G149" t="str">
-        <f t="shared" si="4"/>
-        <v>00:00</v>
-      </c>
     </row>
     <row r="150" spans="1:7" hidden="1">
       <c r="A150" s="1" t="s">
@@ -5880,10 +5572,6 @@
       <c r="F150" s="1">
         <v>0.46</v>
       </c>
-      <c r="G150" t="str">
-        <f t="shared" si="4"/>
-        <v>06:00</v>
-      </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="1" t="s">
@@ -5896,8 +5584,8 @@
         <v>0.88</v>
       </c>
       <c r="G151" t="str">
-        <f t="shared" si="4"/>
-        <v>07:00</v>
+        <f>TEXT(A149,"HH:MM")</f>
+        <v>00:00</v>
       </c>
     </row>
     <row r="152" spans="1:7" hidden="1">
@@ -5910,10 +5598,6 @@
       <c r="F152" s="1">
         <v>0.66</v>
       </c>
-      <c r="G152" t="str">
-        <f t="shared" si="4"/>
-        <v>07:00</v>
-      </c>
     </row>
     <row r="153" spans="1:7" hidden="1">
       <c r="A153" s="1" t="s">
@@ -5928,10 +5612,6 @@
       <c r="F153" s="1">
         <v>0.4</v>
       </c>
-      <c r="G153" t="str">
-        <f t="shared" si="4"/>
-        <v>07:30</v>
-      </c>
     </row>
     <row r="154" spans="1:7">
       <c r="A154" s="1" t="s">
@@ -5944,8 +5624,8 @@
         <v>0.84</v>
       </c>
       <c r="G154" t="str">
-        <f t="shared" ref="G154:G169" si="5">RIGHT(A154,5)</f>
-        <v>08:00</v>
+        <f t="shared" ref="G154:G155" si="14">TEXT(A152,"HH:MM")</f>
+        <v>07:00</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -5959,8 +5639,8 @@
         <v>0.24</v>
       </c>
       <c r="G155" t="str">
-        <f t="shared" si="5"/>
-        <v>09:00</v>
+        <f t="shared" si="14"/>
+        <v>07:30</v>
       </c>
     </row>
     <row r="156" spans="1:7" hidden="1">
@@ -5976,10 +5656,6 @@
       <c r="F156" s="1">
         <v>0.54</v>
       </c>
-      <c r="G156" t="str">
-        <f t="shared" si="5"/>
-        <v>10:00</v>
-      </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="1" t="s">
@@ -5992,8 +5668,8 @@
         <v>0.52</v>
       </c>
       <c r="G157" t="str">
-        <f t="shared" si="5"/>
-        <v>12:00</v>
+        <f>TEXT(A155,"HH:MM")</f>
+        <v>09:00</v>
       </c>
     </row>
     <row r="158" spans="1:7" hidden="1">
@@ -6009,10 +5685,6 @@
       <c r="F158" s="1">
         <v>0.93</v>
       </c>
-      <c r="G158" t="str">
-        <f t="shared" si="5"/>
-        <v>12:00</v>
-      </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="1" t="s">
@@ -6025,8 +5697,8 @@
         <v>0.85</v>
       </c>
       <c r="G159" t="str">
-        <f t="shared" si="5"/>
-        <v>13:00</v>
+        <f>TEXT(A157,"HH:MM")</f>
+        <v>12:00</v>
       </c>
     </row>
     <row r="160" spans="1:7" hidden="1">
@@ -6042,10 +5714,6 @@
       <c r="F160" s="1">
         <v>0.71</v>
       </c>
-      <c r="G160" t="str">
-        <f t="shared" si="5"/>
-        <v>13:00</v>
-      </c>
     </row>
     <row r="161" spans="1:7">
       <c r="A161" s="1" t="s">
@@ -6058,8 +5726,8 @@
         <v>0.65</v>
       </c>
       <c r="G161" t="str">
-        <f t="shared" si="5"/>
-        <v>14:00</v>
+        <f>TEXT(A159,"HH:MM")</f>
+        <v>13:00</v>
       </c>
     </row>
     <row r="162" spans="1:7" hidden="1">
@@ -6075,10 +5743,6 @@
       <c r="F162" s="1">
         <v>0.28999999999999998</v>
       </c>
-      <c r="G162" t="str">
-        <f t="shared" si="5"/>
-        <v>16:00</v>
-      </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="1" t="s">
@@ -6091,8 +5755,8 @@
         <v>0.42</v>
       </c>
       <c r="G163" t="str">
-        <f t="shared" si="5"/>
-        <v>18:00</v>
+        <f>TEXT(A161,"HH:MM")</f>
+        <v>14:00</v>
       </c>
     </row>
     <row r="164" spans="1:7" hidden="1">
@@ -6108,10 +5772,6 @@
       <c r="F164" s="1">
         <v>0.34</v>
       </c>
-      <c r="G164" t="str">
-        <f t="shared" si="5"/>
-        <v>18:00</v>
-      </c>
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="1" t="s">
@@ -6124,8 +5784,8 @@
         <v>0.54</v>
       </c>
       <c r="G165" t="str">
-        <f t="shared" si="5"/>
-        <v>19:00</v>
+        <f>TEXT(A163,"HH:MM")</f>
+        <v>18:00</v>
       </c>
     </row>
     <row r="166" spans="1:7" hidden="1">
@@ -6141,10 +5801,6 @@
       <c r="F166" s="1">
         <v>0.69</v>
       </c>
-      <c r="G166" t="str">
-        <f t="shared" si="5"/>
-        <v>19:00</v>
-      </c>
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="1" t="s">
@@ -6157,8 +5813,8 @@
         <v>0.27</v>
       </c>
       <c r="G167" t="str">
-        <f t="shared" si="5"/>
-        <v>20:00</v>
+        <f t="shared" ref="G167:G168" si="15">TEXT(A165,"HH:MM")</f>
+        <v>19:00</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -6172,8 +5828,8 @@
         <v>0.46</v>
       </c>
       <c r="G168" t="str">
-        <f t="shared" si="5"/>
-        <v>22:00</v>
+        <f t="shared" si="15"/>
+        <v>19:00</v>
       </c>
     </row>
     <row r="169" spans="1:7" hidden="1">
@@ -6188,10 +5844,6 @@
       </c>
       <c r="F169" s="1">
         <v>0.6</v>
-      </c>
-      <c r="G169" t="str">
-        <f t="shared" si="5"/>
-        <v>22:00</v>
       </c>
     </row>
   </sheetData>
